--- a/Financial Analysis/PYPL.xlsx
+++ b/Financial Analysis/PYPL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21912399-3E94-42FB-9A16-78F9B3BADFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E1653C-1623-471E-AC1A-7B08813D6220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7B33BECD-2B6A-465C-BF18-30C78DC6ADF8}"/>
   </bookViews>
@@ -226,7 +226,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Undervalued</t>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -748,14 +748,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="9">
-        <v>62.89</v>
+        <v>71.069999999999993</v>
       </c>
       <c r="E3" s="4">
-        <v>45776</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45867</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>62210.788</v>
+        <v>70302.444000000003</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -821,7 +821,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>57803.788</v>
+        <v>65895.444000000003</v>
       </c>
     </row>
   </sheetData>
@@ -5299,7 +5299,8 @@
         <v>59</v>
       </c>
       <c r="AX28" s="9">
-        <v>61</v>
+        <f>Main!D3</f>
+        <v>71.069999999999993</v>
       </c>
     </row>
     <row r="29" spans="1:146" x14ac:dyDescent="0.3">
@@ -5308,7 +5309,7 @@
       </c>
       <c r="AX29" s="10">
         <f>AX27/AX28-1</f>
-        <v>0.35514137882871299</v>
+        <v>0.16312964835446042</v>
       </c>
     </row>
     <row r="30" spans="1:146" x14ac:dyDescent="0.3">

--- a/Financial Analysis/PYPL.xlsx
+++ b/Financial Analysis/PYPL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E1653C-1623-471E-AC1A-7B08813D6220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1391F526-CEAA-4D42-9CBF-4D6788A0454E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7B33BECD-2B6A-465C-BF18-30C78DC6ADF8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t>Price</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q225 8K</t>
   </si>
   <si>
     <t>Slightly undervalued</t>
@@ -326,13 +329,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
@@ -350,7 +353,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14584680" y="0"/>
+          <a:off x="15803880" y="0"/>
           <a:ext cx="0" cy="5920740"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -748,17 +751,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="9">
-        <v>71.069999999999993</v>
+        <v>71.430000000000007</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45867</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45868</v>
       </c>
       <c r="G3" s="4">
-        <v>45867</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -766,11 +769,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <f>989.2</f>
-        <v>989.2</v>
+        <v>969</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -779,7 +781,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>70302.444000000003</v>
+        <v>69215.670000000013</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -787,11 +789,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <f>7449+3762+4613</f>
-        <v>15824</v>
+        <f>6688+3320+3645</f>
+        <v>13653</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -799,11 +801,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="1">
-        <f>11417</f>
-        <v>11417</v>
+        <f>11296</f>
+        <v>11296</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -812,7 +814,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>4407</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -821,7 +823,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>65895.444000000003</v>
+        <v>66858.670000000013</v>
       </c>
     </row>
   </sheetData>
@@ -1039,12 +1041,11 @@
         <v>7791</v>
       </c>
       <c r="X3" s="7">
-        <f>T3*1.02</f>
-        <v>8042.7</v>
+        <v>8288</v>
       </c>
       <c r="Y3" s="7">
-        <f>U3*1.03</f>
-        <v>8082.41</v>
+        <f>U3*1.02</f>
+        <v>8003.9400000000005</v>
       </c>
       <c r="Z3" s="7">
         <f>V3*1.01</f>
@@ -1078,47 +1079,47 @@
       </c>
       <c r="AJ3" s="7">
         <f>SUM(W3:Z3)</f>
-        <v>32365.77</v>
+        <v>32532.600000000002</v>
       </c>
       <c r="AK3" s="7">
         <f>AJ3*1.02</f>
-        <v>33013.085400000004</v>
+        <v>33183.252</v>
       </c>
       <c r="AL3" s="7">
         <f>AK3*1.02</f>
-        <v>33673.347108000002</v>
+        <v>33846.91704</v>
       </c>
       <c r="AM3" s="7">
         <f>AL3*1.02</f>
-        <v>34346.814050159999</v>
+        <v>34523.8553808</v>
       </c>
       <c r="AN3" s="7">
         <f t="shared" ref="AN3" si="0">AM3*1.02</f>
-        <v>35033.750331163203</v>
+        <v>35214.332488416003</v>
       </c>
       <c r="AO3" s="7">
         <f>AN3*1.01</f>
-        <v>35384.087834474834</v>
+        <v>35566.47581330016</v>
       </c>
       <c r="AP3" s="7">
         <f t="shared" ref="AP3:AT3" si="1">AO3*1.01</f>
-        <v>35737.928712819587</v>
+        <v>35922.140571433163</v>
       </c>
       <c r="AQ3" s="7">
         <f t="shared" si="1"/>
-        <v>36095.307999947785</v>
+        <v>36281.361977147499</v>
       </c>
       <c r="AR3" s="7">
         <f t="shared" si="1"/>
-        <v>36456.26107994726</v>
+        <v>36644.175596918976</v>
       </c>
       <c r="AS3" s="7">
         <f t="shared" si="1"/>
-        <v>36820.823690746736</v>
+        <v>37010.617352888163</v>
       </c>
       <c r="AT3" s="7">
         <f t="shared" si="1"/>
-        <v>37189.031927654207</v>
+        <v>37380.723526417045</v>
       </c>
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.3">
@@ -1188,7 +1189,9 @@
       <c r="W4" s="1">
         <v>3704</v>
       </c>
-      <c r="X4" s="1"/>
+      <c r="X4" s="1">
+        <v>3968</v>
+      </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AC4" s="1">
@@ -1296,7 +1299,9 @@
       <c r="W5" s="1">
         <v>371</v>
       </c>
-      <c r="X5" s="1"/>
+      <c r="X5" s="1">
+        <v>476</v>
+      </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AC5" s="1">
@@ -1404,7 +1409,9 @@
       <c r="W6" s="1">
         <v>398</v>
       </c>
-      <c r="X6" s="1"/>
+      <c r="X6" s="1">
+        <v>413</v>
+      </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AC6" s="1">
@@ -1450,7 +1457,7 @@
         <v>37</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" ref="C7:W7" si="2">SUM(C4:C6)</f>
+        <f t="shared" ref="C7:X7" si="2">SUM(C4:C6)</f>
         <v>2729</v>
       </c>
       <c r="D7" s="1">
@@ -1534,16 +1541,16 @@
         <v>4473</v>
       </c>
       <c r="X7" s="1">
-        <f t="shared" ref="X7:Z7" si="3">X3-X8</f>
-        <v>4584.3389999999999</v>
+        <f t="shared" si="2"/>
+        <v>4857</v>
       </c>
       <c r="Y7" s="1">
-        <f t="shared" si="3"/>
-        <v>4606.9737000000005</v>
+        <f t="shared" ref="Y7:Z7" si="3">Y3-Y8</f>
+        <v>4722.3245999999999</v>
       </c>
       <c r="Z7" s="1">
         <f t="shared" si="3"/>
-        <v>4816.3062</v>
+        <v>4900.8027999999995</v>
       </c>
       <c r="AC7" s="1">
         <f t="shared" ref="AC7:AH7" si="4">SUM(AC4:AC6)</f>
@@ -1575,47 +1582,47 @@
       </c>
       <c r="AJ7" s="1">
         <f>SUM(W7:Z7)</f>
-        <v>18480.618900000001</v>
+        <v>18953.127399999998</v>
       </c>
       <c r="AK7" s="1">
         <f t="shared" ref="AK7:AT7" si="5">AK3-AK8</f>
-        <v>18157.196970000001</v>
+        <v>18914.45364</v>
       </c>
       <c r="AL7" s="1">
         <f t="shared" si="5"/>
-        <v>18183.607438320003</v>
+        <v>18954.273542399998</v>
       </c>
       <c r="AM7" s="1">
         <f t="shared" si="5"/>
-        <v>18547.279587086399</v>
+        <v>19333.359013248002</v>
       </c>
       <c r="AN7" s="1">
         <f t="shared" si="5"/>
-        <v>18918.225178828128</v>
+        <v>19720.02619351296</v>
       </c>
       <c r="AO7" s="1">
         <f t="shared" si="5"/>
-        <v>19107.407430616411</v>
+        <v>19917.22645544809</v>
       </c>
       <c r="AP7" s="1">
         <f t="shared" si="5"/>
-        <v>19298.481504922576</v>
+        <v>20116.398720002573</v>
       </c>
       <c r="AQ7" s="1">
         <f t="shared" si="5"/>
-        <v>19491.466319971802</v>
+        <v>20317.5627072026</v>
       </c>
       <c r="AR7" s="1">
         <f t="shared" si="5"/>
-        <v>19686.380983171519</v>
+        <v>20520.738334274625</v>
       </c>
       <c r="AS7" s="1">
         <f t="shared" si="5"/>
-        <v>19883.244793003236</v>
+        <v>20725.945717617371</v>
       </c>
       <c r="AT7" s="1">
         <f t="shared" si="5"/>
-        <v>20082.077240933271</v>
+        <v>20933.205174793544</v>
       </c>
     </row>
     <row r="8" spans="1:46" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1624,7 +1631,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="7">
-        <f t="shared" ref="C8:W8" si="6">C3-C7</f>
+        <f t="shared" ref="C8:X8" si="6">C3-C7</f>
         <v>1889</v>
       </c>
       <c r="D8" s="7">
@@ -1708,88 +1715,88 @@
         <v>3318</v>
       </c>
       <c r="X8" s="7">
-        <f>X3*0.43</f>
-        <v>3458.3609999999999</v>
+        <f t="shared" si="6"/>
+        <v>3431</v>
       </c>
       <c r="Y8" s="7">
-        <f t="shared" ref="Y8:Z8" si="7">Y3*0.43</f>
-        <v>3475.4362999999998</v>
+        <f>Y3*0.41</f>
+        <v>3281.6154000000001</v>
       </c>
       <c r="Z8" s="7">
+        <f>Z3*0.42</f>
+        <v>3548.8571999999999</v>
+      </c>
+      <c r="AC8" s="7">
+        <f t="shared" ref="AC8:AJ8" si="7">AC3-AC7</f>
+        <v>7189</v>
+      </c>
+      <c r="AD8" s="7">
         <f t="shared" si="7"/>
-        <v>3633.3537999999999</v>
-      </c>
-      <c r="AC8" s="7">
-        <f t="shared" ref="AC8:AJ8" si="8">AC3-AC7</f>
-        <v>7189</v>
-      </c>
-      <c r="AD8" s="7">
+        <v>7987</v>
+      </c>
+      <c r="AE8" s="7">
+        <f t="shared" si="7"/>
+        <v>10001</v>
+      </c>
+      <c r="AF8" s="7">
+        <f t="shared" si="7"/>
+        <v>11921</v>
+      </c>
+      <c r="AG8" s="7">
+        <f t="shared" si="7"/>
+        <v>11653</v>
+      </c>
+      <c r="AH8" s="7">
+        <f t="shared" si="7"/>
+        <v>11785</v>
+      </c>
+      <c r="AI8" s="7">
+        <f t="shared" si="7"/>
+        <v>12890</v>
+      </c>
+      <c r="AJ8" s="7">
+        <f t="shared" si="7"/>
+        <v>13579.472600000005</v>
+      </c>
+      <c r="AK8" s="7">
+        <f>AK3*0.43</f>
+        <v>14268.798360000001</v>
+      </c>
+      <c r="AL8" s="7">
+        <f>AL3*0.44</f>
+        <v>14892.6434976</v>
+      </c>
+      <c r="AM8" s="7">
+        <f t="shared" ref="AM8:AT8" si="8">AM3*0.44</f>
+        <v>15190.496367551999</v>
+      </c>
+      <c r="AN8" s="7">
         <f t="shared" si="8"/>
-        <v>7987</v>
-      </c>
-      <c r="AE8" s="7">
+        <v>15494.306294903041</v>
+      </c>
+      <c r="AO8" s="7">
         <f t="shared" si="8"/>
-        <v>10001</v>
-      </c>
-      <c r="AF8" s="7">
+        <v>15649.24935785207</v>
+      </c>
+      <c r="AP8" s="7">
         <f t="shared" si="8"/>
-        <v>11921</v>
-      </c>
-      <c r="AG8" s="7">
+        <v>15805.741851430592</v>
+      </c>
+      <c r="AQ8" s="7">
         <f t="shared" si="8"/>
-        <v>11653</v>
-      </c>
-      <c r="AH8" s="7">
+        <v>15963.799269944899</v>
+      </c>
+      <c r="AR8" s="7">
         <f t="shared" si="8"/>
-        <v>11785</v>
-      </c>
-      <c r="AI8" s="7">
+        <v>16123.437262644349</v>
+      </c>
+      <c r="AS8" s="7">
         <f t="shared" si="8"/>
-        <v>12890</v>
-      </c>
-      <c r="AJ8" s="7">
+        <v>16284.671635270792</v>
+      </c>
+      <c r="AT8" s="7">
         <f t="shared" si="8"/>
-        <v>13885.151099999999</v>
-      </c>
-      <c r="AK8" s="7">
-        <f>AK3*0.45</f>
-        <v>14855.888430000003</v>
-      </c>
-      <c r="AL8" s="7">
-        <f>AL3*0.46</f>
-        <v>15489.739669680001</v>
-      </c>
-      <c r="AM8" s="7">
-        <f t="shared" ref="AM8:AT8" si="9">AM3*0.46</f>
-        <v>15799.5344630736</v>
-      </c>
-      <c r="AN8" s="7">
-        <f t="shared" si="9"/>
-        <v>16115.525152335074</v>
-      </c>
-      <c r="AO8" s="7">
-        <f t="shared" si="9"/>
-        <v>16276.680403858425</v>
-      </c>
-      <c r="AP8" s="7">
-        <f t="shared" si="9"/>
-        <v>16439.44720789701</v>
-      </c>
-      <c r="AQ8" s="7">
-        <f t="shared" si="9"/>
-        <v>16603.841679975983</v>
-      </c>
-      <c r="AR8" s="7">
-        <f t="shared" si="9"/>
-        <v>16769.880096775742</v>
-      </c>
-      <c r="AS8" s="7">
-        <f t="shared" si="9"/>
-        <v>16937.5788977435</v>
-      </c>
-      <c r="AT8" s="7">
-        <f t="shared" si="9"/>
-        <v>17106.954686720936</v>
+        <v>16447.518351623501</v>
       </c>
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.3">
@@ -1860,12 +1867,11 @@
         <v>488</v>
       </c>
       <c r="X9" s="1">
-        <f>X3*0.06</f>
-        <v>482.56199999999995</v>
+        <v>583</v>
       </c>
       <c r="Y9" s="1">
         <f>Y3*0.06</f>
-        <v>484.94459999999998</v>
+        <v>480.2364</v>
       </c>
       <c r="Z9" s="1">
         <f>Z3*0.07</f>
@@ -1898,48 +1904,48 @@
         <v>2001</v>
       </c>
       <c r="AJ9" s="1">
-        <f t="shared" ref="AJ9:AJ12" si="10">SUM(W9:Z9)</f>
-        <v>2046.9828</v>
+        <f t="shared" ref="AJ9:AJ12" si="9">SUM(W9:Z9)</f>
+        <v>2142.7125999999998</v>
       </c>
       <c r="AK9" s="1">
-        <f t="shared" ref="AK9:AT9" si="11">AK3*0.06</f>
-        <v>1980.7851240000002</v>
+        <f>AK3*0.07</f>
+        <v>2322.8276400000004</v>
       </c>
       <c r="AL9" s="1">
-        <f t="shared" si="11"/>
-        <v>2020.40082648</v>
+        <f t="shared" ref="AL9:AT9" si="10">AL3*0.07</f>
+        <v>2369.2841928000003</v>
       </c>
       <c r="AM9" s="1">
-        <f t="shared" si="11"/>
-        <v>2060.8088430096</v>
+        <f t="shared" si="10"/>
+        <v>2416.6698766560003</v>
       </c>
       <c r="AN9" s="1">
-        <f t="shared" si="11"/>
-        <v>2102.0250198697922</v>
+        <f t="shared" si="10"/>
+        <v>2465.0032741891205</v>
       </c>
       <c r="AO9" s="1">
-        <f t="shared" si="11"/>
-        <v>2123.04527006849</v>
+        <f t="shared" si="10"/>
+        <v>2489.6533069310112</v>
       </c>
       <c r="AP9" s="1">
-        <f t="shared" si="11"/>
-        <v>2144.275722769175</v>
+        <f t="shared" si="10"/>
+        <v>2514.5498400003216</v>
       </c>
       <c r="AQ9" s="1">
-        <f t="shared" si="11"/>
-        <v>2165.7184799968672</v>
+        <f t="shared" si="10"/>
+        <v>2539.695338400325</v>
       </c>
       <c r="AR9" s="1">
-        <f t="shared" si="11"/>
-        <v>2187.3756647968357</v>
+        <f t="shared" si="10"/>
+        <v>2565.0922917843286</v>
       </c>
       <c r="AS9" s="1">
-        <f t="shared" si="11"/>
-        <v>2209.2494214448043</v>
+        <f t="shared" si="10"/>
+        <v>2590.7432147021718</v>
       </c>
       <c r="AT9" s="1">
-        <f t="shared" si="11"/>
-        <v>2231.3419156592522</v>
+        <f t="shared" si="10"/>
+        <v>2616.6506468491934</v>
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.3">
@@ -2010,15 +2016,14 @@
         <v>731</v>
       </c>
       <c r="X10" s="1">
-        <f t="shared" ref="X10:Z10" si="12">T10*1.01</f>
-        <v>725.18</v>
+        <v>767</v>
       </c>
       <c r="Y10" s="1">
-        <f t="shared" si="12"/>
-        <v>753.46</v>
+        <f>U10*1.04</f>
+        <v>775.84</v>
       </c>
       <c r="Z10" s="1">
-        <f t="shared" si="12"/>
+        <f>V10*1.01</f>
         <v>780.73</v>
       </c>
       <c r="AC10" s="1">
@@ -2048,48 +2053,48 @@
         <v>2979</v>
       </c>
       <c r="AJ10" s="1">
-        <f t="shared" si="10"/>
-        <v>2990.37</v>
+        <f t="shared" si="9"/>
+        <v>3054.57</v>
       </c>
       <c r="AK10" s="1">
-        <f t="shared" ref="AK10" si="13">AJ10*1.02</f>
-        <v>3050.1774</v>
+        <f t="shared" ref="AK10" si="11">AJ10*1.02</f>
+        <v>3115.6614000000004</v>
       </c>
       <c r="AL10" s="1">
         <f>AK10*1.01</f>
-        <v>3080.6791739999999</v>
+        <v>3146.8180140000004</v>
       </c>
       <c r="AM10" s="1">
-        <f t="shared" ref="AM10:AT10" si="14">AL10*1.01</f>
-        <v>3111.4859657399998</v>
+        <f t="shared" ref="AM10:AT10" si="12">AL10*1.01</f>
+        <v>3178.2861941400006</v>
       </c>
       <c r="AN10" s="1">
-        <f t="shared" si="14"/>
-        <v>3142.6008253973996</v>
+        <f t="shared" si="12"/>
+        <v>3210.0690560814005</v>
       </c>
       <c r="AO10" s="1">
-        <f t="shared" si="14"/>
-        <v>3174.0268336513736</v>
+        <f t="shared" si="12"/>
+        <v>3242.1697466422147</v>
       </c>
       <c r="AP10" s="1">
-        <f t="shared" si="14"/>
-        <v>3205.7671019878876</v>
+        <f t="shared" si="12"/>
+        <v>3274.591444108637</v>
       </c>
       <c r="AQ10" s="1">
-        <f t="shared" si="14"/>
-        <v>3237.8247730077665</v>
+        <f t="shared" si="12"/>
+        <v>3307.3373585497234</v>
       </c>
       <c r="AR10" s="1">
-        <f t="shared" si="14"/>
-        <v>3270.2030207378443</v>
+        <f t="shared" si="12"/>
+        <v>3340.4107321352208</v>
       </c>
       <c r="AS10" s="1">
-        <f t="shared" si="14"/>
-        <v>3302.9050509452227</v>
+        <f t="shared" si="12"/>
+        <v>3373.8148394565728</v>
       </c>
       <c r="AT10" s="1">
-        <f t="shared" si="14"/>
-        <v>3335.9341014546749</v>
+        <f t="shared" si="12"/>
+        <v>3407.5529878511384</v>
       </c>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.3">
@@ -2160,16 +2165,15 @@
         <v>503</v>
       </c>
       <c r="X11" s="1">
-        <f>T11*0.95</f>
-        <v>541.5</v>
+        <v>461</v>
       </c>
       <c r="Y11" s="1">
-        <f t="shared" ref="Y11" si="15">U11*1.05</f>
-        <v>544.95000000000005</v>
+        <f>U11*0.98</f>
+        <v>508.62</v>
       </c>
       <c r="Z11" s="1">
-        <f>V11*1.03</f>
-        <v>611.82000000000005</v>
+        <f t="shared" ref="Z11" si="13">V11*0.98</f>
+        <v>582.12</v>
       </c>
       <c r="AC11" s="1">
         <v>1541</v>
@@ -2198,48 +2202,48 @@
         <v>2147</v>
       </c>
       <c r="AJ11" s="1">
-        <f t="shared" si="10"/>
-        <v>2201.27</v>
+        <f t="shared" si="9"/>
+        <v>2054.7399999999998</v>
       </c>
       <c r="AK11" s="1">
         <f>AJ11*1.02</f>
-        <v>2245.2954</v>
+        <v>2095.8347999999996</v>
       </c>
       <c r="AL11" s="1">
-        <f t="shared" ref="AL11:AT11" si="16">AK11*1.01</f>
-        <v>2267.7483539999998</v>
+        <f t="shared" ref="AL11:AT11" si="14">AK11*1.01</f>
+        <v>2116.7931479999997</v>
       </c>
       <c r="AM11" s="1">
-        <f t="shared" si="16"/>
-        <v>2290.42583754</v>
+        <f t="shared" si="14"/>
+        <v>2137.9610794799996</v>
       </c>
       <c r="AN11" s="1">
-        <f t="shared" si="16"/>
-        <v>2313.3300959153999</v>
+        <f t="shared" si="14"/>
+        <v>2159.3406902747997</v>
       </c>
       <c r="AO11" s="1">
-        <f t="shared" si="16"/>
-        <v>2336.4633968745538</v>
+        <f t="shared" si="14"/>
+        <v>2180.9340971775478</v>
       </c>
       <c r="AP11" s="1">
-        <f t="shared" si="16"/>
-        <v>2359.8280308432995</v>
+        <f t="shared" si="14"/>
+        <v>2202.7434381493231</v>
       </c>
       <c r="AQ11" s="1">
-        <f t="shared" si="16"/>
-        <v>2383.4263111517325</v>
+        <f t="shared" si="14"/>
+        <v>2224.7708725308162</v>
       </c>
       <c r="AR11" s="1">
-        <f t="shared" si="16"/>
-        <v>2407.26057426325</v>
+        <f t="shared" si="14"/>
+        <v>2247.0185812561244</v>
       </c>
       <c r="AS11" s="1">
-        <f t="shared" si="16"/>
-        <v>2431.3331800058827</v>
+        <f t="shared" si="14"/>
+        <v>2269.4887670686858</v>
       </c>
       <c r="AT11" s="1">
-        <f t="shared" si="16"/>
-        <v>2455.6465118059414</v>
+        <f t="shared" si="14"/>
+        <v>2292.1836547393727</v>
       </c>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.3">
@@ -2310,10 +2314,10 @@
         <v>66</v>
       </c>
       <c r="X12" s="1">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="Y12" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Z12" s="1">
         <v>50</v>
@@ -2345,8 +2349,8 @@
         <v>438</v>
       </c>
       <c r="AJ12" s="1">
-        <f t="shared" si="10"/>
-        <v>216</v>
+        <f t="shared" si="9"/>
+        <v>332</v>
       </c>
       <c r="AK12" s="1">
         <v>100</v>
@@ -2385,172 +2389,172 @@
         <v>31</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:S13" si="17">C8-SUM(C9:C12)</f>
+        <f t="shared" ref="C13:S13" si="15">C8-SUM(C9:C12)</f>
         <v>398</v>
       </c>
       <c r="D13" s="7">
+        <f t="shared" si="15"/>
+        <v>951</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="15"/>
+        <v>977</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="15"/>
+        <v>963</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="15"/>
+        <v>1042</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="15"/>
+        <v>1127</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="15"/>
+        <v>1043</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="15"/>
+        <v>1050</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="15"/>
+        <v>711</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="15"/>
+        <v>764</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="15"/>
+        <v>1118</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="15"/>
+        <v>1244</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" si="15"/>
+        <v>999</v>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" si="15"/>
+        <v>1133</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="15"/>
+        <v>1168</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="15"/>
+        <v>1728</v>
+      </c>
+      <c r="S13" s="7">
+        <f t="shared" si="15"/>
+        <v>1168</v>
+      </c>
+      <c r="T13" s="7">
+        <f t="shared" ref="T13:Z13" si="16">T8-SUM(T9:T12)</f>
+        <v>1325</v>
+      </c>
+      <c r="U13" s="7">
+        <f t="shared" si="16"/>
+        <v>1391</v>
+      </c>
+      <c r="V13" s="7">
+        <f t="shared" si="16"/>
+        <v>1441</v>
+      </c>
+      <c r="W13" s="7">
+        <f t="shared" si="16"/>
+        <v>1530</v>
+      </c>
+      <c r="X13" s="7">
+        <f t="shared" si="16"/>
+        <v>1504</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="16"/>
+        <v>1416.9190000000003</v>
+      </c>
+      <c r="Z13" s="7">
+        <f t="shared" si="16"/>
+        <v>1544.5309999999999</v>
+      </c>
+      <c r="AC13" s="7">
+        <f t="shared" ref="AC13:AJ13" si="17">AC8-SUM(AC9:AC12)</f>
+        <v>2194</v>
+      </c>
+      <c r="AD13" s="7">
         <f t="shared" si="17"/>
-        <v>951</v>
-      </c>
-      <c r="E13" s="7">
+        <v>2719</v>
+      </c>
+      <c r="AE13" s="7">
         <f t="shared" si="17"/>
-        <v>977</v>
-      </c>
-      <c r="F13" s="7">
+        <v>3289</v>
+      </c>
+      <c r="AF13" s="7">
         <f t="shared" si="17"/>
-        <v>963</v>
-      </c>
-      <c r="G13" s="7">
+        <v>4262</v>
+      </c>
+      <c r="AG13" s="7">
         <f t="shared" si="17"/>
-        <v>1042</v>
-      </c>
-      <c r="H13" s="7">
+        <v>3837</v>
+      </c>
+      <c r="AH13" s="7">
         <f t="shared" si="17"/>
-        <v>1127</v>
-      </c>
-      <c r="I13" s="7">
+        <v>5028</v>
+      </c>
+      <c r="AI13" s="7">
         <f t="shared" si="17"/>
-        <v>1043</v>
-      </c>
-      <c r="J13" s="7">
+        <v>5325</v>
+      </c>
+      <c r="AJ13" s="7">
         <f t="shared" si="17"/>
-        <v>1050</v>
-      </c>
-      <c r="K13" s="7">
-        <f t="shared" si="17"/>
-        <v>711</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="17"/>
-        <v>764</v>
-      </c>
-      <c r="M13" s="7">
-        <f t="shared" si="17"/>
-        <v>1118</v>
-      </c>
-      <c r="N13" s="7">
-        <f t="shared" si="17"/>
-        <v>1244</v>
-      </c>
-      <c r="O13" s="7">
-        <f t="shared" si="17"/>
-        <v>999</v>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="17"/>
-        <v>1133</v>
-      </c>
-      <c r="Q13" s="7">
-        <f t="shared" si="17"/>
-        <v>1168</v>
-      </c>
-      <c r="R13" s="7">
-        <f t="shared" si="17"/>
-        <v>1728</v>
-      </c>
-      <c r="S13" s="7">
-        <f t="shared" si="17"/>
-        <v>1168</v>
-      </c>
-      <c r="T13" s="7">
-        <f t="shared" ref="T13:Z13" si="18">T8-SUM(T9:T12)</f>
-        <v>1325</v>
-      </c>
-      <c r="U13" s="7">
+        <v>5995.4500000000044</v>
+      </c>
+      <c r="AK13" s="7">
+        <f t="shared" ref="AK13:AT13" si="18">AK8-SUM(AK9:AK12)</f>
+        <v>6634.4745200000007</v>
+      </c>
+      <c r="AL13" s="7">
         <f t="shared" si="18"/>
-        <v>1391</v>
-      </c>
-      <c r="V13" s="7">
+        <v>7159.7481428000001</v>
+      </c>
+      <c r="AM13" s="7">
         <f t="shared" si="18"/>
-        <v>1441</v>
-      </c>
-      <c r="W13" s="7">
+        <v>7357.5792172759993</v>
+      </c>
+      <c r="AN13" s="7">
         <f t="shared" si="18"/>
-        <v>1530</v>
-      </c>
-      <c r="X13" s="7">
+        <v>7559.8932743577207</v>
+      </c>
+      <c r="AO13" s="7">
         <f t="shared" si="18"/>
-        <v>1659.1189999999999</v>
-      </c>
-      <c r="Y13" s="7">
+        <v>7636.492207101297</v>
+      </c>
+      <c r="AP13" s="7">
         <f t="shared" si="18"/>
-        <v>1642.0816999999997</v>
-      </c>
-      <c r="Z13" s="7">
+        <v>7713.8571291723101</v>
+      </c>
+      <c r="AQ13" s="7">
         <f t="shared" si="18"/>
-        <v>1599.3275999999996</v>
-      </c>
-      <c r="AC13" s="7">
-        <f t="shared" ref="AC13:AJ13" si="19">AC8-SUM(AC9:AC12)</f>
-        <v>2194</v>
-      </c>
-      <c r="AD13" s="7">
-        <f t="shared" si="19"/>
-        <v>2719</v>
-      </c>
-      <c r="AE13" s="7">
-        <f t="shared" si="19"/>
-        <v>3289</v>
-      </c>
-      <c r="AF13" s="7">
-        <f t="shared" si="19"/>
-        <v>4262</v>
-      </c>
-      <c r="AG13" s="7">
-        <f t="shared" si="19"/>
-        <v>3837</v>
-      </c>
-      <c r="AH13" s="7">
-        <f t="shared" si="19"/>
-        <v>5028</v>
-      </c>
-      <c r="AI13" s="7">
-        <f t="shared" si="19"/>
-        <v>5325</v>
-      </c>
-      <c r="AJ13" s="7">
-        <f t="shared" si="19"/>
-        <v>6430.5282999999999</v>
-      </c>
-      <c r="AK13" s="7">
-        <f t="shared" ref="AK13:AT13" si="20">AK8-SUM(AK9:AK12)</f>
-        <v>7479.6305060000022</v>
-      </c>
-      <c r="AL13" s="7">
-        <f t="shared" si="20"/>
-        <v>8020.9113152000009</v>
-      </c>
-      <c r="AM13" s="7">
-        <f t="shared" si="20"/>
-        <v>8236.8138167840007</v>
-      </c>
-      <c r="AN13" s="7">
-        <f t="shared" si="20"/>
-        <v>8457.5692111524822</v>
-      </c>
-      <c r="AO13" s="7">
-        <f t="shared" si="20"/>
-        <v>8543.1449032640085</v>
-      </c>
-      <c r="AP13" s="7">
-        <f t="shared" si="20"/>
-        <v>8629.5763522966481</v>
-      </c>
-      <c r="AQ13" s="7">
-        <f t="shared" si="20"/>
-        <v>8716.8721158196167</v>
+        <v>7791.9957004640346</v>
       </c>
       <c r="AR13" s="7">
-        <f t="shared" si="20"/>
-        <v>8805.0408369778124</v>
+        <f t="shared" si="18"/>
+        <v>7870.9156574686749</v>
       </c>
       <c r="AS13" s="7">
-        <f t="shared" si="20"/>
-        <v>8894.0912453475903</v>
+        <f t="shared" si="18"/>
+        <v>7950.6248140433618</v>
       </c>
       <c r="AT13" s="7">
-        <f t="shared" si="20"/>
-        <v>8984.0321578010662</v>
+        <f t="shared" si="18"/>
+        <v>8031.1310621837965</v>
       </c>
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.3">
@@ -2621,7 +2625,7 @@
         <v>-73</v>
       </c>
       <c r="X14" s="1">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="Y14" s="1">
         <v>-20</v>
@@ -2657,7 +2661,7 @@
       </c>
       <c r="AJ14" s="1">
         <f>SUM(W14:Z14)</f>
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="AK14" s="1">
         <v>0</v>
@@ -2696,172 +2700,172 @@
         <v>33</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:S15" si="21">C13-C14</f>
+        <f t="shared" ref="C15:S15" si="19">C13-C14</f>
         <v>263</v>
       </c>
       <c r="D15" s="7">
+        <f t="shared" si="19"/>
+        <v>1799</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="19"/>
+        <v>1144</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="19"/>
+        <v>1859</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="19"/>
+        <v>872</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="19"/>
+        <v>1356</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="19"/>
+        <v>1165</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="19"/>
+        <v>706</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="19"/>
+        <v>629</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="19"/>
+        <v>49</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="19"/>
+        <v>1578</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="19"/>
+        <v>1110</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" si="19"/>
+        <v>1074</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" si="19"/>
+        <v>1303</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="19"/>
+        <v>1241</v>
+      </c>
+      <c r="R15" s="7">
+        <f t="shared" si="19"/>
+        <v>1793</v>
+      </c>
+      <c r="S15" s="7">
+        <f t="shared" si="19"/>
+        <v>1209</v>
+      </c>
+      <c r="T15" s="7">
+        <f t="shared" ref="T15:Z15" si="20">T13-T14</f>
+        <v>1399</v>
+      </c>
+      <c r="U15" s="7">
+        <f t="shared" si="20"/>
+        <v>1311</v>
+      </c>
+      <c r="V15" s="7">
+        <f t="shared" si="20"/>
+        <v>1410</v>
+      </c>
+      <c r="W15" s="7">
+        <f t="shared" si="20"/>
+        <v>1603</v>
+      </c>
+      <c r="X15" s="7">
+        <f t="shared" si="20"/>
+        <v>1529</v>
+      </c>
+      <c r="Y15" s="7">
+        <f t="shared" si="20"/>
+        <v>1436.9190000000003</v>
+      </c>
+      <c r="Z15" s="7">
+        <f t="shared" si="20"/>
+        <v>1564.5309999999999</v>
+      </c>
+      <c r="AC15" s="7">
+        <f t="shared" ref="AC15:AJ15" si="21">AC13-AC14</f>
+        <v>2376</v>
+      </c>
+      <c r="AD15" s="7">
         <f t="shared" si="21"/>
-        <v>1799</v>
-      </c>
-      <c r="E15" s="7">
+        <v>2998</v>
+      </c>
+      <c r="AE15" s="7">
         <f t="shared" si="21"/>
-        <v>1144</v>
-      </c>
-      <c r="F15" s="7">
+        <v>5065</v>
+      </c>
+      <c r="AF15" s="7">
         <f t="shared" si="21"/>
-        <v>1859</v>
-      </c>
-      <c r="G15" s="7">
+        <v>4099</v>
+      </c>
+      <c r="AG15" s="7">
         <f t="shared" si="21"/>
-        <v>872</v>
-      </c>
-      <c r="H15" s="7">
+        <v>3366</v>
+      </c>
+      <c r="AH15" s="7">
         <f t="shared" si="21"/>
-        <v>1356</v>
-      </c>
-      <c r="I15" s="7">
+        <v>5411</v>
+      </c>
+      <c r="AI15" s="7">
         <f t="shared" si="21"/>
-        <v>1165</v>
-      </c>
-      <c r="J15" s="7">
+        <v>5329</v>
+      </c>
+      <c r="AJ15" s="7">
         <f t="shared" si="21"/>
-        <v>706</v>
-      </c>
-      <c r="K15" s="7">
-        <f t="shared" si="21"/>
-        <v>629</v>
-      </c>
-      <c r="L15" s="7">
-        <f t="shared" si="21"/>
-        <v>49</v>
-      </c>
-      <c r="M15" s="7">
-        <f t="shared" si="21"/>
-        <v>1578</v>
-      </c>
-      <c r="N15" s="7">
-        <f t="shared" si="21"/>
-        <v>1110</v>
-      </c>
-      <c r="O15" s="7">
-        <f t="shared" si="21"/>
-        <v>1074</v>
-      </c>
-      <c r="P15" s="7">
-        <f t="shared" si="21"/>
-        <v>1303</v>
-      </c>
-      <c r="Q15" s="7">
-        <f t="shared" si="21"/>
-        <v>1241</v>
-      </c>
-      <c r="R15" s="7">
-        <f t="shared" si="21"/>
-        <v>1793</v>
-      </c>
-      <c r="S15" s="7">
-        <f t="shared" si="21"/>
-        <v>1209</v>
-      </c>
-      <c r="T15" s="7">
-        <f t="shared" ref="T15:Z15" si="22">T13-T14</f>
-        <v>1399</v>
-      </c>
-      <c r="U15" s="7">
+        <v>6133.4500000000044</v>
+      </c>
+      <c r="AK15" s="7">
+        <f t="shared" ref="AK15:AT15" si="22">AK13-AK14</f>
+        <v>6634.4745200000007</v>
+      </c>
+      <c r="AL15" s="7">
         <f t="shared" si="22"/>
-        <v>1311</v>
-      </c>
-      <c r="V15" s="7">
+        <v>7159.7481428000001</v>
+      </c>
+      <c r="AM15" s="7">
         <f t="shared" si="22"/>
-        <v>1410</v>
-      </c>
-      <c r="W15" s="7">
+        <v>7357.5792172759993</v>
+      </c>
+      <c r="AN15" s="7">
         <f t="shared" si="22"/>
-        <v>1603</v>
-      </c>
-      <c r="X15" s="7">
+        <v>7559.8932743577207</v>
+      </c>
+      <c r="AO15" s="7">
         <f t="shared" si="22"/>
-        <v>1679.1189999999999</v>
-      </c>
-      <c r="Y15" s="7">
+        <v>7636.492207101297</v>
+      </c>
+      <c r="AP15" s="7">
         <f t="shared" si="22"/>
-        <v>1662.0816999999997</v>
-      </c>
-      <c r="Z15" s="7">
+        <v>7713.8571291723101</v>
+      </c>
+      <c r="AQ15" s="7">
         <f t="shared" si="22"/>
-        <v>1619.3275999999996</v>
-      </c>
-      <c r="AC15" s="7">
-        <f t="shared" ref="AC15:AJ15" si="23">AC13-AC14</f>
-        <v>2376</v>
-      </c>
-      <c r="AD15" s="7">
-        <f t="shared" si="23"/>
-        <v>2998</v>
-      </c>
-      <c r="AE15" s="7">
-        <f t="shared" si="23"/>
-        <v>5065</v>
-      </c>
-      <c r="AF15" s="7">
-        <f t="shared" si="23"/>
-        <v>4099</v>
-      </c>
-      <c r="AG15" s="7">
-        <f t="shared" si="23"/>
-        <v>3366</v>
-      </c>
-      <c r="AH15" s="7">
-        <f t="shared" si="23"/>
-        <v>5411</v>
-      </c>
-      <c r="AI15" s="7">
-        <f t="shared" si="23"/>
-        <v>5329</v>
-      </c>
-      <c r="AJ15" s="7">
-        <f t="shared" si="23"/>
-        <v>6563.5282999999999</v>
-      </c>
-      <c r="AK15" s="7">
-        <f t="shared" ref="AK15:AT15" si="24">AK13-AK14</f>
-        <v>7479.6305060000022</v>
-      </c>
-      <c r="AL15" s="7">
-        <f t="shared" si="24"/>
-        <v>8020.9113152000009</v>
-      </c>
-      <c r="AM15" s="7">
-        <f t="shared" si="24"/>
-        <v>8236.8138167840007</v>
-      </c>
-      <c r="AN15" s="7">
-        <f t="shared" si="24"/>
-        <v>8457.5692111524822</v>
-      </c>
-      <c r="AO15" s="7">
-        <f t="shared" si="24"/>
-        <v>8543.1449032640085</v>
-      </c>
-      <c r="AP15" s="7">
-        <f t="shared" si="24"/>
-        <v>8629.5763522966481</v>
-      </c>
-      <c r="AQ15" s="7">
-        <f t="shared" si="24"/>
-        <v>8716.8721158196167</v>
+        <v>7791.9957004640346</v>
       </c>
       <c r="AR15" s="7">
-        <f t="shared" si="24"/>
-        <v>8805.0408369778124</v>
+        <f t="shared" si="22"/>
+        <v>7870.9156574686749</v>
       </c>
       <c r="AS15" s="7">
-        <f t="shared" si="24"/>
-        <v>8894.0912453475903</v>
+        <f t="shared" si="22"/>
+        <v>7950.6248140433618</v>
       </c>
       <c r="AT15" s="7">
-        <f t="shared" si="24"/>
-        <v>8984.0321578010662</v>
+        <f t="shared" si="22"/>
+        <v>8031.1310621837965</v>
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.3">
@@ -2932,16 +2936,15 @@
         <v>316</v>
       </c>
       <c r="X16" s="1">
-        <f t="shared" ref="X16:Z16" si="25">X15*0.22</f>
-        <v>369.40618000000001</v>
+        <v>268</v>
       </c>
       <c r="Y16" s="1">
-        <f t="shared" si="25"/>
-        <v>365.65797399999997</v>
+        <f>Y15*0.2</f>
+        <v>287.38380000000006</v>
       </c>
       <c r="Z16" s="1">
-        <f t="shared" si="25"/>
-        <v>356.25207199999994</v>
+        <f t="shared" ref="Z16" si="23">Z15*0.2</f>
+        <v>312.90620000000001</v>
       </c>
       <c r="AC16" s="1">
         <v>319</v>
@@ -2971,47 +2974,47 @@
       </c>
       <c r="AJ16" s="1">
         <f>SUM(W16:Z16)</f>
-        <v>1407.3162259999999</v>
+        <v>1184.29</v>
       </c>
       <c r="AK16" s="1">
-        <f t="shared" ref="AK16:AT16" si="26">AK15*0.22</f>
-        <v>1645.5187113200004</v>
+        <f>AK15*0.2</f>
+        <v>1326.8949040000002</v>
       </c>
       <c r="AL16" s="1">
-        <f t="shared" si="26"/>
-        <v>1764.6004893440002</v>
+        <f t="shared" ref="AL16:AT16" si="24">AL15*0.2</f>
+        <v>1431.9496285600001</v>
       </c>
       <c r="AM16" s="1">
-        <f t="shared" si="26"/>
-        <v>1812.0990396924801</v>
+        <f t="shared" si="24"/>
+        <v>1471.5158434552</v>
       </c>
       <c r="AN16" s="1">
-        <f t="shared" si="26"/>
-        <v>1860.6652264535462</v>
+        <f t="shared" si="24"/>
+        <v>1511.9786548715442</v>
       </c>
       <c r="AO16" s="1">
-        <f t="shared" si="26"/>
-        <v>1879.4918787180818</v>
+        <f t="shared" si="24"/>
+        <v>1527.2984414202595</v>
       </c>
       <c r="AP16" s="1">
-        <f t="shared" si="26"/>
-        <v>1898.5067975052625</v>
+        <f t="shared" si="24"/>
+        <v>1542.7714258344622</v>
       </c>
       <c r="AQ16" s="1">
-        <f t="shared" si="26"/>
-        <v>1917.7118654803157</v>
+        <f t="shared" si="24"/>
+        <v>1558.3991400928071</v>
       </c>
       <c r="AR16" s="1">
-        <f t="shared" si="26"/>
-        <v>1937.1089841351188</v>
+        <f t="shared" si="24"/>
+        <v>1574.1831314937351</v>
       </c>
       <c r="AS16" s="1">
-        <f t="shared" si="26"/>
-        <v>1956.7000739764699</v>
+        <f t="shared" si="24"/>
+        <v>1590.1249628086725</v>
       </c>
       <c r="AT16" s="1">
-        <f t="shared" si="26"/>
-        <v>1976.4870747162345</v>
+        <f t="shared" si="24"/>
+        <v>1606.2262124367594</v>
       </c>
     </row>
     <row r="17" spans="1:146" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3020,572 +3023,572 @@
         <v>35</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:S17" si="27">C15-C16</f>
+        <f t="shared" ref="C17:S17" si="25">C15-C16</f>
         <v>84</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="25"/>
+        <v>1530</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="25"/>
+        <v>1021</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="25"/>
+        <v>1567</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="25"/>
+        <v>1097</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="25"/>
+        <v>1184</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="25"/>
+        <v>1087</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="25"/>
+        <v>801</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="25"/>
+        <v>509</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="25"/>
+        <v>-341</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" si="25"/>
+        <v>1330</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="25"/>
+        <v>921</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="25"/>
+        <v>795</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="25"/>
+        <v>1029</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="25"/>
+        <v>1020</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="25"/>
+        <v>1402</v>
+      </c>
+      <c r="S17" s="7">
+        <f t="shared" si="25"/>
+        <v>888</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:V17" si="26">T15-T16</f>
+        <v>1128</v>
+      </c>
+      <c r="U17" s="7">
+        <f t="shared" si="26"/>
+        <v>1010</v>
+      </c>
+      <c r="V17" s="7">
+        <f t="shared" si="26"/>
+        <v>1121</v>
+      </c>
+      <c r="W17" s="7">
+        <f t="shared" ref="W17:Z17" si="27">W15-W16</f>
+        <v>1287</v>
+      </c>
+      <c r="X17" s="7">
         <f t="shared" si="27"/>
-        <v>1530</v>
-      </c>
-      <c r="E17" s="7">
+        <v>1261</v>
+      </c>
+      <c r="Y17" s="7">
         <f t="shared" si="27"/>
-        <v>1021</v>
-      </c>
-      <c r="F17" s="7">
+        <v>1149.5352000000003</v>
+      </c>
+      <c r="Z17" s="7">
         <f t="shared" si="27"/>
-        <v>1567</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="27"/>
-        <v>1097</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="27"/>
-        <v>1184</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="27"/>
-        <v>1087</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="27"/>
-        <v>801</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="27"/>
-        <v>509</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="27"/>
-        <v>-341</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" si="27"/>
-        <v>1330</v>
-      </c>
-      <c r="N17" s="7">
-        <f t="shared" si="27"/>
-        <v>921</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" si="27"/>
-        <v>795</v>
-      </c>
-      <c r="P17" s="7">
-        <f t="shared" si="27"/>
-        <v>1029</v>
-      </c>
-      <c r="Q17" s="7">
-        <f t="shared" si="27"/>
-        <v>1020</v>
-      </c>
-      <c r="R17" s="7">
-        <f t="shared" si="27"/>
-        <v>1402</v>
-      </c>
-      <c r="S17" s="7">
-        <f t="shared" si="27"/>
-        <v>888</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:V17" si="28">T15-T16</f>
-        <v>1128</v>
-      </c>
-      <c r="U17" s="7">
+        <v>1251.6248000000001</v>
+      </c>
+      <c r="AC17" s="7">
+        <f t="shared" ref="AC17:AJ17" si="28">AC15-AC16</f>
+        <v>2057</v>
+      </c>
+      <c r="AD17" s="7">
         <f t="shared" si="28"/>
-        <v>1010</v>
-      </c>
-      <c r="V17" s="7">
+        <v>2459</v>
+      </c>
+      <c r="AE17" s="7">
         <f t="shared" si="28"/>
-        <v>1121</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" ref="W17:Z17" si="29">W15-W16</f>
-        <v>1287</v>
-      </c>
-      <c r="X17" s="7">
+        <v>4202</v>
+      </c>
+      <c r="AF17" s="7">
+        <f t="shared" si="28"/>
+        <v>4169</v>
+      </c>
+      <c r="AG17" s="7">
+        <f t="shared" si="28"/>
+        <v>2419</v>
+      </c>
+      <c r="AH17" s="7">
+        <f t="shared" si="28"/>
+        <v>4246</v>
+      </c>
+      <c r="AI17" s="7">
+        <f t="shared" si="28"/>
+        <v>4147</v>
+      </c>
+      <c r="AJ17" s="7">
+        <f t="shared" si="28"/>
+        <v>4949.1600000000044</v>
+      </c>
+      <c r="AK17" s="7">
+        <f t="shared" ref="AK17:AT17" si="29">AK15-AK16</f>
+        <v>5307.5796160000009</v>
+      </c>
+      <c r="AL17" s="7">
         <f t="shared" si="29"/>
-        <v>1309.71282</v>
-      </c>
-      <c r="Y17" s="7">
+        <v>5727.7985142400003</v>
+      </c>
+      <c r="AM17" s="7">
         <f t="shared" si="29"/>
-        <v>1296.4237259999998</v>
-      </c>
-      <c r="Z17" s="7">
+        <v>5886.0633738207998</v>
+      </c>
+      <c r="AN17" s="7">
         <f t="shared" si="29"/>
-        <v>1263.0755279999996</v>
-      </c>
-      <c r="AC17" s="7">
-        <f t="shared" ref="AC17:AJ17" si="30">AC15-AC16</f>
-        <v>2057</v>
-      </c>
-      <c r="AD17" s="7">
-        <f t="shared" si="30"/>
-        <v>2459</v>
-      </c>
-      <c r="AE17" s="7">
-        <f t="shared" si="30"/>
-        <v>4202</v>
-      </c>
-      <c r="AF17" s="7">
-        <f t="shared" si="30"/>
-        <v>4169</v>
-      </c>
-      <c r="AG17" s="7">
-        <f t="shared" si="30"/>
-        <v>2419</v>
-      </c>
-      <c r="AH17" s="7">
-        <f t="shared" si="30"/>
-        <v>4246</v>
-      </c>
-      <c r="AI17" s="7">
-        <f t="shared" si="30"/>
-        <v>4147</v>
-      </c>
-      <c r="AJ17" s="7">
-        <f t="shared" si="30"/>
-        <v>5156.212074</v>
-      </c>
-      <c r="AK17" s="7">
-        <f t="shared" ref="AK17:AT17" si="31">AK15-AK16</f>
-        <v>5834.1117946800023</v>
-      </c>
-      <c r="AL17" s="7">
-        <f t="shared" si="31"/>
-        <v>6256.3108258560005</v>
-      </c>
-      <c r="AM17" s="7">
-        <f t="shared" si="31"/>
-        <v>6424.7147770915208</v>
-      </c>
-      <c r="AN17" s="7">
-        <f t="shared" si="31"/>
-        <v>6596.9039846989363</v>
+        <v>6047.9146194861769</v>
       </c>
       <c r="AO17" s="7">
-        <f t="shared" si="31"/>
-        <v>6663.6530245459271</v>
+        <f t="shared" si="29"/>
+        <v>6109.1937656810378</v>
       </c>
       <c r="AP17" s="7">
-        <f t="shared" si="31"/>
-        <v>6731.0695547913856</v>
+        <f t="shared" si="29"/>
+        <v>6171.0857033378479</v>
       </c>
       <c r="AQ17" s="7">
-        <f t="shared" si="31"/>
-        <v>6799.1602503393005</v>
+        <f t="shared" si="29"/>
+        <v>6233.5965603712275</v>
       </c>
       <c r="AR17" s="7">
-        <f t="shared" si="31"/>
-        <v>6867.9318528426938</v>
+        <f t="shared" si="29"/>
+        <v>6296.7325259749396</v>
       </c>
       <c r="AS17" s="7">
-        <f t="shared" si="31"/>
-        <v>6937.3911713711204</v>
+        <f t="shared" si="29"/>
+        <v>6360.4998512346892</v>
       </c>
       <c r="AT17" s="7">
-        <f t="shared" si="31"/>
-        <v>7007.5450830848313</v>
+        <f t="shared" si="29"/>
+        <v>6424.9048497470376</v>
       </c>
       <c r="AU17" s="6">
         <f>AT17*(1+$AX$22)</f>
-        <v>6937.469632253983</v>
+        <v>6360.655801249567</v>
       </c>
       <c r="AV17" s="6">
-        <f t="shared" ref="AV17:DG17" si="32">AU17*(1+$AX$22)</f>
-        <v>6868.0949359314427</v>
+        <f t="shared" ref="AV17:DG17" si="30">AU17*(1+$AX$22)</f>
+        <v>6297.0492432370711</v>
       </c>
       <c r="AW17" s="6">
-        <f t="shared" si="32"/>
-        <v>6799.4139865721281</v>
+        <f t="shared" si="30"/>
+        <v>6234.0787508047006</v>
       </c>
       <c r="AX17" s="6">
-        <f t="shared" si="32"/>
-        <v>6731.419846706407</v>
+        <f t="shared" si="30"/>
+        <v>6171.7379632966531</v>
       </c>
       <c r="AY17" s="6">
-        <f t="shared" si="32"/>
-        <v>6664.1056482393433</v>
+        <f t="shared" si="30"/>
+        <v>6110.0205836636869</v>
       </c>
       <c r="AZ17" s="6">
-        <f t="shared" si="32"/>
-        <v>6597.4645917569496</v>
+        <f t="shared" si="30"/>
+        <v>6048.9203778270503</v>
       </c>
       <c r="BA17" s="6">
-        <f t="shared" si="32"/>
-        <v>6531.4899458393802</v>
+        <f t="shared" si="30"/>
+        <v>5988.4311740487801</v>
       </c>
       <c r="BB17" s="6">
-        <f t="shared" si="32"/>
-        <v>6466.1750463809867</v>
+        <f t="shared" si="30"/>
+        <v>5928.5468623082925</v>
       </c>
       <c r="BC17" s="6">
-        <f t="shared" si="32"/>
-        <v>6401.5132959171769</v>
+        <f t="shared" si="30"/>
+        <v>5869.2613936852094</v>
       </c>
       <c r="BD17" s="6">
-        <f t="shared" si="32"/>
-        <v>6337.4981629580052</v>
+        <f t="shared" si="30"/>
+        <v>5810.568779748357</v>
       </c>
       <c r="BE17" s="6">
-        <f t="shared" si="32"/>
-        <v>6274.1231813284248</v>
+        <f t="shared" si="30"/>
+        <v>5752.4630919508736</v>
       </c>
       <c r="BF17" s="6">
-        <f t="shared" si="32"/>
-        <v>6211.3819495151401</v>
+        <f t="shared" si="30"/>
+        <v>5694.9384610313646</v>
       </c>
       <c r="BG17" s="6">
-        <f t="shared" si="32"/>
-        <v>6149.2681300199883</v>
+        <f t="shared" si="30"/>
+        <v>5637.9890764210513</v>
       </c>
       <c r="BH17" s="6">
-        <f t="shared" si="32"/>
-        <v>6087.7754487197881</v>
+        <f t="shared" si="30"/>
+        <v>5581.609185656841</v>
       </c>
       <c r="BI17" s="6">
-        <f t="shared" si="32"/>
-        <v>6026.8976942325899</v>
+        <f t="shared" si="30"/>
+        <v>5525.7930938002728</v>
       </c>
       <c r="BJ17" s="6">
-        <f t="shared" si="32"/>
-        <v>5966.6287172902639</v>
+        <f t="shared" si="30"/>
+        <v>5470.5351628622702</v>
       </c>
       <c r="BK17" s="6">
-        <f t="shared" si="32"/>
-        <v>5906.9624301173608</v>
+        <f t="shared" si="30"/>
+        <v>5415.8298112336479</v>
       </c>
       <c r="BL17" s="6">
-        <f t="shared" si="32"/>
-        <v>5847.8928058161873</v>
+        <f t="shared" si="30"/>
+        <v>5361.6715131213114</v>
       </c>
       <c r="BM17" s="6">
-        <f t="shared" si="32"/>
-        <v>5789.4138777580256</v>
+        <f t="shared" si="30"/>
+        <v>5308.0547979900985</v>
       </c>
       <c r="BN17" s="6">
-        <f t="shared" si="32"/>
-        <v>5731.5197389804453</v>
+        <f t="shared" si="30"/>
+        <v>5254.9742500101975</v>
       </c>
       <c r="BO17" s="6">
-        <f t="shared" si="32"/>
-        <v>5674.2045415906405</v>
+        <f t="shared" si="30"/>
+        <v>5202.4245075100953</v>
       </c>
       <c r="BP17" s="6">
-        <f t="shared" si="32"/>
-        <v>5617.462496174734</v>
+        <f t="shared" si="30"/>
+        <v>5150.4002624349941</v>
       </c>
       <c r="BQ17" s="6">
-        <f t="shared" si="32"/>
-        <v>5561.2878712129868</v>
+        <f t="shared" si="30"/>
+        <v>5098.8962598106446</v>
       </c>
       <c r="BR17" s="6">
-        <f t="shared" si="32"/>
-        <v>5505.6749925008571</v>
+        <f t="shared" si="30"/>
+        <v>5047.9072972125377</v>
       </c>
       <c r="BS17" s="6">
-        <f t="shared" si="32"/>
-        <v>5450.6182425758489</v>
+        <f t="shared" si="30"/>
+        <v>4997.4282242404124</v>
       </c>
       <c r="BT17" s="6">
-        <f t="shared" si="32"/>
-        <v>5396.1120601500907</v>
+        <f t="shared" si="30"/>
+        <v>4947.4539419980083</v>
       </c>
       <c r="BU17" s="6">
-        <f t="shared" si="32"/>
-        <v>5342.15093954859</v>
+        <f t="shared" si="30"/>
+        <v>4897.9794025780284</v>
       </c>
       <c r="BV17" s="6">
-        <f t="shared" si="32"/>
-        <v>5288.7294301531037</v>
+        <f t="shared" si="30"/>
+        <v>4848.999608552248</v>
       </c>
       <c r="BW17" s="6">
-        <f t="shared" si="32"/>
-        <v>5235.8421358515725</v>
+        <f t="shared" si="30"/>
+        <v>4800.5096124667252</v>
       </c>
       <c r="BX17" s="6">
-        <f t="shared" si="32"/>
-        <v>5183.4837144930571</v>
+        <f t="shared" si="30"/>
+        <v>4752.5045163420582</v>
       </c>
       <c r="BY17" s="6">
-        <f t="shared" si="32"/>
-        <v>5131.648877348126</v>
+        <f t="shared" si="30"/>
+        <v>4704.9794711786371</v>
       </c>
       <c r="BZ17" s="6">
-        <f t="shared" si="32"/>
-        <v>5080.3323885746449</v>
+        <f t="shared" si="30"/>
+        <v>4657.9296764668507</v>
       </c>
       <c r="CA17" s="6">
-        <f t="shared" si="32"/>
-        <v>5029.5290646888989</v>
+        <f t="shared" si="30"/>
+        <v>4611.3503797021822</v>
       </c>
       <c r="CB17" s="6">
-        <f t="shared" si="32"/>
-        <v>4979.2337740420098</v>
+        <f t="shared" si="30"/>
+        <v>4565.2368759051606</v>
       </c>
       <c r="CC17" s="6">
-        <f t="shared" si="32"/>
-        <v>4929.4414363015894</v>
+        <f t="shared" si="30"/>
+        <v>4519.584507146109</v>
       </c>
       <c r="CD17" s="6">
-        <f t="shared" si="32"/>
-        <v>4880.1470219385737</v>
+        <f t="shared" si="30"/>
+        <v>4474.388662074648</v>
       </c>
       <c r="CE17" s="6">
-        <f t="shared" si="32"/>
-        <v>4831.3455517191878</v>
+        <f t="shared" si="30"/>
+        <v>4429.6447754539013</v>
       </c>
       <c r="CF17" s="6">
-        <f t="shared" si="32"/>
-        <v>4783.032096201996</v>
+        <f t="shared" si="30"/>
+        <v>4385.348327699362</v>
       </c>
       <c r="CG17" s="6">
-        <f t="shared" si="32"/>
-        <v>4735.2017752399761</v>
+        <f t="shared" si="30"/>
+        <v>4341.4948444223683</v>
       </c>
       <c r="CH17" s="6">
-        <f t="shared" si="32"/>
-        <v>4687.8497574875764</v>
+        <f t="shared" si="30"/>
+        <v>4298.0798959781441</v>
       </c>
       <c r="CI17" s="6">
-        <f t="shared" si="32"/>
-        <v>4640.9712599127006</v>
+        <f t="shared" si="30"/>
+        <v>4255.099097018363</v>
       </c>
       <c r="CJ17" s="6">
-        <f t="shared" si="32"/>
-        <v>4594.5615473135731</v>
+        <f t="shared" si="30"/>
+        <v>4212.5481060481789</v>
       </c>
       <c r="CK17" s="6">
-        <f t="shared" si="32"/>
-        <v>4548.615931840437</v>
+        <f t="shared" si="30"/>
+        <v>4170.4226249876974</v>
       </c>
       <c r="CL17" s="6">
-        <f t="shared" si="32"/>
-        <v>4503.1297725220329</v>
+        <f t="shared" si="30"/>
+        <v>4128.7183987378203</v>
       </c>
       <c r="CM17" s="6">
-        <f t="shared" si="32"/>
-        <v>4458.0984747968123</v>
+        <f t="shared" si="30"/>
+        <v>4087.431214750442</v>
       </c>
       <c r="CN17" s="6">
-        <f t="shared" si="32"/>
-        <v>4413.5174900488437</v>
+        <f t="shared" si="30"/>
+        <v>4046.5569026029375</v>
       </c>
       <c r="CO17" s="6">
-        <f t="shared" si="32"/>
-        <v>4369.3823151483548</v>
+        <f t="shared" si="30"/>
+        <v>4006.0913335769083</v>
       </c>
       <c r="CP17" s="6">
-        <f t="shared" si="32"/>
-        <v>4325.6884919968716</v>
+        <f t="shared" si="30"/>
+        <v>3966.0304202411389</v>
       </c>
       <c r="CQ17" s="6">
-        <f t="shared" si="32"/>
-        <v>4282.4316070769028</v>
+        <f t="shared" si="30"/>
+        <v>3926.3701160387277</v>
       </c>
       <c r="CR17" s="6">
-        <f t="shared" si="32"/>
-        <v>4239.6072910061339</v>
+        <f t="shared" si="30"/>
+        <v>3887.1064148783403</v>
       </c>
       <c r="CS17" s="6">
-        <f t="shared" si="32"/>
-        <v>4197.2112180960721</v>
+        <f t="shared" si="30"/>
+        <v>3848.235350729557</v>
       </c>
       <c r="CT17" s="6">
-        <f t="shared" si="32"/>
-        <v>4155.2391059151114</v>
+        <f t="shared" si="30"/>
+        <v>3809.7529972222615</v>
       </c>
       <c r="CU17" s="6">
-        <f t="shared" si="32"/>
-        <v>4113.6867148559604</v>
+        <f t="shared" si="30"/>
+        <v>3771.6554672500388</v>
       </c>
       <c r="CV17" s="6">
-        <f t="shared" si="32"/>
-        <v>4072.5498477074007</v>
+        <f t="shared" si="30"/>
+        <v>3733.9389125775383</v>
       </c>
       <c r="CW17" s="6">
-        <f t="shared" si="32"/>
-        <v>4031.8243492303268</v>
+        <f t="shared" si="30"/>
+        <v>3696.5995234517627</v>
       </c>
       <c r="CX17" s="6">
-        <f t="shared" si="32"/>
-        <v>3991.5061057380235</v>
+        <f t="shared" si="30"/>
+        <v>3659.6335282172449</v>
       </c>
       <c r="CY17" s="6">
-        <f t="shared" si="32"/>
-        <v>3951.5910446806433</v>
+        <f t="shared" si="30"/>
+        <v>3623.0371929350727</v>
       </c>
       <c r="CZ17" s="6">
-        <f t="shared" si="32"/>
-        <v>3912.0751342338367</v>
+        <f t="shared" si="30"/>
+        <v>3586.8068210057218</v>
       </c>
       <c r="DA17" s="6">
-        <f t="shared" si="32"/>
-        <v>3872.9543828914984</v>
+        <f t="shared" si="30"/>
+        <v>3550.9387527956646</v>
       </c>
       <c r="DB17" s="6">
-        <f t="shared" si="32"/>
-        <v>3834.2248390625832</v>
+        <f t="shared" si="30"/>
+        <v>3515.4293652677079</v>
       </c>
       <c r="DC17" s="6">
-        <f t="shared" si="32"/>
-        <v>3795.8825906719571</v>
+        <f t="shared" si="30"/>
+        <v>3480.2750716150308</v>
       </c>
       <c r="DD17" s="6">
-        <f t="shared" si="32"/>
-        <v>3757.9237647652376</v>
+        <f t="shared" si="30"/>
+        <v>3445.4723208988803</v>
       </c>
       <c r="DE17" s="6">
-        <f t="shared" si="32"/>
-        <v>3720.3445271175851</v>
+        <f t="shared" si="30"/>
+        <v>3411.0175976898913</v>
       </c>
       <c r="DF17" s="6">
-        <f t="shared" si="32"/>
-        <v>3683.1410818464092</v>
+        <f t="shared" si="30"/>
+        <v>3376.9074217129923</v>
       </c>
       <c r="DG17" s="6">
-        <f t="shared" si="32"/>
-        <v>3646.3096710279451</v>
+        <f t="shared" si="30"/>
+        <v>3343.1383474958625</v>
       </c>
       <c r="DH17" s="6">
-        <f t="shared" ref="DH17:EP17" si="33">DG17*(1+$AX$22)</f>
-        <v>3609.8465743176657</v>
+        <f t="shared" ref="DH17:EP17" si="31">DG17*(1+$AX$22)</f>
+        <v>3309.7069640209038</v>
       </c>
       <c r="DI17" s="6">
-        <f t="shared" si="33"/>
-        <v>3573.7481085744889</v>
+        <f t="shared" si="31"/>
+        <v>3276.6098943806946</v>
       </c>
       <c r="DJ17" s="6">
-        <f t="shared" si="33"/>
-        <v>3538.0106274887439</v>
+        <f t="shared" si="31"/>
+        <v>3243.8437954368878</v>
       </c>
       <c r="DK17" s="6">
-        <f t="shared" si="33"/>
-        <v>3502.6305212138564</v>
+        <f t="shared" si="31"/>
+        <v>3211.4053574825189</v>
       </c>
       <c r="DL17" s="6">
-        <f t="shared" si="33"/>
-        <v>3467.6042160017178</v>
+        <f t="shared" si="31"/>
+        <v>3179.2913039076939</v>
       </c>
       <c r="DM17" s="6">
-        <f t="shared" si="33"/>
-        <v>3432.9281738417008</v>
+        <f t="shared" si="31"/>
+        <v>3147.4983908686168</v>
       </c>
       <c r="DN17" s="6">
-        <f t="shared" si="33"/>
-        <v>3398.5988921032836</v>
+        <f t="shared" si="31"/>
+        <v>3116.0234069599305</v>
       </c>
       <c r="DO17" s="6">
-        <f t="shared" si="33"/>
-        <v>3364.6129031822506</v>
+        <f t="shared" si="31"/>
+        <v>3084.863172890331</v>
       </c>
       <c r="DP17" s="6">
-        <f t="shared" si="33"/>
-        <v>3330.9667741504281</v>
+        <f t="shared" si="31"/>
+        <v>3054.0145411614276</v>
       </c>
       <c r="DQ17" s="6">
-        <f t="shared" si="33"/>
-        <v>3297.6571064089239</v>
+        <f t="shared" si="31"/>
+        <v>3023.4743957498131</v>
       </c>
       <c r="DR17" s="6">
-        <f t="shared" si="33"/>
-        <v>3264.6805353448349</v>
+        <f t="shared" si="31"/>
+        <v>2993.2396517923148</v>
       </c>
       <c r="DS17" s="6">
-        <f t="shared" si="33"/>
-        <v>3232.0337299913863</v>
+        <f t="shared" si="31"/>
+        <v>2963.3072552743915</v>
       </c>
       <c r="DT17" s="6">
-        <f t="shared" si="33"/>
-        <v>3199.7133926914726</v>
+        <f t="shared" si="31"/>
+        <v>2933.6741827216474</v>
       </c>
       <c r="DU17" s="6">
-        <f t="shared" si="33"/>
-        <v>3167.716258764558</v>
+        <f t="shared" si="31"/>
+        <v>2904.337440894431</v>
       </c>
       <c r="DV17" s="6">
-        <f t="shared" si="33"/>
-        <v>3136.0390961769126</v>
+        <f t="shared" si="31"/>
+        <v>2875.2940664854868</v>
       </c>
       <c r="DW17" s="6">
-        <f t="shared" si="33"/>
-        <v>3104.6787052151435</v>
+        <f t="shared" si="31"/>
+        <v>2846.5411258206318</v>
       </c>
       <c r="DX17" s="6">
-        <f t="shared" si="33"/>
-        <v>3073.631918162992</v>
+        <f t="shared" si="31"/>
+        <v>2818.0757145624257</v>
       </c>
       <c r="DY17" s="6">
-        <f t="shared" si="33"/>
-        <v>3042.8955989813621</v>
+        <f t="shared" si="31"/>
+        <v>2789.8949574168014</v>
       </c>
       <c r="DZ17" s="6">
-        <f t="shared" si="33"/>
-        <v>3012.4666429915483</v>
+        <f t="shared" si="31"/>
+        <v>2761.9960078426334</v>
       </c>
       <c r="EA17" s="6">
-        <f t="shared" si="33"/>
-        <v>2982.3419765616327</v>
+        <f t="shared" si="31"/>
+        <v>2734.3760477642072</v>
       </c>
       <c r="EB17" s="6">
-        <f t="shared" si="33"/>
-        <v>2952.5185567960161</v>
+        <f t="shared" si="31"/>
+        <v>2707.032287286565</v>
       </c>
       <c r="EC17" s="6">
-        <f t="shared" si="33"/>
-        <v>2922.9933712280558</v>
+        <f t="shared" si="31"/>
+        <v>2679.9619644136992</v>
       </c>
       <c r="ED17" s="6">
-        <f t="shared" si="33"/>
-        <v>2893.7634375157754</v>
+        <f t="shared" si="31"/>
+        <v>2653.162344769562</v>
       </c>
       <c r="EE17" s="6">
-        <f t="shared" si="33"/>
-        <v>2864.8258031406176</v>
+        <f t="shared" si="31"/>
+        <v>2626.6307213218665</v>
       </c>
       <c r="EF17" s="6">
-        <f t="shared" si="33"/>
-        <v>2836.1775451092112</v>
+        <f t="shared" si="31"/>
+        <v>2600.3644141086479</v>
       </c>
       <c r="EG17" s="6">
-        <f t="shared" si="33"/>
-        <v>2807.8157696581193</v>
+        <f t="shared" si="31"/>
+        <v>2574.3607699675613</v>
       </c>
       <c r="EH17" s="6">
-        <f t="shared" si="33"/>
-        <v>2779.7376119615383</v>
+        <f t="shared" si="31"/>
+        <v>2548.6171622678858</v>
       </c>
       <c r="EI17" s="6">
-        <f t="shared" si="33"/>
-        <v>2751.9402358419229</v>
+        <f t="shared" si="31"/>
+        <v>2523.130990645207</v>
       </c>
       <c r="EJ17" s="6">
-        <f t="shared" si="33"/>
-        <v>2724.4208334835039</v>
+        <f t="shared" si="31"/>
+        <v>2497.8996807387548</v>
       </c>
       <c r="EK17" s="6">
-        <f t="shared" si="33"/>
-        <v>2697.1766251486688</v>
+        <f t="shared" si="31"/>
+        <v>2472.9206839313674</v>
       </c>
       <c r="EL17" s="6">
-        <f t="shared" si="33"/>
-        <v>2670.204858897182</v>
+        <f t="shared" si="31"/>
+        <v>2448.1914770920539</v>
       </c>
       <c r="EM17" s="6">
-        <f t="shared" si="33"/>
-        <v>2643.50281030821</v>
+        <f t="shared" si="31"/>
+        <v>2423.7095623211335</v>
       </c>
       <c r="EN17" s="6">
-        <f t="shared" si="33"/>
-        <v>2617.067782205128</v>
+        <f t="shared" si="31"/>
+        <v>2399.4724666979223</v>
       </c>
       <c r="EO17" s="6">
-        <f t="shared" si="33"/>
-        <v>2590.8971043830766</v>
+        <f t="shared" si="31"/>
+        <v>2375.4777420309429</v>
       </c>
       <c r="EP17" s="6">
-        <f t="shared" si="33"/>
-        <v>2564.9881333392459</v>
+        <f t="shared" si="31"/>
+        <v>2351.7229646106334</v>
       </c>
     </row>
     <row r="18" spans="1:146" x14ac:dyDescent="0.3">
@@ -3655,20 +3658,17 @@
         <v>989.2</v>
       </c>
       <c r="W18" s="1">
-        <f t="shared" ref="W18:Z18" si="34">989.2</f>
+        <f t="shared" ref="W18" si="32">989.2</f>
         <v>989.2</v>
       </c>
       <c r="X18" s="1">
-        <f t="shared" si="34"/>
-        <v>989.2</v>
+        <v>969</v>
       </c>
       <c r="Y18" s="1">
-        <f t="shared" si="34"/>
-        <v>989.2</v>
+        <v>969</v>
       </c>
       <c r="Z18" s="1">
-        <f t="shared" si="34"/>
-        <v>989.2</v>
+        <v>969</v>
       </c>
       <c r="AC18" s="1">
         <v>1064</v>
@@ -3689,51 +3689,51 @@
         <v>1064</v>
       </c>
       <c r="AI18" s="1">
-        <f t="shared" ref="AI18:AT18" si="35">1002.5</f>
+        <f t="shared" ref="AI18:AT18" si="33">1002.5</f>
         <v>1002.5</v>
       </c>
       <c r="AJ18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AK18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AL18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AM18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AN18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AO18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AP18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AQ18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AR18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AS18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
       <c r="AT18" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1002.5</v>
       </c>
     </row>
@@ -3742,172 +3742,172 @@
         <v>36</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:S19" si="36">C17/C18</f>
+        <f t="shared" ref="C19:S19" si="34">C17/C18</f>
         <v>7.3748902546093065E-2</v>
       </c>
       <c r="D19" s="5">
+        <f t="shared" si="34"/>
+        <v>1.3432835820895523</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.89640035118525019</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="34"/>
+        <v>1.3757682177348551</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.96312554872695344</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="34"/>
+        <v>1.0395083406496928</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.95434591747146624</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.7032484635645303</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.44688323090430204</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="34"/>
+        <v>-0.29938542581211591</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" si="34"/>
+        <v>1.1676909569798068</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.80860403863037755</v>
+      </c>
+      <c r="O19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.70416297608503098</v>
+      </c>
+      <c r="P19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.90342405618964006</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.89552238805970152</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="34"/>
+        <v>1.3017641597028784</v>
+      </c>
+      <c r="S19" s="5">
+        <f t="shared" si="34"/>
+        <v>0.83458646616541354</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" ref="T19:V19" si="35">T17/T18</f>
+        <v>1.1033943069549057</v>
+      </c>
+      <c r="U19" s="5">
+        <f t="shared" si="35"/>
+        <v>1.0074812967581048</v>
+      </c>
+      <c r="V19" s="5">
+        <f t="shared" si="35"/>
+        <v>1.1332389809947432</v>
+      </c>
+      <c r="W19" s="5">
+        <f t="shared" ref="W19:Z19" si="36">W17/W18</f>
+        <v>1.301051354630004</v>
+      </c>
+      <c r="X19" s="5">
         <f t="shared" si="36"/>
-        <v>1.3432835820895523</v>
-      </c>
-      <c r="E19" s="5">
+        <v>1.3013415892672859</v>
+      </c>
+      <c r="Y19" s="5">
         <f t="shared" si="36"/>
-        <v>0.89640035118525019</v>
-      </c>
-      <c r="F19" s="5">
+        <v>1.186310835913313</v>
+      </c>
+      <c r="Z19" s="5">
         <f t="shared" si="36"/>
-        <v>1.3757682177348551</v>
-      </c>
-      <c r="G19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.96312554872695344</v>
-      </c>
-      <c r="H19" s="5">
-        <f t="shared" si="36"/>
-        <v>1.0395083406496928</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.95434591747146624</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.7032484635645303</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.44688323090430204</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="36"/>
-        <v>-0.29938542581211591</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" si="36"/>
-        <v>1.1676909569798068</v>
-      </c>
-      <c r="N19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.80860403863037755</v>
-      </c>
-      <c r="O19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.70416297608503098</v>
-      </c>
-      <c r="P19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.90342405618964006</v>
-      </c>
-      <c r="Q19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.89552238805970152</v>
-      </c>
-      <c r="R19" s="5">
-        <f t="shared" si="36"/>
-        <v>1.3017641597028784</v>
-      </c>
-      <c r="S19" s="5">
-        <f t="shared" si="36"/>
-        <v>0.83458646616541354</v>
-      </c>
-      <c r="T19" s="5">
-        <f t="shared" ref="T19:V19" si="37">T17/T18</f>
-        <v>1.1033943069549057</v>
-      </c>
-      <c r="U19" s="5">
+        <v>1.2916664602683179</v>
+      </c>
+      <c r="AC19" s="5">
+        <f t="shared" ref="AC19:AJ19" si="37">AC17/AC18</f>
+        <v>1.9332706766917294</v>
+      </c>
+      <c r="AD19" s="5">
         <f t="shared" si="37"/>
-        <v>1.0074812967581048</v>
-      </c>
-      <c r="V19" s="5">
+        <v>2.3110902255639099</v>
+      </c>
+      <c r="AE19" s="5">
         <f t="shared" si="37"/>
-        <v>1.1332389809947432</v>
-      </c>
-      <c r="W19" s="5">
-        <f t="shared" ref="W19:Z19" si="38">W17/W18</f>
-        <v>1.301051354630004</v>
-      </c>
-      <c r="X19" s="5">
+        <v>3.9492481203007519</v>
+      </c>
+      <c r="AF19" s="5">
+        <f t="shared" si="37"/>
+        <v>3.9182330827067671</v>
+      </c>
+      <c r="AG19" s="5">
+        <f t="shared" si="37"/>
+        <v>2.2734962406015038</v>
+      </c>
+      <c r="AH19" s="5">
+        <f t="shared" si="37"/>
+        <v>3.9906015037593985</v>
+      </c>
+      <c r="AI19" s="5">
+        <f t="shared" si="37"/>
+        <v>4.1366583541147133</v>
+      </c>
+      <c r="AJ19" s="5">
+        <f t="shared" si="37"/>
+        <v>4.9368179551122235</v>
+      </c>
+      <c r="AK19" s="5">
+        <f t="shared" ref="AK19:AT19" si="38">AK17/AK18</f>
+        <v>5.2943437566084794</v>
+      </c>
+      <c r="AL19" s="5">
         <f t="shared" si="38"/>
-        <v>1.3240121512333198</v>
-      </c>
-      <c r="Y19" s="5">
+        <v>5.7135147274214466</v>
+      </c>
+      <c r="AM19" s="5">
         <f t="shared" si="38"/>
-        <v>1.3105779680549936</v>
-      </c>
-      <c r="Z19" s="5">
+        <v>5.871384911541945</v>
+      </c>
+      <c r="AN19" s="5">
         <f t="shared" si="38"/>
-        <v>1.2768656773150016</v>
-      </c>
-      <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AJ19" si="39">AC17/AC18</f>
-        <v>1.9332706766917294</v>
-      </c>
-      <c r="AD19" s="5">
-        <f t="shared" si="39"/>
-        <v>2.3110902255639099</v>
-      </c>
-      <c r="AE19" s="5">
-        <f t="shared" si="39"/>
-        <v>3.9492481203007519</v>
-      </c>
-      <c r="AF19" s="5">
-        <f t="shared" si="39"/>
-        <v>3.9182330827067671</v>
-      </c>
-      <c r="AG19" s="5">
-        <f t="shared" si="39"/>
-        <v>2.2734962406015038</v>
-      </c>
-      <c r="AH19" s="5">
-        <f t="shared" si="39"/>
-        <v>3.9906015037593985</v>
-      </c>
-      <c r="AI19" s="5">
-        <f t="shared" si="39"/>
-        <v>4.1366583541147133</v>
-      </c>
-      <c r="AJ19" s="5">
-        <f t="shared" si="39"/>
-        <v>5.1433536897755614</v>
-      </c>
-      <c r="AK19" s="5">
-        <f t="shared" ref="AK19:AT19" si="40">AK17/AK18</f>
-        <v>5.8195628874613492</v>
-      </c>
-      <c r="AL19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.2407090532229432</v>
-      </c>
-      <c r="AM19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.4086930444803203</v>
-      </c>
-      <c r="AN19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.5804528525675172</v>
+        <v>6.0328325381408252</v>
       </c>
       <c r="AO19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.6470354359560373</v>
+        <f t="shared" si="38"/>
+        <v>6.0939588685097634</v>
       </c>
       <c r="AP19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.7142838451784392</v>
+        <f t="shared" si="38"/>
+        <v>6.1556964621823917</v>
       </c>
       <c r="AQ19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.7822047384930677</v>
+        <f t="shared" si="38"/>
+        <v>6.2180514317917481</v>
       </c>
       <c r="AR19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.8508048407408415</v>
+        <f t="shared" si="38"/>
+        <v>6.2810299510971968</v>
       </c>
       <c r="AS19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.9200909440110925</v>
+        <f t="shared" si="38"/>
+        <v>6.3446382555956999</v>
       </c>
       <c r="AT19" s="5">
-        <f t="shared" si="40"/>
-        <v>6.9900699083140463</v>
+        <f t="shared" si="38"/>
+        <v>6.4088826431391892</v>
       </c>
     </row>
     <row r="21" spans="1:146" x14ac:dyDescent="0.3">
@@ -3923,79 +3923,79 @@
         <v>0.30640970116933741</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" ref="H21:V21" si="41">H3/D3-1</f>
+        <f t="shared" ref="H21:V21" si="39">H3/D3-1</f>
         <v>0.18570613951720216</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>0.13244183916468222</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>0.13113145846958796</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>7.458975634012921E-2</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>9.105482526450781E-2</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>0.10740860562924626</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>6.7215958369470918E-2</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>8.5917013728212144E-2</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>7.0672935645019086E-2</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>8.3552439380660148E-2</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>8.7091968034674228E-2</v>
       </c>
       <c r="S21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>9.3607954545454453E-2</v>
       </c>
       <c r="T21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>8.2063949499108002E-2</v>
       </c>
       <c r="U21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>5.7832299811269916E-2</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>4.2362322452030865E-2</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" ref="W21" si="42">W3/S3-1</f>
+        <f t="shared" ref="W21" si="40">W3/S3-1</f>
         <v>1.1949603844655154E-2</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" ref="X21" si="43">X3/T3-1</f>
+        <f t="shared" ref="X21" si="41">X3/T3-1</f>
+        <v>5.1109701965757814E-2</v>
+      </c>
+      <c r="Y21" s="8">
+        <f t="shared" ref="Y21" si="42">Y3/U3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Y21" s="8">
-        <f t="shared" ref="Y21" si="44">Y3/U3-1</f>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="Z21" s="8">
-        <f t="shared" ref="Z21" si="45">Z3/V3-1</f>
+        <f t="shared" ref="Z21" si="43">Z3/V3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA21" s="8"/>
@@ -4005,67 +4005,67 @@
         <v>0.15021681444566704</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AT21" si="46">AE3/AD3-1</f>
+        <f t="shared" ref="AE21:AT21" si="44">AE3/AD3-1</f>
         <v>0.20717983344586988</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0.18257667567819524</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>8.4624177210200546E-2</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>8.1873682680427384E-2</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>6.8052803063383793E-2</v>
       </c>
       <c r="AJ21" s="8">
-        <f t="shared" si="46"/>
-        <v>1.7887536560052819E-2</v>
+        <f t="shared" si="44"/>
+        <v>2.3134257948863146E-2</v>
       </c>
       <c r="AK21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT21" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4074,19 +4074,19 @@
         <v>50</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:F22" si="47">C8/C3</f>
+        <f t="shared" ref="C22:F22" si="45">C8/C3</f>
         <v>0.40905153746210482</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0.48564911613761641</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0.4843377908041766</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0.47629169391759318</v>
       </c>
       <c r="G22" s="8">
@@ -4094,153 +4094,153 @@
         <v>0.4917951268025858</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" ref="H22:V22" si="48">H8/H3</f>
+        <f t="shared" ref="H22:V22" si="46">H8/H3</f>
         <v>0.48477075985892915</v>
       </c>
       <c r="I22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.46036881268197993</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.4457935819601041</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.4261915779731606</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.40816926241551571</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.43558282208588955</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.42394690505214683</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.40156249999999999</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.39193083573487031</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.39026691830682125</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.39957637677547969</v>
+      </c>
+      <c r="S22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.39057020392258734</v>
+      </c>
+      <c r="T22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.40228281547241596</v>
+      </c>
+      <c r="U22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.41123996431757359</v>
+      </c>
+      <c r="V22" s="8">
+        <f t="shared" si="46"/>
+        <v>0.41644752569925891</v>
+      </c>
+      <c r="W22" s="8">
+        <f t="shared" ref="W22:Z22" si="47">W8/W3</f>
+        <v>0.42587601078167114</v>
+      </c>
+      <c r="X22" s="8">
+        <f t="shared" si="47"/>
+        <v>0.41397200772200771</v>
+      </c>
+      <c r="Y22" s="8">
+        <f t="shared" si="47"/>
+        <v>0.41</v>
+      </c>
+      <c r="Z22" s="8">
+        <f t="shared" si="47"/>
+        <v>0.42</v>
+      </c>
+      <c r="AA22" s="8"/>
+      <c r="AC22" s="8">
+        <f t="shared" ref="AC22:AD22" si="48">AC8/AC3</f>
+        <v>0.46527732832826352</v>
+      </c>
+      <c r="AD22" s="8">
         <f t="shared" si="48"/>
-        <v>0.46036881268197993</v>
-      </c>
-      <c r="J22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.4457935819601041</v>
-      </c>
-      <c r="K22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.4261915779731606</v>
-      </c>
-      <c r="L22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.40816926241551571</v>
-      </c>
-      <c r="M22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.43558282208588955</v>
-      </c>
-      <c r="N22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.42394690505214683</v>
-      </c>
-      <c r="O22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.40156249999999999</v>
-      </c>
-      <c r="P22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.39193083573487031</v>
-      </c>
-      <c r="Q22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.39026691830682125</v>
-      </c>
-      <c r="R22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.39957637677547969</v>
-      </c>
-      <c r="S22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.39057020392258734</v>
-      </c>
-      <c r="T22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.40228281547241596</v>
-      </c>
-      <c r="U22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.41123996431757359</v>
-      </c>
-      <c r="V22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.41644752569925891</v>
-      </c>
-      <c r="W22" s="8">
-        <f t="shared" ref="W22:Z22" si="49">W8/W3</f>
-        <v>0.42587601078167114</v>
-      </c>
-      <c r="X22" s="8">
+        <v>0.44941480981318926</v>
+      </c>
+      <c r="AE22" s="8">
+        <f t="shared" ref="AE22:AT22" si="49">AE8/AE3</f>
+        <v>0.46616015661415122</v>
+      </c>
+      <c r="AF22" s="8">
+        <f t="shared" si="49"/>
+        <v>0.46986717117969334</v>
+      </c>
+      <c r="AG22" s="8">
+        <f t="shared" si="49"/>
+        <v>0.42346827531070574</v>
+      </c>
+      <c r="AH22" s="8">
+        <f t="shared" si="49"/>
+        <v>0.39585502670383932</v>
+      </c>
+      <c r="AI22" s="8">
+        <f t="shared" si="49"/>
+        <v>0.40538415573796271</v>
+      </c>
+      <c r="AJ22" s="8">
+        <f t="shared" si="49"/>
+        <v>0.41741123058101731</v>
+      </c>
+      <c r="AK22" s="8">
         <f t="shared" si="49"/>
         <v>0.43</v>
       </c>
-      <c r="Y22" s="8">
+      <c r="AL22" s="8">
         <f t="shared" si="49"/>
-        <v>0.43</v>
-      </c>
-      <c r="Z22" s="8">
+        <v>0.44</v>
+      </c>
+      <c r="AM22" s="8">
         <f t="shared" si="49"/>
-        <v>0.43</v>
-      </c>
-      <c r="AA22" s="8"/>
-      <c r="AC22" s="8">
-        <f t="shared" ref="AC22:AD22" si="50">AC8/AC3</f>
-        <v>0.46527732832826352</v>
-      </c>
-      <c r="AD22" s="8">
-        <f t="shared" si="50"/>
-        <v>0.44941480981318926</v>
-      </c>
-      <c r="AE22" s="8">
-        <f t="shared" ref="AE22:AT22" si="51">AE8/AE3</f>
-        <v>0.46616015661415122</v>
-      </c>
-      <c r="AF22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46986717117969334</v>
-      </c>
-      <c r="AG22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.42346827531070574</v>
-      </c>
-      <c r="AH22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.39585502670383932</v>
-      </c>
-      <c r="AI22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.40538415573796271</v>
-      </c>
-      <c r="AJ22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.42900728454784171</v>
-      </c>
-      <c r="AK22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.45</v>
-      </c>
-      <c r="AL22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46</v>
-      </c>
-      <c r="AM22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="AN22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46</v>
+        <f t="shared" si="49"/>
+        <v>0.44</v>
       </c>
       <c r="AO22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46</v>
+        <f t="shared" si="49"/>
+        <v>0.44</v>
       </c>
       <c r="AP22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46</v>
+        <f t="shared" si="49"/>
+        <v>0.44</v>
       </c>
       <c r="AQ22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46000000000000008</v>
+        <f t="shared" si="49"/>
+        <v>0.44</v>
       </c>
       <c r="AR22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46000000000000008</v>
+        <f t="shared" si="49"/>
+        <v>0.44</v>
       </c>
       <c r="AS22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46</v>
+        <f t="shared" si="49"/>
+        <v>0.44</v>
       </c>
       <c r="AT22" s="8">
-        <f t="shared" si="51"/>
-        <v>0.46</v>
+        <f t="shared" si="49"/>
+        <v>0.44000000000000006</v>
       </c>
       <c r="AW22" t="s">
         <v>53</v>
@@ -4254,19 +4254,19 @@
         <v>47</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" ref="C23:F23" si="52">C9/C3</f>
+        <f t="shared" ref="C23:F23" si="50">C9/C3</f>
         <v>8.0337808575140751E-2</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>7.8692263828169545E-2</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>8.6279538376992121E-2</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>9.8920863309352514E-2</v>
       </c>
       <c r="G23" s="8">
@@ -4274,159 +4274,159 @@
         <v>9.978451848168407E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" ref="H23:V23" si="53">H9/H3</f>
+        <f t="shared" ref="H23:V23" si="51">H9/H3</f>
         <v>0.10067329272202628</v>
       </c>
       <c r="I23" s="8">
+        <f t="shared" si="51"/>
+        <v>8.8806211582012295E-2</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="51"/>
+        <v>9.6270598438855159E-2</v>
+      </c>
+      <c r="K23" s="8">
+        <f t="shared" si="51"/>
+        <v>9.1624248033317909E-2</v>
+      </c>
+      <c r="L23" s="8">
+        <f t="shared" si="51"/>
+        <v>8.7422862180429037E-2</v>
+      </c>
+      <c r="M23" s="8">
+        <f t="shared" si="51"/>
+        <v>7.9462459830557997E-2</v>
+      </c>
+      <c r="N23" s="8">
+        <f t="shared" si="51"/>
+        <v>7.0973858864960049E-2</v>
+      </c>
+      <c r="O23" s="8">
+        <f t="shared" si="51"/>
+        <v>6.1931818181818185E-2</v>
+      </c>
+      <c r="P23" s="8">
+        <f t="shared" si="51"/>
+        <v>6.3812268423219437E-2</v>
+      </c>
+      <c r="Q23" s="8">
+        <f t="shared" si="51"/>
+        <v>5.9584793744944728E-2</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="51"/>
+        <v>5.8061300772489409E-2</v>
+      </c>
+      <c r="S23" s="8">
+        <f t="shared" si="51"/>
+        <v>5.4682426289128457E-2</v>
+      </c>
+      <c r="T23" s="8">
+        <f t="shared" si="51"/>
+        <v>5.6563094483195943E-2</v>
+      </c>
+      <c r="U23" s="8">
+        <f t="shared" si="51"/>
+        <v>6.4738116477634763E-2</v>
+      </c>
+      <c r="V23" s="8">
+        <f t="shared" si="51"/>
+        <v>7.4826679416686595E-2</v>
+      </c>
+      <c r="W23" s="8">
+        <f t="shared" ref="W23:Z23" si="52">W9/W3</f>
+        <v>6.2636375304838912E-2</v>
+      </c>
+      <c r="X23" s="8">
+        <f t="shared" si="52"/>
+        <v>7.0342664092664098E-2</v>
+      </c>
+      <c r="Y23" s="8">
+        <f t="shared" si="52"/>
+        <v>0.06</v>
+      </c>
+      <c r="Z23" s="8">
+        <f t="shared" si="52"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AA23" s="8"/>
+      <c r="AC23" s="8">
+        <f t="shared" ref="AC23:AD23" si="53">AC9/AC3</f>
+        <v>8.5043039285483138E-2</v>
+      </c>
+      <c r="AD23" s="8">
         <f t="shared" si="53"/>
-        <v>8.8806211582012295E-2</v>
-      </c>
-      <c r="J23" s="8">
-        <f t="shared" si="53"/>
-        <v>9.6270598438855159E-2</v>
-      </c>
-      <c r="K23" s="8">
-        <f t="shared" si="53"/>
-        <v>9.1624248033317909E-2</v>
-      </c>
-      <c r="L23" s="8">
-        <f t="shared" si="53"/>
-        <v>8.7422862180429037E-2</v>
-      </c>
-      <c r="M23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.9462459830557997E-2</v>
-      </c>
-      <c r="N23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0973858864960049E-2</v>
-      </c>
-      <c r="O23" s="8">
-        <f t="shared" si="53"/>
-        <v>6.1931818181818185E-2</v>
-      </c>
-      <c r="P23" s="8">
-        <f t="shared" si="53"/>
-        <v>6.3812268423219437E-2</v>
-      </c>
-      <c r="Q23" s="8">
-        <f t="shared" si="53"/>
-        <v>5.9584793744944728E-2</v>
-      </c>
-      <c r="R23" s="8">
-        <f t="shared" si="53"/>
-        <v>5.8061300772489409E-2</v>
-      </c>
-      <c r="S23" s="8">
-        <f t="shared" si="53"/>
-        <v>5.4682426289128457E-2</v>
-      </c>
-      <c r="T23" s="8">
-        <f t="shared" si="53"/>
-        <v>5.6563094483195943E-2</v>
-      </c>
-      <c r="U23" s="8">
-        <f t="shared" si="53"/>
-        <v>6.4738116477634763E-2</v>
-      </c>
-      <c r="V23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.4826679416686595E-2</v>
-      </c>
-      <c r="W23" s="8">
-        <f t="shared" ref="W23:Z23" si="54">W9/W3</f>
-        <v>6.2636375304838912E-2</v>
-      </c>
-      <c r="X23" s="8">
+        <v>7.8831870357866304E-2</v>
+      </c>
+      <c r="AE23" s="8">
+        <f t="shared" ref="AE23:AT23" si="54">AE9/AE3</f>
+        <v>8.674373077281626E-2</v>
+      </c>
+      <c r="AF23" s="8">
         <f t="shared" si="54"/>
-        <v>0.06</v>
-      </c>
-      <c r="Y23" s="8">
+        <v>9.6369871112687716E-2</v>
+      </c>
+      <c r="AG23" s="8">
         <f t="shared" si="54"/>
-        <v>0.06</v>
-      </c>
-      <c r="Z23" s="8">
+        <v>8.2019042081546631E-2</v>
+      </c>
+      <c r="AH23" s="8">
+        <f t="shared" si="54"/>
+        <v>6.0763830573376774E-2</v>
+      </c>
+      <c r="AI23" s="8">
+        <f t="shared" si="54"/>
+        <v>6.2930465138220593E-2</v>
+      </c>
+      <c r="AJ23" s="8">
+        <f t="shared" si="54"/>
+        <v>6.5863552252202404E-2</v>
+      </c>
+      <c r="AK23" s="8">
         <f t="shared" si="54"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AA23" s="8"/>
-      <c r="AC23" s="8">
-        <f t="shared" ref="AC23:AD23" si="55">AC9/AC3</f>
-        <v>8.5043039285483138E-2</v>
-      </c>
-      <c r="AD23" s="8">
-        <f t="shared" si="55"/>
-        <v>7.8831870357866304E-2</v>
-      </c>
-      <c r="AE23" s="8">
-        <f t="shared" ref="AE23:AT23" si="56">AE9/AE3</f>
-        <v>8.674373077281626E-2</v>
-      </c>
-      <c r="AF23" s="8">
-        <f t="shared" si="56"/>
-        <v>9.6369871112687716E-2</v>
-      </c>
-      <c r="AG23" s="8">
-        <f t="shared" si="56"/>
-        <v>8.2019042081546631E-2</v>
-      </c>
-      <c r="AH23" s="8">
-        <f t="shared" si="56"/>
-        <v>6.0763830573376774E-2</v>
-      </c>
-      <c r="AI23" s="8">
-        <f t="shared" si="56"/>
-        <v>6.2930465138220593E-2</v>
-      </c>
-      <c r="AJ23" s="8">
-        <f t="shared" si="56"/>
-        <v>6.3245298968632596E-2</v>
-      </c>
-      <c r="AK23" s="8">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
-      </c>
       <c r="AL23" s="8">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AM23" s="8">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AN23" s="8">
-        <f t="shared" si="56"/>
-        <v>6.0000000000000005E-2</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AO23" s="8">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AP23" s="8">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AQ23" s="8">
-        <f t="shared" si="56"/>
-        <v>6.0000000000000005E-2</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AR23" s="8">
-        <f t="shared" si="56"/>
-        <v>6.0000000000000005E-2</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AS23" s="8">
-        <f t="shared" si="56"/>
-        <v>6.0000000000000005E-2</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AT23" s="8">
-        <f t="shared" si="56"/>
-        <v>0.06</v>
+        <f t="shared" si="54"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AW23" t="s">
         <v>54</v>
       </c>
       <c r="AX23" s="8">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="24" spans="1:146" x14ac:dyDescent="0.3">
@@ -4442,79 +4442,79 @@
         <v>0.22479338842975216</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" ref="H24:V24" si="57">H10/D10-1</f>
+        <f t="shared" ref="H24:V24" si="55">H10/D10-1</f>
         <v>0.1822503961965134</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.12017804154302669</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>8.7431693989071135E-2</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>9.986504723346834E-2</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>9.2493297587131318E-2</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>6.0927152317880706E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>3.2663316582914659E-2</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>-0.11533742331288344</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>-8.8343558282208634E-2</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>-7.7403245942571752E-2</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>-6.326034063260344E-2</v>
       </c>
       <c r="S24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>2.9126213592232997E-2</v>
       </c>
       <c r="T24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>-3.3647375504710642E-2</v>
       </c>
       <c r="U24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>9.4722598105547728E-3</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>3.8961038961038419E-3</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" ref="W24:W25" si="58">W10/S10-1</f>
+        <f t="shared" ref="W24:W25" si="56">W10/S10-1</f>
         <v>-1.4824797843665749E-2</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" ref="X24:X25" si="59">X10/T10-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="X24:X25" si="57">X10/T10-1</f>
+        <v>6.8245125348189495E-2</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" ref="Y24:Y25" si="60">Y10/U10-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="Y24:Y25" si="58">Y10/U10-1</f>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" ref="Z24:Z25" si="61">Z10/V10-1</f>
+        <f t="shared" ref="Z24:Z25" si="59">Z10/V10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA24" s="8"/>
@@ -4524,67 +4524,67 @@
         <v>0.1387220098306936</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" ref="AE24:AT24" si="62">AE10/AD10-1</f>
+        <f t="shared" ref="AE24:AT24" si="60">AE10/AD10-1</f>
         <v>0.26714628297362109</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.14988644965934905</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>7.0770243581303571E-2</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>-8.6074392868121685E-2</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>2.0181634712410634E-3</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" si="62"/>
-        <v>3.8167170191338862E-3</v>
+        <f t="shared" si="60"/>
+        <v>2.5367573011077615E-2</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT24" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW24" t="s">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AX24" s="1">
         <f>NPV(AX23,AJ17:EP17)</f>
-        <v>78463.283168822862</v>
+        <v>81749.837904463639</v>
       </c>
     </row>
     <row r="25" spans="1:146" x14ac:dyDescent="0.3">
@@ -4608,80 +4608,80 @@
         <v>7.8189300411522611E-2</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" ref="H25:V25" si="63">H11/D11-1</f>
+        <f t="shared" ref="H25:V25" si="61">H11/D11-1</f>
         <v>1.953125E-2</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-9.9403578528827197E-3</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>1.7574692442883233E-3</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.15839694656488557</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-1.5325670498084309E-2</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-7.0281124497991954E-2</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-9.6491228070175405E-2</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-0.16474464579901149</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-4.4747081712062209E-2</v>
       </c>
       <c r="Q25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>9.5032397408207236E-2</v>
       </c>
       <c r="R25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>7.5728155339805925E-2</v>
       </c>
       <c r="S25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-8.4812623274161725E-2</v>
       </c>
       <c r="T25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.16089613034623218</v>
       </c>
       <c r="U25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>2.3668639053254337E-2</v>
       </c>
       <c r="V25" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>7.2202166064981865E-2</v>
       </c>
       <c r="W25" s="8">
+        <f t="shared" si="56"/>
+        <v>8.405172413793105E-2</v>
+      </c>
+      <c r="X25" s="8">
+        <f t="shared" si="57"/>
+        <v>-0.19122807017543864</v>
+      </c>
+      <c r="Y25" s="8">
         <f t="shared" si="58"/>
-        <v>8.405172413793105E-2</v>
-      </c>
-      <c r="X25" s="8">
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="Z25" s="8">
         <f t="shared" si="59"/>
-        <v>-5.0000000000000044E-2</v>
-      </c>
-      <c r="Y25" s="8">
-        <f t="shared" si="60"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="Z25" s="8">
-        <f t="shared" si="61"/>
-        <v>3.0000000000000027E-2</v>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AA25" s="8"/>
       <c r="AC25" s="8"/>
@@ -4690,67 +4690,67 @@
         <v>0.11031797534068777</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" ref="AE25:AT25" si="64">AE11/AD11-1</f>
+        <f t="shared" ref="AE25:AT25" si="62">AE11/AD11-1</f>
         <v>0.20981881940385749</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>2.1256038647343045E-2</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>-7.0955534531693676E-3</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>-1.9056693663649371E-2</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>4.2739193783390084E-2</v>
       </c>
       <c r="AJ25" s="8">
-        <f t="shared" si="64"/>
-        <v>2.5277130880298149E-2</v>
+        <f t="shared" si="62"/>
+        <v>-4.2971588262692206E-2</v>
       </c>
       <c r="AK25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT25" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW25" t="s">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="AX25" s="1">
         <f>Main!D8</f>
-        <v>4407</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="26" spans="1:146" x14ac:dyDescent="0.3">
@@ -4766,19 +4766,19 @@
         <v>51</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" ref="C26:F26" si="65">C13/C3</f>
+        <f t="shared" ref="C26:F26" si="63">C13/C3</f>
         <v>8.6184495452576879E-2</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.18076411328644745</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.17897050741894119</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.15745585349901897</v>
       </c>
       <c r="G26" s="8">
@@ -4786,160 +4786,160 @@
         <v>0.17271672468092159</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:V26" si="66">H13/H3</f>
+        <f t="shared" ref="H26:V26" si="64">H13/H3</f>
         <v>0.18066688041038795</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.16871562601099968</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.15177797051170858</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.10967144840351689</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.11225389362327358</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.16330704060765411</v>
       </c>
       <c r="N26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.1684951916565082</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.14190340909090909</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.15548236585700562</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.15745483957940146</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.21530027410914529</v>
       </c>
       <c r="S26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.15170801402779582</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.16804058338617628</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.17726519689053141</v>
       </c>
       <c r="V26" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.17224480038250059</v>
       </c>
       <c r="W26" s="8">
-        <f t="shared" ref="W26:Z26" si="67">W13/W3</f>
+        <f t="shared" ref="W26:Z26" si="65">W13/W3</f>
         <v>0.19638043896804006</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.20628880848471284</v>
+        <f t="shared" si="65"/>
+        <v>0.18146718146718147</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.2031673349904298</v>
+        <f t="shared" si="65"/>
+        <v>0.17702768886323489</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.18927715434703876</v>
+        <f t="shared" si="65"/>
+        <v>0.18279208867575736</v>
       </c>
       <c r="AA26" s="8"/>
       <c r="AC26" s="8">
-        <f t="shared" ref="AC26:AD26" si="68">AC13/AC3</f>
+        <f t="shared" ref="AC26:AD26" si="66">AC13/AC3</f>
         <v>0.1419972817293379</v>
       </c>
       <c r="AD26" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0.15299347287868556</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" ref="AE26:AT26" si="69">AE13/AE3</f>
+        <f t="shared" ref="AE26:AT26" si="67">AE13/AE3</f>
         <v>0.15330474503589075</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.16798707185369122</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.13943600552365723</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.16888918746431092</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.16746862911595434</v>
       </c>
       <c r="AJ26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.19868300058982066</v>
+        <f t="shared" si="67"/>
+        <v>0.18429052704056867</v>
       </c>
       <c r="AK26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.22656563042726086</v>
+        <f t="shared" si="67"/>
+        <v>0.19993442836765971</v>
       </c>
       <c r="AL26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.23819762524570715</v>
+        <f t="shared" si="67"/>
+        <v>0.21153324346612337</v>
       </c>
       <c r="AM26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.23981303781931504</v>
+        <f t="shared" si="67"/>
+        <v>0.21311580459718363</v>
       </c>
       <c r="AN26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.24141204213667383</v>
+        <f t="shared" si="67"/>
+        <v>0.21468228247247337</v>
       </c>
       <c r="AO26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.2414403034275874</v>
+        <f t="shared" si="67"/>
+        <v>0.21471039883703108</v>
       </c>
       <c r="AP26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.24146828490373939</v>
+        <f t="shared" si="67"/>
+        <v>0.2147382368217417</v>
       </c>
       <c r="AQ26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.24149598933557309</v>
+        <f t="shared" si="67"/>
+        <v>0.21476579918284133</v>
       </c>
       <c r="AR26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.24152341946610151</v>
+        <f t="shared" si="67"/>
+        <v>0.21479308864927657</v>
       </c>
       <c r="AS26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.24155057801117907</v>
+        <f t="shared" si="67"/>
+        <v>0.21482010792297487</v>
       </c>
       <c r="AT26" s="8">
-        <f t="shared" si="69"/>
-        <v>0.24157746765977076</v>
+        <f t="shared" si="67"/>
+        <v>0.21484685967911182</v>
       </c>
       <c r="AW26" t="s">
         <v>57</v>
       </c>
       <c r="AX26" s="1">
         <f>AX24+AX25</f>
-        <v>82870.283168822862</v>
+        <v>84106.837904463639</v>
       </c>
     </row>
     <row r="27" spans="1:146" x14ac:dyDescent="0.3">
@@ -4947,19 +4947,19 @@
         <v>34</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:F27" si="70">C16/C15</f>
+        <f t="shared" ref="C27:F27" si="68">C16/C15</f>
         <v>0.68060836501901145</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.14952751528627015</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.10751748251748251</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.15707369553523401</v>
       </c>
       <c r="G27" s="8">
@@ -4967,160 +4967,160 @@
         <v>-0.2580275229357798</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" ref="H27:V27" si="71">H16/H15</f>
+        <f t="shared" ref="H27:V27" si="69">H16/H15</f>
         <v>0.12684365781710916</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>6.6952789699570817E-2</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>-0.13456090651558072</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.19077901430842609</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>7.9591836734693882</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.15716096324461343</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.17027027027027028</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.25977653631284914</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.21028396009209516</v>
       </c>
       <c r="Q27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.17808219178082191</v>
       </c>
       <c r="R27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.2180702732849972</v>
       </c>
       <c r="S27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.26550868486352358</v>
       </c>
       <c r="T27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.1937097927090779</v>
       </c>
       <c r="U27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.2295957284515637</v>
       </c>
       <c r="V27" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.20496453900709219</v>
       </c>
       <c r="W27" s="8">
-        <f t="shared" ref="W27:Z27" si="72">W16/W15</f>
+        <f t="shared" ref="W27:Z27" si="70">W16/W15</f>
         <v>0.19713038053649407</v>
       </c>
       <c r="X27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.22</v>
+        <f t="shared" si="70"/>
+        <v>0.17527795945062133</v>
       </c>
       <c r="Y27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.22000000000000003</v>
+        <f t="shared" si="70"/>
+        <v>0.2</v>
       </c>
       <c r="Z27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.22000000000000003</v>
+        <f t="shared" si="70"/>
+        <v>0.2</v>
       </c>
       <c r="AA27" s="8"/>
       <c r="AC27" s="8">
-        <f t="shared" ref="AC27:AD27" si="73">AC16/AC15</f>
+        <f t="shared" ref="AC27:AD27" si="71">AC16/AC15</f>
         <v>0.13425925925925927</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.17978652434956638</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" ref="AE27:AT27" si="74">AE16/AE15</f>
+        <f t="shared" ref="AE27:AT27" si="72">AE16/AE15</f>
         <v>0.17038499506416585</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>-1.7077335935594046E-2</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>0.28134284016636957</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>0.21530216226205878</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>0.22180521673860012</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.21441458948230632</v>
+        <f t="shared" si="72"/>
+        <v>0.19308708801734736</v>
       </c>
       <c r="AK27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AL27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AM27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AN27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AO27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AP27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AQ27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AR27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AS27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AT27" s="8">
-        <f t="shared" si="74"/>
-        <v>0.22</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="AW27" t="s">
         <v>58</v>
       </c>
       <c r="AX27" s="9">
         <f>AX26/AT18</f>
-        <v>82.663624108551488</v>
+        <v>83.897095166547274</v>
       </c>
     </row>
     <row r="28" spans="1:146" x14ac:dyDescent="0.3">
@@ -5132,175 +5132,175 @@
         <v>1.8189692507579038E-2</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" ref="D28:V28" si="75">D17/D3</f>
+        <f t="shared" ref="D28:V28" si="73">D17/D3</f>
         <v>0.29081923588671355</v>
       </c>
       <c r="E28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.18703059168345851</v>
+      </c>
+      <c r="F28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.25621321124918245</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.1818332504558263</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.18980442449503046</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.17583306373341961</v>
+      </c>
+      <c r="J28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.11578490893321769</v>
+      </c>
+      <c r="K28" s="8">
+        <f t="shared" si="73"/>
+        <v>7.8513034089156261E-2</v>
+      </c>
+      <c r="L28" s="8">
+        <f t="shared" si="73"/>
+        <v>-5.0102850426094622E-2</v>
+      </c>
+      <c r="M28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.19427402862985685</v>
+      </c>
+      <c r="N28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.12474603819585535</v>
+      </c>
+      <c r="O28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.11292613636363637</v>
+      </c>
+      <c r="P28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.14121037463976946</v>
+      </c>
+      <c r="Q28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.13750337018064168</v>
+      </c>
+      <c r="R28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.17468228258160975</v>
+      </c>
+      <c r="S28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.11533965450058449</v>
+      </c>
+      <c r="T28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.14305643627140138</v>
+      </c>
+      <c r="U28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.12871160953230534</v>
+      </c>
+      <c r="V28" s="8">
+        <f t="shared" si="73"/>
+        <v>0.13399474061678221</v>
+      </c>
+      <c r="W28" s="8">
+        <f t="shared" ref="W28:Z28" si="74">W17/W3</f>
+        <v>0.16519060454370427</v>
+      </c>
+      <c r="X28" s="8">
+        <f t="shared" si="74"/>
+        <v>0.15214768339768339</v>
+      </c>
+      <c r="Y28" s="8">
+        <f t="shared" si="74"/>
+        <v>0.14362116657546162</v>
+      </c>
+      <c r="Z28" s="8">
+        <f t="shared" si="74"/>
+        <v>0.14812723825574048</v>
+      </c>
+      <c r="AC28" s="8">
+        <f t="shared" ref="AC28:AT28" si="75">AC17/AC3</f>
+        <v>0.13313054171251051</v>
+      </c>
+      <c r="AD28" s="8">
         <f t="shared" si="75"/>
-        <v>0.18703059168345851</v>
-      </c>
-      <c r="F28" s="8">
+        <v>0.13836371820841772</v>
+      </c>
+      <c r="AE28" s="8">
         <f t="shared" si="75"/>
-        <v>0.25621321124918245</v>
-      </c>
-      <c r="G28" s="8">
+        <v>0.19586091171809453</v>
+      </c>
+      <c r="AF28" s="8">
         <f t="shared" si="75"/>
-        <v>0.1818332504558263</v>
-      </c>
-      <c r="H28" s="8">
+        <v>0.16432146939419021</v>
+      </c>
+      <c r="AG28" s="8">
         <f t="shared" si="75"/>
-        <v>0.18980442449503046</v>
-      </c>
-      <c r="I28" s="8">
+        <v>8.7906097826876958E-2</v>
+      </c>
+      <c r="AH28" s="8">
         <f t="shared" si="75"/>
-        <v>0.17583306373341961</v>
-      </c>
-      <c r="J28" s="8">
+        <v>0.14262201471230393</v>
+      </c>
+      <c r="AI28" s="8">
         <f t="shared" si="75"/>
-        <v>0.11578490893321769</v>
-      </c>
-      <c r="K28" s="8">
+        <v>0.13042110890964556</v>
+      </c>
+      <c r="AJ28" s="8">
         <f t="shared" si="75"/>
-        <v>7.8513034089156261E-2</v>
-      </c>
-      <c r="L28" s="8">
+        <v>0.1521292488150349</v>
+      </c>
+      <c r="AK28" s="8">
         <f t="shared" si="75"/>
-        <v>-5.0102850426094622E-2</v>
-      </c>
-      <c r="M28" s="8">
+        <v>0.15994754269412778</v>
+      </c>
+      <c r="AL28" s="8">
         <f t="shared" si="75"/>
-        <v>0.19427402862985685</v>
-      </c>
-      <c r="N28" s="8">
+        <v>0.1692265947728987</v>
+      </c>
+      <c r="AM28" s="8">
         <f t="shared" si="75"/>
-        <v>0.12474603819585535</v>
-      </c>
-      <c r="O28" s="8">
+        <v>0.17049264367774691</v>
+      </c>
+      <c r="AN28" s="8">
         <f t="shared" si="75"/>
-        <v>0.11292613636363637</v>
-      </c>
-      <c r="P28" s="8">
+        <v>0.17174582597797872</v>
+      </c>
+      <c r="AO28" s="8">
         <f t="shared" si="75"/>
-        <v>0.14121037463976946</v>
-      </c>
-      <c r="Q28" s="8">
+        <v>0.17176831906962489</v>
+      </c>
+      <c r="AP28" s="8">
         <f t="shared" si="75"/>
-        <v>0.13750337018064168</v>
-      </c>
-      <c r="R28" s="8">
+        <v>0.17179058945739334</v>
+      </c>
+      <c r="AQ28" s="8">
         <f t="shared" si="75"/>
-        <v>0.17468228258160975</v>
-      </c>
-      <c r="S28" s="8">
+        <v>0.17181263934627306</v>
+      </c>
+      <c r="AR28" s="8">
         <f t="shared" si="75"/>
-        <v>0.11533965450058449</v>
-      </c>
-      <c r="T28" s="8">
+        <v>0.17183447091942125</v>
+      </c>
+      <c r="AS28" s="8">
         <f t="shared" si="75"/>
-        <v>0.14305643627140138</v>
-      </c>
-      <c r="U28" s="8">
+        <v>0.1718560863383799</v>
+      </c>
+      <c r="AT28" s="8">
         <f t="shared" si="75"/>
-        <v>0.12871160953230534</v>
-      </c>
-      <c r="V28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.13399474061678221</v>
-      </c>
-      <c r="W28" s="8">
-        <f t="shared" ref="W28:Z28" si="76">W17/W3</f>
-        <v>0.16519060454370427</v>
-      </c>
-      <c r="X28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.16284491775150137</v>
-      </c>
-      <c r="Y28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.16040063867089147</v>
-      </c>
-      <c r="Z28" s="8">
-        <f t="shared" si="76"/>
-        <v>0.14948240852294645</v>
-      </c>
-      <c r="AC28" s="8">
-        <f t="shared" ref="AC28:AT28" si="77">AC17/AC3</f>
-        <v>0.13313054171251051</v>
-      </c>
-      <c r="AD28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.13836371820841772</v>
-      </c>
-      <c r="AE28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.19586091171809453</v>
-      </c>
-      <c r="AF28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.16432146939419021</v>
-      </c>
-      <c r="AG28" s="8">
-        <f t="shared" si="77"/>
-        <v>8.7906097826876958E-2</v>
-      </c>
-      <c r="AH28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.14262201471230393</v>
-      </c>
-      <c r="AI28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.13042110890964556</v>
-      </c>
-      <c r="AJ28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.15931065672159198</v>
-      </c>
-      <c r="AK28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.17672119173326348</v>
-      </c>
-      <c r="AL28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.18579414769165156</v>
-      </c>
-      <c r="AM28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.18705416949906573</v>
-      </c>
-      <c r="AN28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.1883013928666056</v>
-      </c>
-      <c r="AO28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.1883234366735182</v>
-      </c>
-      <c r="AP28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.18834526222491671</v>
-      </c>
-      <c r="AQ28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.18836687168174701</v>
-      </c>
-      <c r="AR28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.18838826718355917</v>
-      </c>
-      <c r="AS28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.18840945084871968</v>
-      </c>
-      <c r="AT28" s="8">
-        <f t="shared" si="77"/>
-        <v>0.18843042477462119</v>
+        <v>0.17187748774328945</v>
       </c>
       <c r="AW28" t="s">
         <v>59</v>
       </c>
       <c r="AX28" s="9">
         <f>Main!D3</f>
-        <v>71.069999999999993</v>
+        <v>71.430000000000007</v>
       </c>
     </row>
     <row r="29" spans="1:146" x14ac:dyDescent="0.3">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AX29" s="10">
         <f>AX27/AX28-1</f>
-        <v>0.16312964835446042</v>
+        <v>0.17453584161482949</v>
       </c>
     </row>
     <row r="30" spans="1:146" x14ac:dyDescent="0.3">
@@ -5317,7 +5317,7 @@
         <v>61</v>
       </c>
       <c r="AX30" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/PYPL.xlsx
+++ b/Financial Analysis/PYPL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1391F526-CEAA-4D42-9CBF-4D6788A0454E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421D06A5-FCA0-49D9-99DF-5D55EDA894FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7B33BECD-2B6A-465C-BF18-30C78DC6ADF8}"/>
   </bookViews>
@@ -751,14 +751,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="9">
-        <v>71.430000000000007</v>
+        <v>74.84</v>
       </c>
       <c r="E3" s="4">
-        <v>45867</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45868</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="4">
         <v>45958</v>
@@ -781,7 +781,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>69215.670000000013</v>
+        <v>72519.960000000006</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -823,7 +823,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>66858.670000000013</v>
+        <v>70162.960000000006</v>
       </c>
     </row>
   </sheetData>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AX28" s="9">
         <f>Main!D3</f>
-        <v>71.430000000000007</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="29" spans="1:146" x14ac:dyDescent="0.3">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AX29" s="10">
         <f>AX27/AX28-1</f>
-        <v>0.17453584161482949</v>
+        <v>0.12101944370052475</v>
       </c>
     </row>
     <row r="30" spans="1:146" x14ac:dyDescent="0.3">

--- a/Financial Analysis/PYPL.xlsx
+++ b/Financial Analysis/PYPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421D06A5-FCA0-49D9-99DF-5D55EDA894FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957C3C14-2D1A-4208-8E85-50EDF8CF4193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7B33BECD-2B6A-465C-BF18-30C78DC6ADF8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>Price</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>Q425</t>
-  </si>
-  <si>
-    <t>Q225 8K</t>
   </si>
   <si>
     <t>Slightly undervalued</t>
@@ -751,17 +748,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="9">
-        <v>74.84</v>
+        <v>73.02</v>
       </c>
       <c r="E3" s="4">
-        <v>45937</v>
+        <v>45959</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45959</v>
       </c>
       <c r="G3" s="4">
-        <v>45958</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -769,10 +766,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>969</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -781,7 +779,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>72519.960000000006</v>
+        <v>68324.813999999998</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -789,11 +787,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <f>6688+3320+3645</f>
-        <v>13653</v>
+        <f>8995+1760+3601</f>
+        <v>14356</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -801,11 +799,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="1">
-        <f>11296</f>
-        <v>11296</v>
+        <f>11276</f>
+        <v>11276</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -814,7 +812,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>2357</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -823,7 +821,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>70162.960000000006</v>
+        <v>65244.813999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1044,8 +1042,7 @@
         <v>8288</v>
       </c>
       <c r="Y3" s="7">
-        <f>U3*1.02</f>
-        <v>8003.9400000000005</v>
+        <v>8417</v>
       </c>
       <c r="Z3" s="7">
         <f>V3*1.01</f>
@@ -1079,47 +1076,47 @@
       </c>
       <c r="AJ3" s="7">
         <f>SUM(W3:Z3)</f>
-        <v>32532.600000000002</v>
+        <v>32945.660000000003</v>
       </c>
       <c r="AK3" s="7">
         <f>AJ3*1.02</f>
-        <v>33183.252</v>
+        <v>33604.573200000006</v>
       </c>
       <c r="AL3" s="7">
         <f>AK3*1.02</f>
-        <v>33846.91704</v>
+        <v>34276.664664000004</v>
       </c>
       <c r="AM3" s="7">
         <f>AL3*1.02</f>
-        <v>34523.8553808</v>
+        <v>34962.197957280005</v>
       </c>
       <c r="AN3" s="7">
         <f t="shared" ref="AN3" si="0">AM3*1.02</f>
-        <v>35214.332488416003</v>
+        <v>35661.441916425603</v>
       </c>
       <c r="AO3" s="7">
         <f>AN3*1.01</f>
-        <v>35566.47581330016</v>
+        <v>36018.056335589863</v>
       </c>
       <c r="AP3" s="7">
         <f t="shared" ref="AP3:AT3" si="1">AO3*1.01</f>
-        <v>35922.140571433163</v>
+        <v>36378.236898945761</v>
       </c>
       <c r="AQ3" s="7">
         <f t="shared" si="1"/>
-        <v>36281.361977147499</v>
+        <v>36742.019267935219</v>
       </c>
       <c r="AR3" s="7">
         <f t="shared" si="1"/>
-        <v>36644.175596918976</v>
+        <v>37109.439460614572</v>
       </c>
       <c r="AS3" s="7">
         <f t="shared" si="1"/>
-        <v>37010.617352888163</v>
+        <v>37480.533855220718</v>
       </c>
       <c r="AT3" s="7">
         <f t="shared" si="1"/>
-        <v>37380.723526417045</v>
+        <v>37855.339193772925</v>
       </c>
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.3">
@@ -1192,7 +1189,9 @@
       <c r="X4" s="1">
         <v>3968</v>
       </c>
-      <c r="Y4" s="1"/>
+      <c r="Y4" s="1">
+        <v>4063</v>
+      </c>
       <c r="Z4" s="1"/>
       <c r="AC4" s="1">
         <v>5581</v>
@@ -1302,7 +1301,9 @@
       <c r="X5" s="1">
         <v>476</v>
       </c>
-      <c r="Y5" s="1"/>
+      <c r="Y5" s="1">
+        <v>483</v>
+      </c>
       <c r="Z5" s="1"/>
       <c r="AC5" s="1">
         <v>1274</v>
@@ -1412,7 +1413,9 @@
       <c r="X6" s="1">
         <v>413</v>
       </c>
-      <c r="Y6" s="1"/>
+      <c r="Y6" s="1">
+        <v>447</v>
+      </c>
       <c r="Z6" s="1"/>
       <c r="AC6" s="1">
         <v>1407</v>
@@ -1457,7 +1460,7 @@
         <v>37</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" ref="C7:X7" si="2">SUM(C4:C6)</f>
+        <f t="shared" ref="C7:Y7" si="2">SUM(C4:C6)</f>
         <v>2729</v>
       </c>
       <c r="D7" s="1">
@@ -1545,11 +1548,11 @@
         <v>4857</v>
       </c>
       <c r="Y7" s="1">
-        <f t="shared" ref="Y7:Z7" si="3">Y3-Y8</f>
-        <v>4722.3245999999999</v>
+        <f t="shared" si="2"/>
+        <v>4993</v>
       </c>
       <c r="Z7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="Y7:Z7" si="3">Z3-Z8</f>
         <v>4900.8027999999995</v>
       </c>
       <c r="AC7" s="1">
@@ -1582,47 +1585,47 @@
       </c>
       <c r="AJ7" s="1">
         <f>SUM(W7:Z7)</f>
-        <v>18953.127399999998</v>
+        <v>19223.802799999998</v>
       </c>
       <c r="AK7" s="1">
         <f t="shared" ref="AK7:AT7" si="5">AK3-AK8</f>
-        <v>18914.45364</v>
+        <v>19154.606724000005</v>
       </c>
       <c r="AL7" s="1">
         <f t="shared" si="5"/>
-        <v>18954.273542399998</v>
+        <v>19194.932211840001</v>
       </c>
       <c r="AM7" s="1">
         <f t="shared" si="5"/>
-        <v>19333.359013248002</v>
+        <v>19578.830856076802</v>
       </c>
       <c r="AN7" s="1">
         <f t="shared" si="5"/>
-        <v>19720.02619351296</v>
+        <v>19970.407473198338</v>
       </c>
       <c r="AO7" s="1">
         <f t="shared" si="5"/>
-        <v>19917.22645544809</v>
+        <v>20170.111547930323</v>
       </c>
       <c r="AP7" s="1">
         <f t="shared" si="5"/>
-        <v>20116.398720002573</v>
+        <v>20371.812663409626</v>
       </c>
       <c r="AQ7" s="1">
         <f t="shared" si="5"/>
-        <v>20317.5627072026</v>
+        <v>20575.530790043722</v>
       </c>
       <c r="AR7" s="1">
         <f t="shared" si="5"/>
-        <v>20520.738334274625</v>
+        <v>20781.286097944161</v>
       </c>
       <c r="AS7" s="1">
         <f t="shared" si="5"/>
-        <v>20725.945717617371</v>
+        <v>20989.098958923601</v>
       </c>
       <c r="AT7" s="1">
         <f t="shared" si="5"/>
-        <v>20933.205174793544</v>
+        <v>21198.989948512837</v>
       </c>
     </row>
     <row r="8" spans="1:46" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1631,7 +1634,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="7">
-        <f t="shared" ref="C8:X8" si="6">C3-C7</f>
+        <f t="shared" ref="C8:Y8" si="6">C3-C7</f>
         <v>1889</v>
       </c>
       <c r="D8" s="7">
@@ -1719,8 +1722,8 @@
         <v>3431</v>
       </c>
       <c r="Y8" s="7">
-        <f>Y3*0.41</f>
-        <v>3281.6154000000001</v>
+        <f t="shared" si="6"/>
+        <v>3424</v>
       </c>
       <c r="Z8" s="7">
         <f>Z3*0.42</f>
@@ -1756,47 +1759,47 @@
       </c>
       <c r="AJ8" s="7">
         <f t="shared" si="7"/>
-        <v>13579.472600000005</v>
+        <v>13721.857200000006</v>
       </c>
       <c r="AK8" s="7">
         <f>AK3*0.43</f>
-        <v>14268.798360000001</v>
+        <v>14449.966476000003</v>
       </c>
       <c r="AL8" s="7">
         <f>AL3*0.44</f>
-        <v>14892.6434976</v>
+        <v>15081.732452160002</v>
       </c>
       <c r="AM8" s="7">
         <f t="shared" ref="AM8:AT8" si="8">AM3*0.44</f>
-        <v>15190.496367551999</v>
+        <v>15383.367101203203</v>
       </c>
       <c r="AN8" s="7">
         <f t="shared" si="8"/>
-        <v>15494.306294903041</v>
+        <v>15691.034443227265</v>
       </c>
       <c r="AO8" s="7">
         <f t="shared" si="8"/>
-        <v>15649.24935785207</v>
+        <v>15847.94478765954</v>
       </c>
       <c r="AP8" s="7">
         <f t="shared" si="8"/>
-        <v>15805.741851430592</v>
+        <v>16006.424235536135</v>
       </c>
       <c r="AQ8" s="7">
         <f t="shared" si="8"/>
-        <v>15963.799269944899</v>
+        <v>16166.488477891497</v>
       </c>
       <c r="AR8" s="7">
         <f t="shared" si="8"/>
-        <v>16123.437262644349</v>
+        <v>16328.153362670411</v>
       </c>
       <c r="AS8" s="7">
         <f t="shared" si="8"/>
-        <v>16284.671635270792</v>
+        <v>16491.434896297116</v>
       </c>
       <c r="AT8" s="7">
         <f t="shared" si="8"/>
-        <v>16447.518351623501</v>
+        <v>16656.349245260088</v>
       </c>
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.3">
@@ -1870,12 +1873,11 @@
         <v>583</v>
       </c>
       <c r="Y9" s="1">
-        <f>Y3*0.06</f>
-        <v>480.2364</v>
+        <v>521</v>
       </c>
       <c r="Z9" s="1">
-        <f>Z3*0.07</f>
-        <v>591.47620000000006</v>
+        <f>Z3*0.08</f>
+        <v>675.97280000000001</v>
       </c>
       <c r="AC9" s="1">
         <v>1314</v>
@@ -1905,47 +1907,47 @@
       </c>
       <c r="AJ9" s="1">
         <f t="shared" ref="AJ9:AJ12" si="9">SUM(W9:Z9)</f>
-        <v>2142.7125999999998</v>
+        <v>2267.9728</v>
       </c>
       <c r="AK9" s="1">
         <f>AK3*0.07</f>
-        <v>2322.8276400000004</v>
+        <v>2352.3201240000008</v>
       </c>
       <c r="AL9" s="1">
         <f t="shared" ref="AL9:AT9" si="10">AL3*0.07</f>
-        <v>2369.2841928000003</v>
+        <v>2399.3665264800006</v>
       </c>
       <c r="AM9" s="1">
         <f t="shared" si="10"/>
-        <v>2416.6698766560003</v>
+        <v>2447.3538570096007</v>
       </c>
       <c r="AN9" s="1">
         <f t="shared" si="10"/>
-        <v>2465.0032741891205</v>
+        <v>2496.3009341497923</v>
       </c>
       <c r="AO9" s="1">
         <f t="shared" si="10"/>
-        <v>2489.6533069310112</v>
+        <v>2521.2639434912908</v>
       </c>
       <c r="AP9" s="1">
         <f t="shared" si="10"/>
-        <v>2514.5498400003216</v>
+        <v>2546.4765829262037</v>
       </c>
       <c r="AQ9" s="1">
         <f t="shared" si="10"/>
-        <v>2539.695338400325</v>
+        <v>2571.9413487554657</v>
       </c>
       <c r="AR9" s="1">
         <f t="shared" si="10"/>
-        <v>2565.0922917843286</v>
+        <v>2597.6607622430201</v>
       </c>
       <c r="AS9" s="1">
         <f t="shared" si="10"/>
-        <v>2590.7432147021718</v>
+        <v>2623.6373698654506</v>
       </c>
       <c r="AT9" s="1">
         <f t="shared" si="10"/>
-        <v>2616.6506468491934</v>
+        <v>2649.8737435641051</v>
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.3">
@@ -2019,12 +2021,11 @@
         <v>767</v>
       </c>
       <c r="Y10" s="1">
-        <f>U10*1.04</f>
-        <v>775.84</v>
+        <v>801</v>
       </c>
       <c r="Z10" s="1">
-        <f>V10*1.01</f>
-        <v>780.73</v>
+        <f>V10*1.05</f>
+        <v>811.65000000000009</v>
       </c>
       <c r="AC10" s="1">
         <v>1831</v>
@@ -2054,47 +2055,47 @@
       </c>
       <c r="AJ10" s="1">
         <f t="shared" si="9"/>
-        <v>3054.57</v>
+        <v>3110.65</v>
       </c>
       <c r="AK10" s="1">
-        <f t="shared" ref="AK10" si="11">AJ10*1.02</f>
-        <v>3115.6614000000004</v>
+        <f>AJ10*1.03</f>
+        <v>3203.9695000000002</v>
       </c>
       <c r="AL10" s="1">
-        <f>AK10*1.01</f>
-        <v>3146.8180140000004</v>
+        <f>AK10*1.02</f>
+        <v>3268.04889</v>
       </c>
       <c r="AM10" s="1">
-        <f t="shared" ref="AM10:AT10" si="12">AL10*1.01</f>
-        <v>3178.2861941400006</v>
+        <f t="shared" ref="AM10:AT10" si="11">AL10*1.01</f>
+        <v>3300.7293789</v>
       </c>
       <c r="AN10" s="1">
-        <f t="shared" si="12"/>
-        <v>3210.0690560814005</v>
+        <f t="shared" si="11"/>
+        <v>3333.736672689</v>
       </c>
       <c r="AO10" s="1">
-        <f t="shared" si="12"/>
-        <v>3242.1697466422147</v>
+        <f t="shared" si="11"/>
+        <v>3367.0740394158902</v>
       </c>
       <c r="AP10" s="1">
-        <f t="shared" si="12"/>
-        <v>3274.591444108637</v>
+        <f t="shared" si="11"/>
+        <v>3400.7447798100493</v>
       </c>
       <c r="AQ10" s="1">
-        <f t="shared" si="12"/>
-        <v>3307.3373585497234</v>
+        <f t="shared" si="11"/>
+        <v>3434.75222760815</v>
       </c>
       <c r="AR10" s="1">
-        <f t="shared" si="12"/>
-        <v>3340.4107321352208</v>
+        <f t="shared" si="11"/>
+        <v>3469.0997498842316</v>
       </c>
       <c r="AS10" s="1">
-        <f t="shared" si="12"/>
-        <v>3373.8148394565728</v>
+        <f t="shared" si="11"/>
+        <v>3503.7907473830742</v>
       </c>
       <c r="AT10" s="1">
-        <f t="shared" si="12"/>
-        <v>3407.5529878511384</v>
+        <f t="shared" si="11"/>
+        <v>3538.8286548569049</v>
       </c>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.3">
@@ -2168,11 +2169,10 @@
         <v>461</v>
       </c>
       <c r="Y11" s="1">
-        <f>U11*0.98</f>
-        <v>508.62</v>
+        <v>513</v>
       </c>
       <c r="Z11" s="1">
-        <f t="shared" ref="Z11" si="13">V11*0.98</f>
+        <f t="shared" ref="Z11" si="12">V11*0.98</f>
         <v>582.12</v>
       </c>
       <c r="AC11" s="1">
@@ -2203,47 +2203,47 @@
       </c>
       <c r="AJ11" s="1">
         <f t="shared" si="9"/>
-        <v>2054.7399999999998</v>
+        <v>2059.12</v>
       </c>
       <c r="AK11" s="1">
         <f>AJ11*1.02</f>
-        <v>2095.8347999999996</v>
+        <v>2100.3024</v>
       </c>
       <c r="AL11" s="1">
-        <f t="shared" ref="AL11:AT11" si="14">AK11*1.01</f>
-        <v>2116.7931479999997</v>
+        <f t="shared" ref="AL11:AT11" si="13">AK11*1.01</f>
+        <v>2121.3054240000001</v>
       </c>
       <c r="AM11" s="1">
-        <f t="shared" si="14"/>
-        <v>2137.9610794799996</v>
+        <f t="shared" si="13"/>
+        <v>2142.5184782400001</v>
       </c>
       <c r="AN11" s="1">
-        <f t="shared" si="14"/>
-        <v>2159.3406902747997</v>
+        <f t="shared" si="13"/>
+        <v>2163.9436630224</v>
       </c>
       <c r="AO11" s="1">
-        <f t="shared" si="14"/>
-        <v>2180.9340971775478</v>
+        <f t="shared" si="13"/>
+        <v>2185.5830996526238</v>
       </c>
       <c r="AP11" s="1">
-        <f t="shared" si="14"/>
-        <v>2202.7434381493231</v>
+        <f t="shared" si="13"/>
+        <v>2207.4389306491498</v>
       </c>
       <c r="AQ11" s="1">
-        <f t="shared" si="14"/>
-        <v>2224.7708725308162</v>
+        <f t="shared" si="13"/>
+        <v>2229.5133199556412</v>
       </c>
       <c r="AR11" s="1">
-        <f t="shared" si="14"/>
-        <v>2247.0185812561244</v>
+        <f t="shared" si="13"/>
+        <v>2251.8084531551976</v>
       </c>
       <c r="AS11" s="1">
-        <f t="shared" si="14"/>
-        <v>2269.4887670686858</v>
+        <f t="shared" si="13"/>
+        <v>2274.3265376867498</v>
       </c>
       <c r="AT11" s="1">
-        <f t="shared" si="14"/>
-        <v>2292.1836547393727</v>
+        <f t="shared" si="13"/>
+        <v>2297.0698030636172</v>
       </c>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.3">
@@ -2317,7 +2317,7 @@
         <v>116</v>
       </c>
       <c r="Y12" s="1">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="Z12" s="1">
         <v>50</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AJ12" s="1">
         <f t="shared" si="9"/>
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="AK12" s="1">
         <v>100</v>
@@ -2389,172 +2389,172 @@
         <v>31</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:S13" si="15">C8-SUM(C9:C12)</f>
+        <f t="shared" ref="C13:S13" si="14">C8-SUM(C9:C12)</f>
         <v>398</v>
       </c>
       <c r="D13" s="7">
+        <f t="shared" si="14"/>
+        <v>951</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="14"/>
+        <v>977</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="14"/>
+        <v>963</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="14"/>
+        <v>1042</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="14"/>
+        <v>1127</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="14"/>
+        <v>1043</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="14"/>
+        <v>1050</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="14"/>
+        <v>711</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="14"/>
+        <v>764</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="14"/>
+        <v>1118</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="14"/>
+        <v>1244</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" si="14"/>
+        <v>999</v>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" si="14"/>
+        <v>1133</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="14"/>
+        <v>1168</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="14"/>
+        <v>1728</v>
+      </c>
+      <c r="S13" s="7">
+        <f t="shared" si="14"/>
+        <v>1168</v>
+      </c>
+      <c r="T13" s="7">
+        <f t="shared" ref="T13:Z13" si="15">T8-SUM(T9:T12)</f>
+        <v>1325</v>
+      </c>
+      <c r="U13" s="7">
         <f t="shared" si="15"/>
-        <v>951</v>
-      </c>
-      <c r="E13" s="7">
+        <v>1391</v>
+      </c>
+      <c r="V13" s="7">
         <f t="shared" si="15"/>
-        <v>977</v>
-      </c>
-      <c r="F13" s="7">
+        <v>1441</v>
+      </c>
+      <c r="W13" s="7">
         <f t="shared" si="15"/>
-        <v>963</v>
-      </c>
-      <c r="G13" s="7">
+        <v>1530</v>
+      </c>
+      <c r="X13" s="7">
         <f t="shared" si="15"/>
-        <v>1042</v>
-      </c>
-      <c r="H13" s="7">
+        <v>1504</v>
+      </c>
+      <c r="Y13" s="7">
         <f t="shared" si="15"/>
-        <v>1127</v>
-      </c>
-      <c r="I13" s="7">
+        <v>1520</v>
+      </c>
+      <c r="Z13" s="7">
         <f t="shared" si="15"/>
-        <v>1043</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="15"/>
-        <v>1050</v>
-      </c>
-      <c r="K13" s="7">
-        <f t="shared" si="15"/>
-        <v>711</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="15"/>
-        <v>764</v>
-      </c>
-      <c r="M13" s="7">
-        <f t="shared" si="15"/>
-        <v>1118</v>
-      </c>
-      <c r="N13" s="7">
-        <f t="shared" si="15"/>
-        <v>1244</v>
-      </c>
-      <c r="O13" s="7">
-        <f t="shared" si="15"/>
-        <v>999</v>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="15"/>
-        <v>1133</v>
-      </c>
-      <c r="Q13" s="7">
-        <f t="shared" si="15"/>
-        <v>1168</v>
-      </c>
-      <c r="R13" s="7">
-        <f t="shared" si="15"/>
-        <v>1728</v>
-      </c>
-      <c r="S13" s="7">
-        <f t="shared" si="15"/>
-        <v>1168</v>
-      </c>
-      <c r="T13" s="7">
-        <f t="shared" ref="T13:Z13" si="16">T8-SUM(T9:T12)</f>
-        <v>1325</v>
-      </c>
-      <c r="U13" s="7">
+        <v>1429.1143999999999</v>
+      </c>
+      <c r="AC13" s="7">
+        <f t="shared" ref="AC13:AJ13" si="16">AC8-SUM(AC9:AC12)</f>
+        <v>2194</v>
+      </c>
+      <c r="AD13" s="7">
         <f t="shared" si="16"/>
-        <v>1391</v>
-      </c>
-      <c r="V13" s="7">
+        <v>2719</v>
+      </c>
+      <c r="AE13" s="7">
         <f t="shared" si="16"/>
-        <v>1441</v>
-      </c>
-      <c r="W13" s="7">
+        <v>3289</v>
+      </c>
+      <c r="AF13" s="7">
         <f t="shared" si="16"/>
-        <v>1530</v>
-      </c>
-      <c r="X13" s="7">
+        <v>4262</v>
+      </c>
+      <c r="AG13" s="7">
         <f t="shared" si="16"/>
-        <v>1504</v>
-      </c>
-      <c r="Y13" s="7">
+        <v>3837</v>
+      </c>
+      <c r="AH13" s="7">
         <f t="shared" si="16"/>
-        <v>1416.9190000000003</v>
-      </c>
-      <c r="Z13" s="7">
+        <v>5028</v>
+      </c>
+      <c r="AI13" s="7">
         <f t="shared" si="16"/>
-        <v>1544.5309999999999</v>
-      </c>
-      <c r="AC13" s="7">
-        <f t="shared" ref="AC13:AJ13" si="17">AC8-SUM(AC9:AC12)</f>
-        <v>2194</v>
-      </c>
-      <c r="AD13" s="7">
+        <v>5325</v>
+      </c>
+      <c r="AJ13" s="7">
+        <f t="shared" si="16"/>
+        <v>5983.1144000000058</v>
+      </c>
+      <c r="AK13" s="7">
+        <f t="shared" ref="AK13:AT13" si="17">AK8-SUM(AK9:AK12)</f>
+        <v>6693.3744520000018</v>
+      </c>
+      <c r="AL13" s="7">
         <f t="shared" si="17"/>
-        <v>2719</v>
-      </c>
-      <c r="AE13" s="7">
+        <v>7193.0116116800018</v>
+      </c>
+      <c r="AM13" s="7">
         <f t="shared" si="17"/>
-        <v>3289</v>
-      </c>
-      <c r="AF13" s="7">
+        <v>7392.7653870536024</v>
+      </c>
+      <c r="AN13" s="7">
         <f t="shared" si="17"/>
-        <v>4262</v>
-      </c>
-      <c r="AG13" s="7">
+        <v>7597.0531733660728</v>
+      </c>
+      <c r="AO13" s="7">
         <f t="shared" si="17"/>
-        <v>3837</v>
-      </c>
-      <c r="AH13" s="7">
+        <v>7674.0237050997357</v>
+      </c>
+      <c r="AP13" s="7">
         <f t="shared" si="17"/>
-        <v>5028</v>
-      </c>
-      <c r="AI13" s="7">
+        <v>7751.763942150732</v>
+      </c>
+      <c r="AQ13" s="7">
         <f t="shared" si="17"/>
-        <v>5325</v>
-      </c>
-      <c r="AJ13" s="7">
+        <v>7830.2815815722388</v>
+      </c>
+      <c r="AR13" s="7">
         <f t="shared" si="17"/>
-        <v>5995.4500000000044</v>
-      </c>
-      <c r="AK13" s="7">
-        <f t="shared" ref="AK13:AT13" si="18">AK8-SUM(AK9:AK12)</f>
-        <v>6634.4745200000007</v>
-      </c>
-      <c r="AL13" s="7">
-        <f t="shared" si="18"/>
-        <v>7159.7481428000001</v>
-      </c>
-      <c r="AM13" s="7">
-        <f t="shared" si="18"/>
-        <v>7357.5792172759993</v>
-      </c>
-      <c r="AN13" s="7">
-        <f t="shared" si="18"/>
-        <v>7559.8932743577207</v>
-      </c>
-      <c r="AO13" s="7">
-        <f t="shared" si="18"/>
-        <v>7636.492207101297</v>
-      </c>
-      <c r="AP13" s="7">
-        <f t="shared" si="18"/>
-        <v>7713.8571291723101</v>
-      </c>
-      <c r="AQ13" s="7">
-        <f t="shared" si="18"/>
-        <v>7791.9957004640346</v>
-      </c>
-      <c r="AR13" s="7">
-        <f t="shared" si="18"/>
-        <v>7870.9156574686749</v>
+        <v>7909.5843973879619</v>
       </c>
       <c r="AS13" s="7">
-        <f t="shared" si="18"/>
-        <v>7950.6248140433618</v>
+        <f t="shared" si="17"/>
+        <v>7989.6802413618425</v>
       </c>
       <c r="AT13" s="7">
-        <f t="shared" si="18"/>
-        <v>8031.1310621837965</v>
+        <f t="shared" si="17"/>
+        <v>8070.57704377546</v>
       </c>
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.3">
@@ -2628,7 +2628,7 @@
         <v>-25</v>
       </c>
       <c r="Y14" s="1">
-        <v>-20</v>
+        <v>-13</v>
       </c>
       <c r="Z14" s="1">
         <v>-20</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AJ14" s="1">
         <f>SUM(W14:Z14)</f>
-        <v>-138</v>
+        <v>-131</v>
       </c>
       <c r="AK14" s="1">
         <v>0</v>
@@ -2700,172 +2700,172 @@
         <v>33</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:S15" si="19">C13-C14</f>
+        <f t="shared" ref="C15:S15" si="18">C13-C14</f>
         <v>263</v>
       </c>
       <c r="D15" s="7">
+        <f t="shared" si="18"/>
+        <v>1799</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="18"/>
+        <v>1144</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="18"/>
+        <v>1859</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="18"/>
+        <v>872</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="18"/>
+        <v>1356</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="18"/>
+        <v>1165</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="18"/>
+        <v>706</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="18"/>
+        <v>629</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="18"/>
+        <v>49</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="18"/>
+        <v>1578</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="18"/>
+        <v>1110</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" si="18"/>
+        <v>1074</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" si="18"/>
+        <v>1303</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="18"/>
+        <v>1241</v>
+      </c>
+      <c r="R15" s="7">
+        <f t="shared" si="18"/>
+        <v>1793</v>
+      </c>
+      <c r="S15" s="7">
+        <f t="shared" si="18"/>
+        <v>1209</v>
+      </c>
+      <c r="T15" s="7">
+        <f t="shared" ref="T15:Z15" si="19">T13-T14</f>
+        <v>1399</v>
+      </c>
+      <c r="U15" s="7">
         <f t="shared" si="19"/>
-        <v>1799</v>
-      </c>
-      <c r="E15" s="7">
+        <v>1311</v>
+      </c>
+      <c r="V15" s="7">
         <f t="shared" si="19"/>
-        <v>1144</v>
-      </c>
-      <c r="F15" s="7">
+        <v>1410</v>
+      </c>
+      <c r="W15" s="7">
         <f t="shared" si="19"/>
-        <v>1859</v>
-      </c>
-      <c r="G15" s="7">
+        <v>1603</v>
+      </c>
+      <c r="X15" s="7">
         <f t="shared" si="19"/>
-        <v>872</v>
-      </c>
-      <c r="H15" s="7">
+        <v>1529</v>
+      </c>
+      <c r="Y15" s="7">
         <f t="shared" si="19"/>
-        <v>1356</v>
-      </c>
-      <c r="I15" s="7">
+        <v>1533</v>
+      </c>
+      <c r="Z15" s="7">
         <f t="shared" si="19"/>
-        <v>1165</v>
-      </c>
-      <c r="J15" s="7">
-        <f t="shared" si="19"/>
-        <v>706</v>
-      </c>
-      <c r="K15" s="7">
-        <f t="shared" si="19"/>
-        <v>629</v>
-      </c>
-      <c r="L15" s="7">
-        <f t="shared" si="19"/>
-        <v>49</v>
-      </c>
-      <c r="M15" s="7">
-        <f t="shared" si="19"/>
-        <v>1578</v>
-      </c>
-      <c r="N15" s="7">
-        <f t="shared" si="19"/>
-        <v>1110</v>
-      </c>
-      <c r="O15" s="7">
-        <f t="shared" si="19"/>
-        <v>1074</v>
-      </c>
-      <c r="P15" s="7">
-        <f t="shared" si="19"/>
-        <v>1303</v>
-      </c>
-      <c r="Q15" s="7">
-        <f t="shared" si="19"/>
-        <v>1241</v>
-      </c>
-      <c r="R15" s="7">
-        <f t="shared" si="19"/>
-        <v>1793</v>
-      </c>
-      <c r="S15" s="7">
-        <f t="shared" si="19"/>
-        <v>1209</v>
-      </c>
-      <c r="T15" s="7">
-        <f t="shared" ref="T15:Z15" si="20">T13-T14</f>
-        <v>1399</v>
-      </c>
-      <c r="U15" s="7">
+        <v>1449.1143999999999</v>
+      </c>
+      <c r="AC15" s="7">
+        <f t="shared" ref="AC15:AJ15" si="20">AC13-AC14</f>
+        <v>2376</v>
+      </c>
+      <c r="AD15" s="7">
         <f t="shared" si="20"/>
-        <v>1311</v>
-      </c>
-      <c r="V15" s="7">
+        <v>2998</v>
+      </c>
+      <c r="AE15" s="7">
         <f t="shared" si="20"/>
-        <v>1410</v>
-      </c>
-      <c r="W15" s="7">
+        <v>5065</v>
+      </c>
+      <c r="AF15" s="7">
         <f t="shared" si="20"/>
-        <v>1603</v>
-      </c>
-      <c r="X15" s="7">
+        <v>4099</v>
+      </c>
+      <c r="AG15" s="7">
         <f t="shared" si="20"/>
-        <v>1529</v>
-      </c>
-      <c r="Y15" s="7">
+        <v>3366</v>
+      </c>
+      <c r="AH15" s="7">
         <f t="shared" si="20"/>
-        <v>1436.9190000000003</v>
-      </c>
-      <c r="Z15" s="7">
+        <v>5411</v>
+      </c>
+      <c r="AI15" s="7">
         <f t="shared" si="20"/>
-        <v>1564.5309999999999</v>
-      </c>
-      <c r="AC15" s="7">
-        <f t="shared" ref="AC15:AJ15" si="21">AC13-AC14</f>
-        <v>2376</v>
-      </c>
-      <c r="AD15" s="7">
+        <v>5329</v>
+      </c>
+      <c r="AJ15" s="7">
+        <f t="shared" si="20"/>
+        <v>6114.1144000000058</v>
+      </c>
+      <c r="AK15" s="7">
+        <f t="shared" ref="AK15:AT15" si="21">AK13-AK14</f>
+        <v>6693.3744520000018</v>
+      </c>
+      <c r="AL15" s="7">
         <f t="shared" si="21"/>
-        <v>2998</v>
-      </c>
-      <c r="AE15" s="7">
+        <v>7193.0116116800018</v>
+      </c>
+      <c r="AM15" s="7">
         <f t="shared" si="21"/>
-        <v>5065</v>
-      </c>
-      <c r="AF15" s="7">
+        <v>7392.7653870536024</v>
+      </c>
+      <c r="AN15" s="7">
         <f t="shared" si="21"/>
-        <v>4099</v>
-      </c>
-      <c r="AG15" s="7">
+        <v>7597.0531733660728</v>
+      </c>
+      <c r="AO15" s="7">
         <f t="shared" si="21"/>
-        <v>3366</v>
-      </c>
-      <c r="AH15" s="7">
+        <v>7674.0237050997357</v>
+      </c>
+      <c r="AP15" s="7">
         <f t="shared" si="21"/>
-        <v>5411</v>
-      </c>
-      <c r="AI15" s="7">
+        <v>7751.763942150732</v>
+      </c>
+      <c r="AQ15" s="7">
         <f t="shared" si="21"/>
-        <v>5329</v>
-      </c>
-      <c r="AJ15" s="7">
+        <v>7830.2815815722388</v>
+      </c>
+      <c r="AR15" s="7">
         <f t="shared" si="21"/>
-        <v>6133.4500000000044</v>
-      </c>
-      <c r="AK15" s="7">
-        <f t="shared" ref="AK15:AT15" si="22">AK13-AK14</f>
-        <v>6634.4745200000007</v>
-      </c>
-      <c r="AL15" s="7">
-        <f t="shared" si="22"/>
-        <v>7159.7481428000001</v>
-      </c>
-      <c r="AM15" s="7">
-        <f t="shared" si="22"/>
-        <v>7357.5792172759993</v>
-      </c>
-      <c r="AN15" s="7">
-        <f t="shared" si="22"/>
-        <v>7559.8932743577207</v>
-      </c>
-      <c r="AO15" s="7">
-        <f t="shared" si="22"/>
-        <v>7636.492207101297</v>
-      </c>
-      <c r="AP15" s="7">
-        <f t="shared" si="22"/>
-        <v>7713.8571291723101</v>
-      </c>
-      <c r="AQ15" s="7">
-        <f t="shared" si="22"/>
-        <v>7791.9957004640346</v>
-      </c>
-      <c r="AR15" s="7">
-        <f t="shared" si="22"/>
-        <v>7870.9156574686749</v>
+        <v>7909.5843973879619</v>
       </c>
       <c r="AS15" s="7">
-        <f t="shared" si="22"/>
-        <v>7950.6248140433618</v>
+        <f t="shared" si="21"/>
+        <v>7989.6802413618425</v>
       </c>
       <c r="AT15" s="7">
-        <f t="shared" si="22"/>
-        <v>8031.1310621837965</v>
+        <f t="shared" si="21"/>
+        <v>8070.57704377546</v>
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.3">
@@ -2939,12 +2939,11 @@
         <v>268</v>
       </c>
       <c r="Y16" s="1">
-        <f>Y15*0.2</f>
-        <v>287.38380000000006</v>
+        <v>285</v>
       </c>
       <c r="Z16" s="1">
-        <f t="shared" ref="Z16" si="23">Z15*0.2</f>
-        <v>312.90620000000001</v>
+        <f t="shared" ref="Z16" si="22">Z15*0.2</f>
+        <v>289.82288</v>
       </c>
       <c r="AC16" s="1">
         <v>319</v>
@@ -2974,47 +2973,47 @@
       </c>
       <c r="AJ16" s="1">
         <f>SUM(W16:Z16)</f>
-        <v>1184.29</v>
+        <v>1158.8228799999999</v>
       </c>
       <c r="AK16" s="1">
         <f>AK15*0.2</f>
-        <v>1326.8949040000002</v>
+        <v>1338.6748904000005</v>
       </c>
       <c r="AL16" s="1">
-        <f t="shared" ref="AL16:AT16" si="24">AL15*0.2</f>
-        <v>1431.9496285600001</v>
+        <f t="shared" ref="AL16:AT16" si="23">AL15*0.2</f>
+        <v>1438.6023223360005</v>
       </c>
       <c r="AM16" s="1">
-        <f t="shared" si="24"/>
-        <v>1471.5158434552</v>
+        <f t="shared" si="23"/>
+        <v>1478.5530774107206</v>
       </c>
       <c r="AN16" s="1">
-        <f t="shared" si="24"/>
-        <v>1511.9786548715442</v>
+        <f t="shared" si="23"/>
+        <v>1519.4106346732146</v>
       </c>
       <c r="AO16" s="1">
-        <f t="shared" si="24"/>
-        <v>1527.2984414202595</v>
+        <f t="shared" si="23"/>
+        <v>1534.8047410199472</v>
       </c>
       <c r="AP16" s="1">
-        <f t="shared" si="24"/>
-        <v>1542.7714258344622</v>
+        <f t="shared" si="23"/>
+        <v>1550.3527884301466</v>
       </c>
       <c r="AQ16" s="1">
-        <f t="shared" si="24"/>
-        <v>1558.3991400928071</v>
+        <f t="shared" si="23"/>
+        <v>1566.0563163144479</v>
       </c>
       <c r="AR16" s="1">
-        <f t="shared" si="24"/>
-        <v>1574.1831314937351</v>
+        <f t="shared" si="23"/>
+        <v>1581.9168794775924</v>
       </c>
       <c r="AS16" s="1">
-        <f t="shared" si="24"/>
-        <v>1590.1249628086725</v>
+        <f t="shared" si="23"/>
+        <v>1597.9360482723687</v>
       </c>
       <c r="AT16" s="1">
-        <f t="shared" si="24"/>
-        <v>1606.2262124367594</v>
+        <f t="shared" si="23"/>
+        <v>1614.1154087550922</v>
       </c>
     </row>
     <row r="17" spans="1:146" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3023,572 +3022,572 @@
         <v>35</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:S17" si="25">C15-C16</f>
+        <f t="shared" ref="C17:S17" si="24">C15-C16</f>
         <v>84</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="24"/>
+        <v>1530</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="24"/>
+        <v>1021</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="24"/>
+        <v>1567</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="24"/>
+        <v>1097</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="24"/>
+        <v>1184</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="24"/>
+        <v>1087</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="24"/>
+        <v>801</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="24"/>
+        <v>509</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="24"/>
+        <v>-341</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" si="24"/>
+        <v>1330</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="24"/>
+        <v>921</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="24"/>
+        <v>795</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="24"/>
+        <v>1029</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="24"/>
+        <v>1020</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="24"/>
+        <v>1402</v>
+      </c>
+      <c r="S17" s="7">
+        <f t="shared" si="24"/>
+        <v>888</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:V17" si="25">T15-T16</f>
+        <v>1128</v>
+      </c>
+      <c r="U17" s="7">
         <f t="shared" si="25"/>
-        <v>1530</v>
-      </c>
-      <c r="E17" s="7">
+        <v>1010</v>
+      </c>
+      <c r="V17" s="7">
         <f t="shared" si="25"/>
-        <v>1021</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="25"/>
-        <v>1567</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="25"/>
-        <v>1097</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="25"/>
-        <v>1184</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="25"/>
-        <v>1087</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="25"/>
-        <v>801</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="25"/>
-        <v>509</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="25"/>
-        <v>-341</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" si="25"/>
-        <v>1330</v>
-      </c>
-      <c r="N17" s="7">
-        <f t="shared" si="25"/>
-        <v>921</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" si="25"/>
-        <v>795</v>
-      </c>
-      <c r="P17" s="7">
-        <f t="shared" si="25"/>
-        <v>1029</v>
-      </c>
-      <c r="Q17" s="7">
-        <f t="shared" si="25"/>
-        <v>1020</v>
-      </c>
-      <c r="R17" s="7">
-        <f t="shared" si="25"/>
-        <v>1402</v>
-      </c>
-      <c r="S17" s="7">
-        <f t="shared" si="25"/>
-        <v>888</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:V17" si="26">T15-T16</f>
-        <v>1128</v>
-      </c>
-      <c r="U17" s="7">
+        <v>1121</v>
+      </c>
+      <c r="W17" s="7">
+        <f t="shared" ref="W17:Z17" si="26">W15-W16</f>
+        <v>1287</v>
+      </c>
+      <c r="X17" s="7">
         <f t="shared" si="26"/>
-        <v>1010</v>
-      </c>
-      <c r="V17" s="7">
+        <v>1261</v>
+      </c>
+      <c r="Y17" s="7">
         <f t="shared" si="26"/>
-        <v>1121</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" ref="W17:Z17" si="27">W15-W16</f>
-        <v>1287</v>
-      </c>
-      <c r="X17" s="7">
+        <v>1248</v>
+      </c>
+      <c r="Z17" s="7">
+        <f t="shared" si="26"/>
+        <v>1159.29152</v>
+      </c>
+      <c r="AC17" s="7">
+        <f t="shared" ref="AC17:AJ17" si="27">AC15-AC16</f>
+        <v>2057</v>
+      </c>
+      <c r="AD17" s="7">
         <f t="shared" si="27"/>
-        <v>1261</v>
-      </c>
-      <c r="Y17" s="7">
+        <v>2459</v>
+      </c>
+      <c r="AE17" s="7">
         <f t="shared" si="27"/>
-        <v>1149.5352000000003</v>
-      </c>
-      <c r="Z17" s="7">
+        <v>4202</v>
+      </c>
+      <c r="AF17" s="7">
         <f t="shared" si="27"/>
-        <v>1251.6248000000001</v>
-      </c>
-      <c r="AC17" s="7">
-        <f t="shared" ref="AC17:AJ17" si="28">AC15-AC16</f>
-        <v>2057</v>
-      </c>
-      <c r="AD17" s="7">
+        <v>4169</v>
+      </c>
+      <c r="AG17" s="7">
+        <f t="shared" si="27"/>
+        <v>2419</v>
+      </c>
+      <c r="AH17" s="7">
+        <f t="shared" si="27"/>
+        <v>4246</v>
+      </c>
+      <c r="AI17" s="7">
+        <f t="shared" si="27"/>
+        <v>4147</v>
+      </c>
+      <c r="AJ17" s="7">
+        <f t="shared" si="27"/>
+        <v>4955.2915200000061</v>
+      </c>
+      <c r="AK17" s="7">
+        <f t="shared" ref="AK17:AT17" si="28">AK15-AK16</f>
+        <v>5354.6995616000013</v>
+      </c>
+      <c r="AL17" s="7">
         <f t="shared" si="28"/>
-        <v>2459</v>
-      </c>
-      <c r="AE17" s="7">
+        <v>5754.4092893440011</v>
+      </c>
+      <c r="AM17" s="7">
         <f t="shared" si="28"/>
-        <v>4202</v>
-      </c>
-      <c r="AF17" s="7">
+        <v>5914.2123096428822</v>
+      </c>
+      <c r="AN17" s="7">
         <f t="shared" si="28"/>
-        <v>4169</v>
-      </c>
-      <c r="AG17" s="7">
+        <v>6077.6425386928586</v>
+      </c>
+      <c r="AO17" s="7">
         <f t="shared" si="28"/>
-        <v>2419</v>
-      </c>
-      <c r="AH17" s="7">
+        <v>6139.2189640797887</v>
+      </c>
+      <c r="AP17" s="7">
         <f t="shared" si="28"/>
-        <v>4246</v>
-      </c>
-      <c r="AI17" s="7">
+        <v>6201.4111537205854</v>
+      </c>
+      <c r="AQ17" s="7">
         <f t="shared" si="28"/>
-        <v>4147</v>
-      </c>
-      <c r="AJ17" s="7">
+        <v>6264.2252652577909</v>
+      </c>
+      <c r="AR17" s="7">
         <f t="shared" si="28"/>
-        <v>4949.1600000000044</v>
-      </c>
-      <c r="AK17" s="7">
-        <f t="shared" ref="AK17:AT17" si="29">AK15-AK16</f>
-        <v>5307.5796160000009</v>
-      </c>
-      <c r="AL17" s="7">
-        <f t="shared" si="29"/>
-        <v>5727.7985142400003</v>
-      </c>
-      <c r="AM17" s="7">
-        <f t="shared" si="29"/>
-        <v>5886.0633738207998</v>
-      </c>
-      <c r="AN17" s="7">
-        <f t="shared" si="29"/>
-        <v>6047.9146194861769</v>
-      </c>
-      <c r="AO17" s="7">
-        <f t="shared" si="29"/>
-        <v>6109.1937656810378</v>
-      </c>
-      <c r="AP17" s="7">
-        <f t="shared" si="29"/>
-        <v>6171.0857033378479</v>
-      </c>
-      <c r="AQ17" s="7">
-        <f t="shared" si="29"/>
-        <v>6233.5965603712275</v>
-      </c>
-      <c r="AR17" s="7">
-        <f t="shared" si="29"/>
-        <v>6296.7325259749396</v>
+        <v>6327.6675179103695</v>
       </c>
       <c r="AS17" s="7">
-        <f t="shared" si="29"/>
-        <v>6360.4998512346892</v>
+        <f t="shared" si="28"/>
+        <v>6391.7441930894738</v>
       </c>
       <c r="AT17" s="7">
-        <f t="shared" si="29"/>
-        <v>6424.9048497470376</v>
+        <f t="shared" si="28"/>
+        <v>6456.4616350203678</v>
       </c>
       <c r="AU17" s="6">
         <f>AT17*(1+$AX$22)</f>
-        <v>6360.655801249567</v>
+        <v>6391.8970186701645</v>
       </c>
       <c r="AV17" s="6">
-        <f t="shared" ref="AV17:DG17" si="30">AU17*(1+$AX$22)</f>
-        <v>6297.0492432370711</v>
+        <f t="shared" ref="AV17:DG17" si="29">AU17*(1+$AX$22)</f>
+        <v>6327.9780484834628</v>
       </c>
       <c r="AW17" s="6">
+        <f t="shared" si="29"/>
+        <v>6264.6982679986277</v>
+      </c>
+      <c r="AX17" s="6">
+        <f t="shared" si="29"/>
+        <v>6202.051285318641</v>
+      </c>
+      <c r="AY17" s="6">
+        <f t="shared" si="29"/>
+        <v>6140.0307724654549</v>
+      </c>
+      <c r="AZ17" s="6">
+        <f t="shared" si="29"/>
+        <v>6078.6304647408006</v>
+      </c>
+      <c r="BA17" s="6">
+        <f t="shared" si="29"/>
+        <v>6017.8441600933929</v>
+      </c>
+      <c r="BB17" s="6">
+        <f t="shared" si="29"/>
+        <v>5957.6657184924588</v>
+      </c>
+      <c r="BC17" s="6">
+        <f t="shared" si="29"/>
+        <v>5898.0890613075344</v>
+      </c>
+      <c r="BD17" s="6">
+        <f t="shared" si="29"/>
+        <v>5839.1081706944587</v>
+      </c>
+      <c r="BE17" s="6">
+        <f t="shared" si="29"/>
+        <v>5780.7170889875142</v>
+      </c>
+      <c r="BF17" s="6">
+        <f t="shared" si="29"/>
+        <v>5722.9099180976391</v>
+      </c>
+      <c r="BG17" s="6">
+        <f t="shared" si="29"/>
+        <v>5665.6808189166622</v>
+      </c>
+      <c r="BH17" s="6">
+        <f t="shared" si="29"/>
+        <v>5609.0240107274958</v>
+      </c>
+      <c r="BI17" s="6">
+        <f t="shared" si="29"/>
+        <v>5552.9337706202205</v>
+      </c>
+      <c r="BJ17" s="6">
+        <f t="shared" si="29"/>
+        <v>5497.4044329140179</v>
+      </c>
+      <c r="BK17" s="6">
+        <f t="shared" si="29"/>
+        <v>5442.4303885848776</v>
+      </c>
+      <c r="BL17" s="6">
+        <f t="shared" si="29"/>
+        <v>5388.0060846990291</v>
+      </c>
+      <c r="BM17" s="6">
+        <f t="shared" si="29"/>
+        <v>5334.126023852039</v>
+      </c>
+      <c r="BN17" s="6">
+        <f t="shared" si="29"/>
+        <v>5280.7847636135184</v>
+      </c>
+      <c r="BO17" s="6">
+        <f t="shared" si="29"/>
+        <v>5227.9769159773832</v>
+      </c>
+      <c r="BP17" s="6">
+        <f t="shared" si="29"/>
+        <v>5175.6971468176089</v>
+      </c>
+      <c r="BQ17" s="6">
+        <f t="shared" si="29"/>
+        <v>5123.940175349433</v>
+      </c>
+      <c r="BR17" s="6">
+        <f t="shared" si="29"/>
+        <v>5072.7007735959387</v>
+      </c>
+      <c r="BS17" s="6">
+        <f t="shared" si="29"/>
+        <v>5021.9737658599797</v>
+      </c>
+      <c r="BT17" s="6">
+        <f t="shared" si="29"/>
+        <v>4971.7540282013797</v>
+      </c>
+      <c r="BU17" s="6">
+        <f t="shared" si="29"/>
+        <v>4922.0364879193658</v>
+      </c>
+      <c r="BV17" s="6">
+        <f t="shared" si="29"/>
+        <v>4872.816123040172</v>
+      </c>
+      <c r="BW17" s="6">
+        <f t="shared" si="29"/>
+        <v>4824.0879618097706</v>
+      </c>
+      <c r="BX17" s="6">
+        <f t="shared" si="29"/>
+        <v>4775.8470821916726</v>
+      </c>
+      <c r="BY17" s="6">
+        <f t="shared" si="29"/>
+        <v>4728.0886113697561</v>
+      </c>
+      <c r="BZ17" s="6">
+        <f t="shared" si="29"/>
+        <v>4680.8077252560588</v>
+      </c>
+      <c r="CA17" s="6">
+        <f t="shared" si="29"/>
+        <v>4633.9996480034979</v>
+      </c>
+      <c r="CB17" s="6">
+        <f t="shared" si="29"/>
+        <v>4587.6596515234633</v>
+      </c>
+      <c r="CC17" s="6">
+        <f t="shared" si="29"/>
+        <v>4541.783055008229</v>
+      </c>
+      <c r="CD17" s="6">
+        <f t="shared" si="29"/>
+        <v>4496.3652244581463</v>
+      </c>
+      <c r="CE17" s="6">
+        <f t="shared" si="29"/>
+        <v>4451.4015722135646</v>
+      </c>
+      <c r="CF17" s="6">
+        <f t="shared" si="29"/>
+        <v>4406.8875564914288</v>
+      </c>
+      <c r="CG17" s="6">
+        <f t="shared" si="29"/>
+        <v>4362.8186809265144</v>
+      </c>
+      <c r="CH17" s="6">
+        <f t="shared" si="29"/>
+        <v>4319.1904941172488</v>
+      </c>
+      <c r="CI17" s="6">
+        <f t="shared" si="29"/>
+        <v>4275.9985891760762</v>
+      </c>
+      <c r="CJ17" s="6">
+        <f t="shared" si="29"/>
+        <v>4233.2386032843151</v>
+      </c>
+      <c r="CK17" s="6">
+        <f t="shared" si="29"/>
+        <v>4190.9062172514723</v>
+      </c>
+      <c r="CL17" s="6">
+        <f t="shared" si="29"/>
+        <v>4148.9971550789578</v>
+      </c>
+      <c r="CM17" s="6">
+        <f t="shared" si="29"/>
+        <v>4107.5071835281678</v>
+      </c>
+      <c r="CN17" s="6">
+        <f t="shared" si="29"/>
+        <v>4066.4321116928863</v>
+      </c>
+      <c r="CO17" s="6">
+        <f t="shared" si="29"/>
+        <v>4025.7677905759574</v>
+      </c>
+      <c r="CP17" s="6">
+        <f t="shared" si="29"/>
+        <v>3985.5101126701979</v>
+      </c>
+      <c r="CQ17" s="6">
+        <f t="shared" si="29"/>
+        <v>3945.6550115434961</v>
+      </c>
+      <c r="CR17" s="6">
+        <f t="shared" si="29"/>
+        <v>3906.1984614280609</v>
+      </c>
+      <c r="CS17" s="6">
+        <f t="shared" si="29"/>
+        <v>3867.1364768137801</v>
+      </c>
+      <c r="CT17" s="6">
+        <f t="shared" si="29"/>
+        <v>3828.4651120456424</v>
+      </c>
+      <c r="CU17" s="6">
+        <f t="shared" si="29"/>
+        <v>3790.1804609251858</v>
+      </c>
+      <c r="CV17" s="6">
+        <f t="shared" si="29"/>
+        <v>3752.2786563159339</v>
+      </c>
+      <c r="CW17" s="6">
+        <f t="shared" si="29"/>
+        <v>3714.7558697527743</v>
+      </c>
+      <c r="CX17" s="6">
+        <f t="shared" si="29"/>
+        <v>3677.6083110552463</v>
+      </c>
+      <c r="CY17" s="6">
+        <f t="shared" si="29"/>
+        <v>3640.8322279446938</v>
+      </c>
+      <c r="CZ17" s="6">
+        <f t="shared" si="29"/>
+        <v>3604.4239056652468</v>
+      </c>
+      <c r="DA17" s="6">
+        <f t="shared" si="29"/>
+        <v>3568.3796666085941</v>
+      </c>
+      <c r="DB17" s="6">
+        <f t="shared" si="29"/>
+        <v>3532.6958699425081</v>
+      </c>
+      <c r="DC17" s="6">
+        <f t="shared" si="29"/>
+        <v>3497.3689112430829</v>
+      </c>
+      <c r="DD17" s="6">
+        <f t="shared" si="29"/>
+        <v>3462.3952221306522</v>
+      </c>
+      <c r="DE17" s="6">
+        <f t="shared" si="29"/>
+        <v>3427.7712699093458</v>
+      </c>
+      <c r="DF17" s="6">
+        <f t="shared" si="29"/>
+        <v>3393.4935572102522</v>
+      </c>
+      <c r="DG17" s="6">
+        <f t="shared" si="29"/>
+        <v>3359.5586216381498</v>
+      </c>
+      <c r="DH17" s="6">
+        <f t="shared" ref="DH17:EP17" si="30">DG17*(1+$AX$22)</f>
+        <v>3325.9630354217684</v>
+      </c>
+      <c r="DI17" s="6">
         <f t="shared" si="30"/>
-        <v>6234.0787508047006</v>
-      </c>
-      <c r="AX17" s="6">
+        <v>3292.7034050675506</v>
+      </c>
+      <c r="DJ17" s="6">
         <f t="shared" si="30"/>
-        <v>6171.7379632966531</v>
-      </c>
-      <c r="AY17" s="6">
+        <v>3259.7763710168751</v>
+      </c>
+      <c r="DK17" s="6">
         <f t="shared" si="30"/>
-        <v>6110.0205836636869</v>
-      </c>
-      <c r="AZ17" s="6">
+        <v>3227.1786073067065</v>
+      </c>
+      <c r="DL17" s="6">
         <f t="shared" si="30"/>
-        <v>6048.9203778270503</v>
-      </c>
-      <c r="BA17" s="6">
+        <v>3194.9068212336392</v>
+      </c>
+      <c r="DM17" s="6">
         <f t="shared" si="30"/>
-        <v>5988.4311740487801</v>
-      </c>
-      <c r="BB17" s="6">
+        <v>3162.9577530213028</v>
+      </c>
+      <c r="DN17" s="6">
         <f t="shared" si="30"/>
-        <v>5928.5468623082925</v>
-      </c>
-      <c r="BC17" s="6">
+        <v>3131.3281754910895</v>
+      </c>
+      <c r="DO17" s="6">
         <f t="shared" si="30"/>
-        <v>5869.2613936852094</v>
-      </c>
-      <c r="BD17" s="6">
+        <v>3100.0148937361787</v>
+      </c>
+      <c r="DP17" s="6">
         <f t="shared" si="30"/>
-        <v>5810.568779748357</v>
-      </c>
-      <c r="BE17" s="6">
+        <v>3069.014744798817</v>
+      </c>
+      <c r="DQ17" s="6">
         <f t="shared" si="30"/>
-        <v>5752.4630919508736</v>
-      </c>
-      <c r="BF17" s="6">
+        <v>3038.3245973508288</v>
+      </c>
+      <c r="DR17" s="6">
         <f t="shared" si="30"/>
-        <v>5694.9384610313646</v>
-      </c>
-      <c r="BG17" s="6">
+        <v>3007.9413513773206</v>
+      </c>
+      <c r="DS17" s="6">
         <f t="shared" si="30"/>
-        <v>5637.9890764210513</v>
-      </c>
-      <c r="BH17" s="6">
+        <v>2977.8619378635476</v>
+      </c>
+      <c r="DT17" s="6">
         <f t="shared" si="30"/>
-        <v>5581.609185656841</v>
-      </c>
-      <c r="BI17" s="6">
+        <v>2948.0833184849121</v>
+      </c>
+      <c r="DU17" s="6">
         <f t="shared" si="30"/>
-        <v>5525.7930938002728</v>
-      </c>
-      <c r="BJ17" s="6">
+        <v>2918.6024853000631</v>
+      </c>
+      <c r="DV17" s="6">
         <f t="shared" si="30"/>
-        <v>5470.5351628622702</v>
-      </c>
-      <c r="BK17" s="6">
+        <v>2889.4164604470625</v>
+      </c>
+      <c r="DW17" s="6">
         <f t="shared" si="30"/>
-        <v>5415.8298112336479</v>
-      </c>
-      <c r="BL17" s="6">
+        <v>2860.522295842592</v>
+      </c>
+      <c r="DX17" s="6">
         <f t="shared" si="30"/>
-        <v>5361.6715131213114</v>
-      </c>
-      <c r="BM17" s="6">
+        <v>2831.9170728841659</v>
+      </c>
+      <c r="DY17" s="6">
         <f t="shared" si="30"/>
-        <v>5308.0547979900985</v>
-      </c>
-      <c r="BN17" s="6">
+        <v>2803.5979021553244</v>
+      </c>
+      <c r="DZ17" s="6">
         <f t="shared" si="30"/>
-        <v>5254.9742500101975</v>
-      </c>
-      <c r="BO17" s="6">
+        <v>2775.561923133771</v>
+      </c>
+      <c r="EA17" s="6">
         <f t="shared" si="30"/>
-        <v>5202.4245075100953</v>
-      </c>
-      <c r="BP17" s="6">
+        <v>2747.8063039024332</v>
+      </c>
+      <c r="EB17" s="6">
         <f t="shared" si="30"/>
-        <v>5150.4002624349941</v>
-      </c>
-      <c r="BQ17" s="6">
+        <v>2720.3282408634091</v>
+      </c>
+      <c r="EC17" s="6">
         <f t="shared" si="30"/>
-        <v>5098.8962598106446</v>
-      </c>
-      <c r="BR17" s="6">
+        <v>2693.124958454775</v>
+      </c>
+      <c r="ED17" s="6">
         <f t="shared" si="30"/>
-        <v>5047.9072972125377</v>
-      </c>
-      <c r="BS17" s="6">
+        <v>2666.1937088702271</v>
+      </c>
+      <c r="EE17" s="6">
         <f t="shared" si="30"/>
-        <v>4997.4282242404124</v>
-      </c>
-      <c r="BT17" s="6">
+        <v>2639.5317717815246</v>
+      </c>
+      <c r="EF17" s="6">
         <f t="shared" si="30"/>
-        <v>4947.4539419980083</v>
-      </c>
-      <c r="BU17" s="6">
+        <v>2613.1364540637092</v>
+      </c>
+      <c r="EG17" s="6">
         <f t="shared" si="30"/>
-        <v>4897.9794025780284</v>
-      </c>
-      <c r="BV17" s="6">
+        <v>2587.005089523072</v>
+      </c>
+      <c r="EH17" s="6">
         <f t="shared" si="30"/>
-        <v>4848.999608552248</v>
-      </c>
-      <c r="BW17" s="6">
+        <v>2561.1350386278414</v>
+      </c>
+      <c r="EI17" s="6">
         <f t="shared" si="30"/>
-        <v>4800.5096124667252</v>
-      </c>
-      <c r="BX17" s="6">
+        <v>2535.5236882415629</v>
+      </c>
+      <c r="EJ17" s="6">
         <f t="shared" si="30"/>
-        <v>4752.5045163420582</v>
-      </c>
-      <c r="BY17" s="6">
+        <v>2510.1684513591472</v>
+      </c>
+      <c r="EK17" s="6">
         <f t="shared" si="30"/>
-        <v>4704.9794711786371</v>
-      </c>
-      <c r="BZ17" s="6">
+        <v>2485.0667668455558</v>
+      </c>
+      <c r="EL17" s="6">
         <f t="shared" si="30"/>
-        <v>4657.9296764668507</v>
-      </c>
-      <c r="CA17" s="6">
+        <v>2460.2160991771002</v>
+      </c>
+      <c r="EM17" s="6">
         <f t="shared" si="30"/>
-        <v>4611.3503797021822</v>
-      </c>
-      <c r="CB17" s="6">
+        <v>2435.6139381853291</v>
+      </c>
+      <c r="EN17" s="6">
         <f t="shared" si="30"/>
-        <v>4565.2368759051606</v>
-      </c>
-      <c r="CC17" s="6">
+        <v>2411.2577988034759</v>
+      </c>
+      <c r="EO17" s="6">
         <f t="shared" si="30"/>
-        <v>4519.584507146109</v>
-      </c>
-      <c r="CD17" s="6">
+        <v>2387.145220815441</v>
+      </c>
+      <c r="EP17" s="6">
         <f t="shared" si="30"/>
-        <v>4474.388662074648</v>
-      </c>
-      <c r="CE17" s="6">
-        <f t="shared" si="30"/>
-        <v>4429.6447754539013</v>
-      </c>
-      <c r="CF17" s="6">
-        <f t="shared" si="30"/>
-        <v>4385.348327699362</v>
-      </c>
-      <c r="CG17" s="6">
-        <f t="shared" si="30"/>
-        <v>4341.4948444223683</v>
-      </c>
-      <c r="CH17" s="6">
-        <f t="shared" si="30"/>
-        <v>4298.0798959781441</v>
-      </c>
-      <c r="CI17" s="6">
-        <f t="shared" si="30"/>
-        <v>4255.099097018363</v>
-      </c>
-      <c r="CJ17" s="6">
-        <f t="shared" si="30"/>
-        <v>4212.5481060481789</v>
-      </c>
-      <c r="CK17" s="6">
-        <f t="shared" si="30"/>
-        <v>4170.4226249876974</v>
-      </c>
-      <c r="CL17" s="6">
-        <f t="shared" si="30"/>
-        <v>4128.7183987378203</v>
-      </c>
-      <c r="CM17" s="6">
-        <f t="shared" si="30"/>
-        <v>4087.431214750442</v>
-      </c>
-      <c r="CN17" s="6">
-        <f t="shared" si="30"/>
-        <v>4046.5569026029375</v>
-      </c>
-      <c r="CO17" s="6">
-        <f t="shared" si="30"/>
-        <v>4006.0913335769083</v>
-      </c>
-      <c r="CP17" s="6">
-        <f t="shared" si="30"/>
-        <v>3966.0304202411389</v>
-      </c>
-      <c r="CQ17" s="6">
-        <f t="shared" si="30"/>
-        <v>3926.3701160387277</v>
-      </c>
-      <c r="CR17" s="6">
-        <f t="shared" si="30"/>
-        <v>3887.1064148783403</v>
-      </c>
-      <c r="CS17" s="6">
-        <f t="shared" si="30"/>
-        <v>3848.235350729557</v>
-      </c>
-      <c r="CT17" s="6">
-        <f t="shared" si="30"/>
-        <v>3809.7529972222615</v>
-      </c>
-      <c r="CU17" s="6">
-        <f t="shared" si="30"/>
-        <v>3771.6554672500388</v>
-      </c>
-      <c r="CV17" s="6">
-        <f t="shared" si="30"/>
-        <v>3733.9389125775383</v>
-      </c>
-      <c r="CW17" s="6">
-        <f t="shared" si="30"/>
-        <v>3696.5995234517627</v>
-      </c>
-      <c r="CX17" s="6">
-        <f t="shared" si="30"/>
-        <v>3659.6335282172449</v>
-      </c>
-      <c r="CY17" s="6">
-        <f t="shared" si="30"/>
-        <v>3623.0371929350727</v>
-      </c>
-      <c r="CZ17" s="6">
-        <f t="shared" si="30"/>
-        <v>3586.8068210057218</v>
-      </c>
-      <c r="DA17" s="6">
-        <f t="shared" si="30"/>
-        <v>3550.9387527956646</v>
-      </c>
-      <c r="DB17" s="6">
-        <f t="shared" si="30"/>
-        <v>3515.4293652677079</v>
-      </c>
-      <c r="DC17" s="6">
-        <f t="shared" si="30"/>
-        <v>3480.2750716150308</v>
-      </c>
-      <c r="DD17" s="6">
-        <f t="shared" si="30"/>
-        <v>3445.4723208988803</v>
-      </c>
-      <c r="DE17" s="6">
-        <f t="shared" si="30"/>
-        <v>3411.0175976898913</v>
-      </c>
-      <c r="DF17" s="6">
-        <f t="shared" si="30"/>
-        <v>3376.9074217129923</v>
-      </c>
-      <c r="DG17" s="6">
-        <f t="shared" si="30"/>
-        <v>3343.1383474958625</v>
-      </c>
-      <c r="DH17" s="6">
-        <f t="shared" ref="DH17:EP17" si="31">DG17*(1+$AX$22)</f>
-        <v>3309.7069640209038</v>
-      </c>
-      <c r="DI17" s="6">
-        <f t="shared" si="31"/>
-        <v>3276.6098943806946</v>
-      </c>
-      <c r="DJ17" s="6">
-        <f t="shared" si="31"/>
-        <v>3243.8437954368878</v>
-      </c>
-      <c r="DK17" s="6">
-        <f t="shared" si="31"/>
-        <v>3211.4053574825189</v>
-      </c>
-      <c r="DL17" s="6">
-        <f t="shared" si="31"/>
-        <v>3179.2913039076939</v>
-      </c>
-      <c r="DM17" s="6">
-        <f t="shared" si="31"/>
-        <v>3147.4983908686168</v>
-      </c>
-      <c r="DN17" s="6">
-        <f t="shared" si="31"/>
-        <v>3116.0234069599305</v>
-      </c>
-      <c r="DO17" s="6">
-        <f t="shared" si="31"/>
-        <v>3084.863172890331</v>
-      </c>
-      <c r="DP17" s="6">
-        <f t="shared" si="31"/>
-        <v>3054.0145411614276</v>
-      </c>
-      <c r="DQ17" s="6">
-        <f t="shared" si="31"/>
-        <v>3023.4743957498131</v>
-      </c>
-      <c r="DR17" s="6">
-        <f t="shared" si="31"/>
-        <v>2993.2396517923148</v>
-      </c>
-      <c r="DS17" s="6">
-        <f t="shared" si="31"/>
-        <v>2963.3072552743915</v>
-      </c>
-      <c r="DT17" s="6">
-        <f t="shared" si="31"/>
-        <v>2933.6741827216474</v>
-      </c>
-      <c r="DU17" s="6">
-        <f t="shared" si="31"/>
-        <v>2904.337440894431</v>
-      </c>
-      <c r="DV17" s="6">
-        <f t="shared" si="31"/>
-        <v>2875.2940664854868</v>
-      </c>
-      <c r="DW17" s="6">
-        <f t="shared" si="31"/>
-        <v>2846.5411258206318</v>
-      </c>
-      <c r="DX17" s="6">
-        <f t="shared" si="31"/>
-        <v>2818.0757145624257</v>
-      </c>
-      <c r="DY17" s="6">
-        <f t="shared" si="31"/>
-        <v>2789.8949574168014</v>
-      </c>
-      <c r="DZ17" s="6">
-        <f t="shared" si="31"/>
-        <v>2761.9960078426334</v>
-      </c>
-      <c r="EA17" s="6">
-        <f t="shared" si="31"/>
-        <v>2734.3760477642072</v>
-      </c>
-      <c r="EB17" s="6">
-        <f t="shared" si="31"/>
-        <v>2707.032287286565</v>
-      </c>
-      <c r="EC17" s="6">
-        <f t="shared" si="31"/>
-        <v>2679.9619644136992</v>
-      </c>
-      <c r="ED17" s="6">
-        <f t="shared" si="31"/>
-        <v>2653.162344769562</v>
-      </c>
-      <c r="EE17" s="6">
-        <f t="shared" si="31"/>
-        <v>2626.6307213218665</v>
-      </c>
-      <c r="EF17" s="6">
-        <f t="shared" si="31"/>
-        <v>2600.3644141086479</v>
-      </c>
-      <c r="EG17" s="6">
-        <f t="shared" si="31"/>
-        <v>2574.3607699675613</v>
-      </c>
-      <c r="EH17" s="6">
-        <f t="shared" si="31"/>
-        <v>2548.6171622678858</v>
-      </c>
-      <c r="EI17" s="6">
-        <f t="shared" si="31"/>
-        <v>2523.130990645207</v>
-      </c>
-      <c r="EJ17" s="6">
-        <f t="shared" si="31"/>
-        <v>2497.8996807387548</v>
-      </c>
-      <c r="EK17" s="6">
-        <f t="shared" si="31"/>
-        <v>2472.9206839313674</v>
-      </c>
-      <c r="EL17" s="6">
-        <f t="shared" si="31"/>
-        <v>2448.1914770920539</v>
-      </c>
-      <c r="EM17" s="6">
-        <f t="shared" si="31"/>
-        <v>2423.7095623211335</v>
-      </c>
-      <c r="EN17" s="6">
-        <f t="shared" si="31"/>
-        <v>2399.4724666979223</v>
-      </c>
-      <c r="EO17" s="6">
-        <f t="shared" si="31"/>
-        <v>2375.4777420309429</v>
-      </c>
-      <c r="EP17" s="6">
-        <f t="shared" si="31"/>
-        <v>2351.7229646106334</v>
+        <v>2363.2737686072865</v>
       </c>
     </row>
     <row r="18" spans="1:146" x14ac:dyDescent="0.3">
@@ -3658,17 +3657,19 @@
         <v>989.2</v>
       </c>
       <c r="W18" s="1">
-        <f t="shared" ref="W18" si="32">989.2</f>
+        <f t="shared" ref="W18" si="31">989.2</f>
         <v>989.2</v>
       </c>
       <c r="X18" s="1">
         <v>969</v>
       </c>
       <c r="Y18" s="1">
-        <v>969</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="Z18" s="1">
-        <v>969</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AC18" s="1">
         <v>1064</v>
@@ -3689,52 +3690,52 @@
         <v>1064</v>
       </c>
       <c r="AI18" s="1">
-        <f t="shared" ref="AI18:AT18" si="33">1002.5</f>
+        <f t="shared" ref="AI18:AT18" si="32">1002.5</f>
         <v>1002.5</v>
       </c>
       <c r="AJ18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AK18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AL18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AM18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AN18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AO18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AP18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AQ18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AR18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AS18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
       <c r="AT18" s="1">
-        <f t="shared" si="33"/>
-        <v>1002.5</v>
+        <f>935.7</f>
+        <v>935.7</v>
       </c>
     </row>
     <row r="19" spans="1:146" x14ac:dyDescent="0.3">
@@ -3742,172 +3743,172 @@
         <v>36</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:S19" si="34">C17/C18</f>
+        <f t="shared" ref="C19:S19" si="33">C17/C18</f>
         <v>7.3748902546093065E-2</v>
       </c>
       <c r="D19" s="5">
+        <f t="shared" si="33"/>
+        <v>1.3432835820895523</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.89640035118525019</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="33"/>
+        <v>1.3757682177348551</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.96312554872695344</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="33"/>
+        <v>1.0395083406496928</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.95434591747146624</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.7032484635645303</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.44688323090430204</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="33"/>
+        <v>-0.29938542581211591</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" si="33"/>
+        <v>1.1676909569798068</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.80860403863037755</v>
+      </c>
+      <c r="O19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.70416297608503098</v>
+      </c>
+      <c r="P19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.90342405618964006</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.89552238805970152</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="33"/>
+        <v>1.3017641597028784</v>
+      </c>
+      <c r="S19" s="5">
+        <f t="shared" si="33"/>
+        <v>0.83458646616541354</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" ref="T19:V19" si="34">T17/T18</f>
+        <v>1.1033943069549057</v>
+      </c>
+      <c r="U19" s="5">
         <f t="shared" si="34"/>
-        <v>1.3432835820895523</v>
-      </c>
-      <c r="E19" s="5">
+        <v>1.0074812967581048</v>
+      </c>
+      <c r="V19" s="5">
         <f t="shared" si="34"/>
-        <v>0.89640035118525019</v>
-      </c>
-      <c r="F19" s="5">
-        <f t="shared" si="34"/>
-        <v>1.3757682177348551</v>
-      </c>
-      <c r="G19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.96312554872695344</v>
-      </c>
-      <c r="H19" s="5">
-        <f t="shared" si="34"/>
-        <v>1.0395083406496928</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.95434591747146624</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.7032484635645303</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.44688323090430204</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="34"/>
-        <v>-0.29938542581211591</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" si="34"/>
-        <v>1.1676909569798068</v>
-      </c>
-      <c r="N19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.80860403863037755</v>
-      </c>
-      <c r="O19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.70416297608503098</v>
-      </c>
-      <c r="P19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.90342405618964006</v>
-      </c>
-      <c r="Q19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.89552238805970152</v>
-      </c>
-      <c r="R19" s="5">
-        <f t="shared" si="34"/>
-        <v>1.3017641597028784</v>
-      </c>
-      <c r="S19" s="5">
-        <f t="shared" si="34"/>
-        <v>0.83458646616541354</v>
-      </c>
-      <c r="T19" s="5">
-        <f t="shared" ref="T19:V19" si="35">T17/T18</f>
-        <v>1.1033943069549057</v>
-      </c>
-      <c r="U19" s="5">
+        <v>1.1332389809947432</v>
+      </c>
+      <c r="W19" s="5">
+        <f t="shared" ref="W19:Z19" si="35">W17/W18</f>
+        <v>1.301051354630004</v>
+      </c>
+      <c r="X19" s="5">
         <f t="shared" si="35"/>
-        <v>1.0074812967581048</v>
-      </c>
-      <c r="V19" s="5">
+        <v>1.3013415892672859</v>
+      </c>
+      <c r="Y19" s="5">
         <f t="shared" si="35"/>
-        <v>1.1332389809947432</v>
-      </c>
-      <c r="W19" s="5">
-        <f t="shared" ref="W19:Z19" si="36">W17/W18</f>
-        <v>1.301051354630004</v>
-      </c>
-      <c r="X19" s="5">
+        <v>1.3337608207758895</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="35"/>
+        <v>1.2389564176552312</v>
+      </c>
+      <c r="AC19" s="5">
+        <f t="shared" ref="AC19:AJ19" si="36">AC17/AC18</f>
+        <v>1.9332706766917294</v>
+      </c>
+      <c r="AD19" s="5">
         <f t="shared" si="36"/>
-        <v>1.3013415892672859</v>
-      </c>
-      <c r="Y19" s="5">
+        <v>2.3110902255639099</v>
+      </c>
+      <c r="AE19" s="5">
         <f t="shared" si="36"/>
-        <v>1.186310835913313</v>
-      </c>
-      <c r="Z19" s="5">
+        <v>3.9492481203007519</v>
+      </c>
+      <c r="AF19" s="5">
         <f t="shared" si="36"/>
-        <v>1.2916664602683179</v>
-      </c>
-      <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AJ19" si="37">AC17/AC18</f>
-        <v>1.9332706766917294</v>
-      </c>
-      <c r="AD19" s="5">
+        <v>3.9182330827067671</v>
+      </c>
+      <c r="AG19" s="5">
+        <f t="shared" si="36"/>
+        <v>2.2734962406015038</v>
+      </c>
+      <c r="AH19" s="5">
+        <f t="shared" si="36"/>
+        <v>3.9906015037593985</v>
+      </c>
+      <c r="AI19" s="5">
+        <f t="shared" si="36"/>
+        <v>4.1366583541147133</v>
+      </c>
+      <c r="AJ19" s="5">
+        <f t="shared" si="36"/>
+        <v>5.2958122475152356</v>
+      </c>
+      <c r="AK19" s="5">
+        <f t="shared" ref="AK19:AT19" si="37">AK17/AK18</f>
+        <v>5.7226670531153161</v>
+      </c>
+      <c r="AL19" s="5">
         <f t="shared" si="37"/>
-        <v>2.3110902255639099</v>
-      </c>
-      <c r="AE19" s="5">
+        <v>6.1498442763107839</v>
+      </c>
+      <c r="AM19" s="5">
         <f t="shared" si="37"/>
-        <v>3.9492481203007519</v>
-      </c>
-      <c r="AF19" s="5">
+        <v>6.320628737461667</v>
+      </c>
+      <c r="AN19" s="5">
         <f t="shared" si="37"/>
-        <v>3.9182330827067671</v>
-      </c>
-      <c r="AG19" s="5">
+        <v>6.4952896640941091</v>
+      </c>
+      <c r="AO19" s="5">
         <f t="shared" si="37"/>
-        <v>2.2734962406015038</v>
-      </c>
-      <c r="AH19" s="5">
+        <v>6.5610975356201653</v>
+      </c>
+      <c r="AP19" s="5">
         <f t="shared" si="37"/>
-        <v>3.9906015037593985</v>
-      </c>
-      <c r="AI19" s="5">
+        <v>6.6275634858614785</v>
+      </c>
+      <c r="AQ19" s="5">
         <f t="shared" si="37"/>
-        <v>4.1366583541147133</v>
-      </c>
-      <c r="AJ19" s="5">
+        <v>6.6946940956052057</v>
+      </c>
+      <c r="AR19" s="5">
         <f t="shared" si="37"/>
-        <v>4.9368179551122235</v>
-      </c>
-      <c r="AK19" s="5">
-        <f t="shared" ref="AK19:AT19" si="38">AK17/AK18</f>
-        <v>5.2943437566084794</v>
-      </c>
-      <c r="AL19" s="5">
-        <f t="shared" si="38"/>
-        <v>5.7135147274214466</v>
-      </c>
-      <c r="AM19" s="5">
-        <f t="shared" si="38"/>
-        <v>5.871384911541945</v>
-      </c>
-      <c r="AN19" s="5">
-        <f t="shared" si="38"/>
-        <v>6.0328325381408252</v>
-      </c>
-      <c r="AO19" s="5">
-        <f t="shared" si="38"/>
-        <v>6.0939588685097634</v>
-      </c>
-      <c r="AP19" s="5">
-        <f t="shared" si="38"/>
-        <v>6.1556964621823917</v>
-      </c>
-      <c r="AQ19" s="5">
-        <f t="shared" si="38"/>
-        <v>6.2180514317917481</v>
-      </c>
-      <c r="AR19" s="5">
-        <f t="shared" si="38"/>
-        <v>6.2810299510971968</v>
+        <v>6.7624960114463706</v>
       </c>
       <c r="AS19" s="5">
-        <f t="shared" si="38"/>
-        <v>6.3446382555956999</v>
+        <f t="shared" si="37"/>
+        <v>6.8309759464459479</v>
       </c>
       <c r="AT19" s="5">
-        <f t="shared" si="38"/>
-        <v>6.4088826431391892</v>
+        <f t="shared" si="37"/>
+        <v>6.900140680795519</v>
       </c>
     </row>
     <row r="21" spans="1:146" x14ac:dyDescent="0.3">
@@ -3923,79 +3924,79 @@
         <v>0.30640970116933741</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" ref="H21:V21" si="39">H3/D3-1</f>
+        <f t="shared" ref="H21:V21" si="38">H3/D3-1</f>
         <v>0.18570613951720216</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0.13244183916468222</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0.13113145846958796</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>7.458975634012921E-2</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>9.105482526450781E-2</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0.10740860562924626</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>6.7215958369470918E-2</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>8.5917013728212144E-2</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>7.0672935645019086E-2</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>8.3552439380660148E-2</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>8.7091968034674228E-2</v>
       </c>
       <c r="S21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>9.3607954545454453E-2</v>
       </c>
       <c r="T21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>8.2063949499108002E-2</v>
       </c>
       <c r="U21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>5.7832299811269916E-2</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>4.2362322452030865E-2</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" ref="W21" si="40">W3/S3-1</f>
+        <f t="shared" ref="W21" si="39">W3/S3-1</f>
         <v>1.1949603844655154E-2</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" ref="X21" si="41">X3/T3-1</f>
+        <f t="shared" ref="X21" si="40">X3/T3-1</f>
         <v>5.1109701965757814E-2</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" ref="Y21" si="42">Y3/U3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="Y21" si="41">Y3/U3-1</f>
+        <v>7.2639225181598155E-2</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" ref="Z21" si="43">Z3/V3-1</f>
+        <f t="shared" ref="Z21" si="42">Z3/V3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA21" s="8"/>
@@ -4005,67 +4006,67 @@
         <v>0.15021681444566704</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AT21" si="44">AE3/AD3-1</f>
+        <f t="shared" ref="AE21:AT21" si="43">AE3/AD3-1</f>
         <v>0.20717983344586988</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0.18257667567819524</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8.4624177210200546E-2</v>
       </c>
       <c r="AH21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8.1873682680427384E-2</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>6.8052803063383793E-2</v>
       </c>
       <c r="AJ21" s="8">
-        <f t="shared" si="44"/>
-        <v>2.3134257948863146E-2</v>
+        <f t="shared" si="43"/>
+        <v>3.6124791647010879E-2</v>
       </c>
       <c r="AK21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT21" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4074,19 +4075,19 @@
         <v>50</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:F22" si="45">C8/C3</f>
+        <f t="shared" ref="C22:F22" si="44">C8/C3</f>
         <v>0.40905153746210482</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>0.48564911613761641</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>0.4843377908041766</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>0.47629169391759318</v>
       </c>
       <c r="G22" s="8">
@@ -4094,153 +4095,153 @@
         <v>0.4917951268025858</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" ref="H22:V22" si="46">H8/H3</f>
+        <f t="shared" ref="H22:V22" si="45">H8/H3</f>
         <v>0.48477075985892915</v>
       </c>
       <c r="I22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.46036881268197993</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.4457935819601041</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.4261915779731606</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.40816926241551571</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.43558282208588955</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.42394690505214683</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.40156249999999999</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.39193083573487031</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.39026691830682125</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.39957637677547969</v>
+      </c>
+      <c r="S22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.39057020392258734</v>
+      </c>
+      <c r="T22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.40228281547241596</v>
+      </c>
+      <c r="U22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.41123996431757359</v>
+      </c>
+      <c r="V22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.41644752569925891</v>
+      </c>
+      <c r="W22" s="8">
+        <f t="shared" ref="W22:Z22" si="46">W8/W3</f>
+        <v>0.42587601078167114</v>
+      </c>
+      <c r="X22" s="8">
         <f t="shared" si="46"/>
-        <v>0.46036881268197993</v>
-      </c>
-      <c r="J22" s="8">
+        <v>0.41397200772200771</v>
+      </c>
+      <c r="Y22" s="8">
         <f t="shared" si="46"/>
-        <v>0.4457935819601041</v>
-      </c>
-      <c r="K22" s="8">
+        <v>0.40679577046453608</v>
+      </c>
+      <c r="Z22" s="8">
         <f t="shared" si="46"/>
-        <v>0.4261915779731606</v>
-      </c>
-      <c r="L22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.40816926241551571</v>
-      </c>
-      <c r="M22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.43558282208588955</v>
-      </c>
-      <c r="N22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.42394690505214683</v>
-      </c>
-      <c r="O22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.40156249999999999</v>
-      </c>
-      <c r="P22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.39193083573487031</v>
-      </c>
-      <c r="Q22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.39026691830682125</v>
-      </c>
-      <c r="R22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.39957637677547969</v>
-      </c>
-      <c r="S22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.39057020392258734</v>
-      </c>
-      <c r="T22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.40228281547241596</v>
-      </c>
-      <c r="U22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.41123996431757359</v>
-      </c>
-      <c r="V22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.41644752569925891</v>
-      </c>
-      <c r="W22" s="8">
-        <f t="shared" ref="W22:Z22" si="47">W8/W3</f>
-        <v>0.42587601078167114</v>
-      </c>
-      <c r="X22" s="8">
-        <f t="shared" si="47"/>
-        <v>0.41397200772200771</v>
-      </c>
-      <c r="Y22" s="8">
-        <f t="shared" si="47"/>
-        <v>0.41</v>
-      </c>
-      <c r="Z22" s="8">
-        <f t="shared" si="47"/>
         <v>0.42</v>
       </c>
       <c r="AA22" s="8"/>
       <c r="AC22" s="8">
-        <f t="shared" ref="AC22:AD22" si="48">AC8/AC3</f>
+        <f t="shared" ref="AC22:AD22" si="47">AC8/AC3</f>
         <v>0.46527732832826352</v>
       </c>
       <c r="AD22" s="8">
+        <f t="shared" si="47"/>
+        <v>0.44941480981318926</v>
+      </c>
+      <c r="AE22" s="8">
+        <f t="shared" ref="AE22:AT22" si="48">AE8/AE3</f>
+        <v>0.46616015661415122</v>
+      </c>
+      <c r="AF22" s="8">
         <f t="shared" si="48"/>
-        <v>0.44941480981318926</v>
-      </c>
-      <c r="AE22" s="8">
-        <f t="shared" ref="AE22:AT22" si="49">AE8/AE3</f>
-        <v>0.46616015661415122</v>
-      </c>
-      <c r="AF22" s="8">
-        <f t="shared" si="49"/>
         <v>0.46986717117969334</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.42346827531070574</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.39585502670383932</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.40538415573796271</v>
       </c>
       <c r="AJ22" s="8">
-        <f t="shared" si="49"/>
-        <v>0.41741123058101731</v>
+        <f t="shared" si="48"/>
+        <v>0.41649969070281195</v>
       </c>
       <c r="AK22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.43</v>
       </c>
       <c r="AL22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.44</v>
       </c>
       <c r="AM22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.44</v>
       </c>
       <c r="AN22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.44</v>
       </c>
       <c r="AO22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.44</v>
       </c>
       <c r="AP22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.44</v>
       </c>
       <c r="AQ22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.44</v>
       </c>
       <c r="AR22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.44</v>
       </c>
       <c r="AS22" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0.44</v>
       </c>
       <c r="AT22" s="8">
-        <f t="shared" si="49"/>
-        <v>0.44000000000000006</v>
+        <f t="shared" si="48"/>
+        <v>0.44</v>
       </c>
       <c r="AW22" t="s">
         <v>53</v>
@@ -4254,19 +4255,19 @@
         <v>47</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" ref="C23:F23" si="50">C9/C3</f>
+        <f t="shared" ref="C23:F23" si="49">C9/C3</f>
         <v>8.0337808575140751E-2</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>7.8692263828169545E-2</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>8.6279538376992121E-2</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>9.8920863309352514E-2</v>
       </c>
       <c r="G23" s="8">
@@ -4274,152 +4275,152 @@
         <v>9.978451848168407E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" ref="H23:V23" si="51">H9/H3</f>
+        <f t="shared" ref="H23:V23" si="50">H9/H3</f>
         <v>0.10067329272202628</v>
       </c>
       <c r="I23" s="8">
+        <f t="shared" si="50"/>
+        <v>8.8806211582012295E-2</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="50"/>
+        <v>9.6270598438855159E-2</v>
+      </c>
+      <c r="K23" s="8">
+        <f t="shared" si="50"/>
+        <v>9.1624248033317909E-2</v>
+      </c>
+      <c r="L23" s="8">
+        <f t="shared" si="50"/>
+        <v>8.7422862180429037E-2</v>
+      </c>
+      <c r="M23" s="8">
+        <f t="shared" si="50"/>
+        <v>7.9462459830557997E-2</v>
+      </c>
+      <c r="N23" s="8">
+        <f t="shared" si="50"/>
+        <v>7.0973858864960049E-2</v>
+      </c>
+      <c r="O23" s="8">
+        <f t="shared" si="50"/>
+        <v>6.1931818181818185E-2</v>
+      </c>
+      <c r="P23" s="8">
+        <f t="shared" si="50"/>
+        <v>6.3812268423219437E-2</v>
+      </c>
+      <c r="Q23" s="8">
+        <f t="shared" si="50"/>
+        <v>5.9584793744944728E-2</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="50"/>
+        <v>5.8061300772489409E-2</v>
+      </c>
+      <c r="S23" s="8">
+        <f t="shared" si="50"/>
+        <v>5.4682426289128457E-2</v>
+      </c>
+      <c r="T23" s="8">
+        <f t="shared" si="50"/>
+        <v>5.6563094483195943E-2</v>
+      </c>
+      <c r="U23" s="8">
+        <f t="shared" si="50"/>
+        <v>6.4738116477634763E-2</v>
+      </c>
+      <c r="V23" s="8">
+        <f t="shared" si="50"/>
+        <v>7.4826679416686595E-2</v>
+      </c>
+      <c r="W23" s="8">
+        <f t="shared" ref="W23:Z23" si="51">W9/W3</f>
+        <v>6.2636375304838912E-2</v>
+      </c>
+      <c r="X23" s="8">
         <f t="shared" si="51"/>
-        <v>8.8806211582012295E-2</v>
-      </c>
-      <c r="J23" s="8">
+        <v>7.0342664092664098E-2</v>
+      </c>
+      <c r="Y23" s="8">
         <f t="shared" si="51"/>
-        <v>9.6270598438855159E-2</v>
-      </c>
-      <c r="K23" s="8">
+        <v>6.1898538671735774E-2</v>
+      </c>
+      <c r="Z23" s="8">
         <f t="shared" si="51"/>
-        <v>9.1624248033317909E-2</v>
-      </c>
-      <c r="L23" s="8">
-        <f t="shared" si="51"/>
-        <v>8.7422862180429037E-2</v>
-      </c>
-      <c r="M23" s="8">
-        <f t="shared" si="51"/>
-        <v>7.9462459830557997E-2</v>
-      </c>
-      <c r="N23" s="8">
-        <f t="shared" si="51"/>
-        <v>7.0973858864960049E-2</v>
-      </c>
-      <c r="O23" s="8">
-        <f t="shared" si="51"/>
-        <v>6.1931818181818185E-2</v>
-      </c>
-      <c r="P23" s="8">
-        <f t="shared" si="51"/>
-        <v>6.3812268423219437E-2</v>
-      </c>
-      <c r="Q23" s="8">
-        <f t="shared" si="51"/>
-        <v>5.9584793744944728E-2</v>
-      </c>
-      <c r="R23" s="8">
-        <f t="shared" si="51"/>
-        <v>5.8061300772489409E-2</v>
-      </c>
-      <c r="S23" s="8">
-        <f t="shared" si="51"/>
-        <v>5.4682426289128457E-2</v>
-      </c>
-      <c r="T23" s="8">
-        <f t="shared" si="51"/>
-        <v>5.6563094483195943E-2</v>
-      </c>
-      <c r="U23" s="8">
-        <f t="shared" si="51"/>
-        <v>6.4738116477634763E-2</v>
-      </c>
-      <c r="V23" s="8">
-        <f t="shared" si="51"/>
-        <v>7.4826679416686595E-2</v>
-      </c>
-      <c r="W23" s="8">
-        <f t="shared" ref="W23:Z23" si="52">W9/W3</f>
-        <v>6.2636375304838912E-2</v>
-      </c>
-      <c r="X23" s="8">
-        <f t="shared" si="52"/>
-        <v>7.0342664092664098E-2</v>
-      </c>
-      <c r="Y23" s="8">
-        <f t="shared" si="52"/>
-        <v>0.06</v>
-      </c>
-      <c r="Z23" s="8">
-        <f t="shared" si="52"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="AA23" s="8"/>
       <c r="AC23" s="8">
-        <f t="shared" ref="AC23:AD23" si="53">AC9/AC3</f>
+        <f t="shared" ref="AC23:AD23" si="52">AC9/AC3</f>
         <v>8.5043039285483138E-2</v>
       </c>
       <c r="AD23" s="8">
+        <f t="shared" si="52"/>
+        <v>7.8831870357866304E-2</v>
+      </c>
+      <c r="AE23" s="8">
+        <f t="shared" ref="AE23:AT23" si="53">AE9/AE3</f>
+        <v>8.674373077281626E-2</v>
+      </c>
+      <c r="AF23" s="8">
         <f t="shared" si="53"/>
-        <v>7.8831870357866304E-2</v>
-      </c>
-      <c r="AE23" s="8">
-        <f t="shared" ref="AE23:AT23" si="54">AE9/AE3</f>
-        <v>8.674373077281626E-2</v>
-      </c>
-      <c r="AF23" s="8">
-        <f t="shared" si="54"/>
         <v>9.6369871112687716E-2</v>
       </c>
       <c r="AG23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>8.2019042081546631E-2</v>
       </c>
       <c r="AH23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>6.0763830573376774E-2</v>
       </c>
       <c r="AI23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>6.2930465138220593E-2</v>
       </c>
       <c r="AJ23" s="8">
-        <f t="shared" si="54"/>
-        <v>6.5863552252202404E-2</v>
+        <f t="shared" si="53"/>
+        <v>6.8839804696582185E-2</v>
       </c>
       <c r="AK23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AL23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AM23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AN23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AO23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AP23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AQ23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AR23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AS23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AT23" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AW23" t="s">
@@ -4442,80 +4443,80 @@
         <v>0.22479338842975216</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" ref="H24:V24" si="55">H10/D10-1</f>
+        <f t="shared" ref="H24:V24" si="54">H10/D10-1</f>
         <v>0.1822503961965134</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0.12017804154302669</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>8.7431693989071135E-2</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>9.986504723346834E-2</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>9.2493297587131318E-2</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>6.0927152317880706E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>3.2663316582914659E-2</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>-0.11533742331288344</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>-8.8343558282208634E-2</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>-7.7403245942571752E-2</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>-6.326034063260344E-2</v>
       </c>
       <c r="S24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>2.9126213592232997E-2</v>
       </c>
       <c r="T24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>-3.3647375504710642E-2</v>
       </c>
       <c r="U24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>9.4722598105547728E-3</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>3.8961038961038419E-3</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" ref="W24:W25" si="56">W10/S10-1</f>
+        <f t="shared" ref="W24:W25" si="55">W10/S10-1</f>
         <v>-1.4824797843665749E-2</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" ref="X24:X25" si="57">X10/T10-1</f>
+        <f t="shared" ref="X24:X25" si="56">X10/T10-1</f>
         <v>6.8245125348189495E-2</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" ref="Y24:Y25" si="58">Y10/U10-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="Y24:Y25" si="57">Y10/U10-1</f>
+        <v>7.3726541554959724E-2</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" ref="Z24:Z25" si="59">Z10/V10-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="Z24:Z25" si="58">Z10/V10-1</f>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AA24" s="8"/>
       <c r="AC24" s="8"/>
@@ -4524,67 +4525,67 @@
         <v>0.1387220098306936</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" ref="AE24:AT24" si="60">AE10/AD10-1</f>
+        <f t="shared" ref="AE24:AT24" si="59">AE10/AD10-1</f>
         <v>0.26714628297362109</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>0.14988644965934905</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>7.0770243581303571E-2</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>-8.6074392868121685E-2</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>2.0181634712410634E-3</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" si="60"/>
-        <v>2.5367573011077615E-2</v>
+        <f t="shared" si="59"/>
+        <v>4.419268210809002E-2</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AL24" s="8">
+        <f t="shared" si="59"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL24" s="8">
-        <f t="shared" si="60"/>
+      <c r="AM24" s="8">
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM24" s="8">
-        <f t="shared" si="60"/>
+      <c r="AN24" s="8">
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN24" s="8">
-        <f t="shared" si="60"/>
+      <c r="AO24" s="8">
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AO24" s="8">
-        <f t="shared" si="60"/>
+      <c r="AP24" s="8">
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP24" s="8">
-        <f t="shared" si="60"/>
+      <c r="AQ24" s="8">
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ24" s="8">
-        <f t="shared" si="60"/>
+      <c r="AR24" s="8">
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR24" s="8">
-        <f t="shared" si="60"/>
+      <c r="AS24" s="8">
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS24" s="8">
-        <f t="shared" si="60"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AT24" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW24" t="s">
@@ -4592,7 +4593,7 @@
       </c>
       <c r="AX24" s="1">
         <f>NPV(AX23,AJ17:EP17)</f>
-        <v>81749.837904463639</v>
+        <v>82150.990424357398</v>
       </c>
     </row>
     <row r="25" spans="1:146" x14ac:dyDescent="0.3">
@@ -4608,79 +4609,79 @@
         <v>7.8189300411522611E-2</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" ref="H25:V25" si="61">H11/D11-1</f>
+        <f t="shared" ref="H25:V25" si="60">H11/D11-1</f>
         <v>1.953125E-2</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-9.9403578528827197E-3</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>1.7574692442883233E-3</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0.15839694656488557</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-1.5325670498084309E-2</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-7.0281124497991954E-2</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-9.6491228070175405E-2</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-0.16474464579901149</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-4.4747081712062209E-2</v>
       </c>
       <c r="Q25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>9.5032397408207236E-2</v>
       </c>
       <c r="R25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>7.5728155339805925E-2</v>
       </c>
       <c r="S25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-8.4812623274161725E-2</v>
       </c>
       <c r="T25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0.16089613034623218</v>
       </c>
       <c r="U25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>2.3668639053254337E-2</v>
       </c>
       <c r="V25" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>7.2202166064981865E-2</v>
       </c>
       <c r="W25" s="8">
+        <f t="shared" si="55"/>
+        <v>8.405172413793105E-2</v>
+      </c>
+      <c r="X25" s="8">
         <f t="shared" si="56"/>
-        <v>8.405172413793105E-2</v>
-      </c>
-      <c r="X25" s="8">
+        <v>-0.19122807017543864</v>
+      </c>
+      <c r="Y25" s="8">
         <f t="shared" si="57"/>
-        <v>-0.19122807017543864</v>
-      </c>
-      <c r="Y25" s="8">
+        <v>-1.1560693641618491E-2</v>
+      </c>
+      <c r="Z25" s="8">
         <f t="shared" si="58"/>
-        <v>-2.0000000000000018E-2</v>
-      </c>
-      <c r="Z25" s="8">
-        <f t="shared" si="59"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AA25" s="8"/>
@@ -4690,67 +4691,67 @@
         <v>0.11031797534068777</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" ref="AE25:AT25" si="62">AE11/AD11-1</f>
+        <f t="shared" ref="AE25:AT25" si="61">AE11/AD11-1</f>
         <v>0.20981881940385749</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>2.1256038647343045E-2</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>-7.0955534531693676E-3</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>-1.9056693663649371E-2</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>4.2739193783390084E-2</v>
       </c>
       <c r="AJ25" s="8">
-        <f t="shared" si="62"/>
-        <v>-4.2971588262692206E-2</v>
+        <f t="shared" si="61"/>
+        <v>-4.0931532370749979E-2</v>
       </c>
       <c r="AK25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT25" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW25" t="s">
@@ -4758,7 +4759,7 @@
       </c>
       <c r="AX25" s="1">
         <f>Main!D8</f>
-        <v>2357</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="26" spans="1:146" x14ac:dyDescent="0.3">
@@ -4766,19 +4767,19 @@
         <v>51</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" ref="C26:F26" si="63">C13/C3</f>
+        <f t="shared" ref="C26:F26" si="62">C13/C3</f>
         <v>8.6184495452576879E-2</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>0.18076411328644745</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>0.17897050741894119</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>0.15745585349901897</v>
       </c>
       <c r="G26" s="8">
@@ -4786,160 +4787,160 @@
         <v>0.17271672468092159</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:V26" si="64">H13/H3</f>
+        <f t="shared" ref="H26:V26" si="63">H13/H3</f>
         <v>0.18066688041038795</v>
       </c>
       <c r="I26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.16871562601099968</v>
+      </c>
+      <c r="J26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.15177797051170858</v>
+      </c>
+      <c r="K26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.10967144840351689</v>
+      </c>
+      <c r="L26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.11225389362327358</v>
+      </c>
+      <c r="M26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.16330704060765411</v>
+      </c>
+      <c r="N26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.1684951916565082</v>
+      </c>
+      <c r="O26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.14190340909090909</v>
+      </c>
+      <c r="P26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.15548236585700562</v>
+      </c>
+      <c r="Q26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.15745483957940146</v>
+      </c>
+      <c r="R26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.21530027410914529</v>
+      </c>
+      <c r="S26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.15170801402779582</v>
+      </c>
+      <c r="T26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.16804058338617628</v>
+      </c>
+      <c r="U26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.17726519689053141</v>
+      </c>
+      <c r="V26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.17224480038250059</v>
+      </c>
+      <c r="W26" s="8">
+        <f t="shared" ref="W26:Z26" si="64">W13/W3</f>
+        <v>0.19638043896804006</v>
+      </c>
+      <c r="X26" s="8">
         <f t="shared" si="64"/>
-        <v>0.16871562601099968</v>
-      </c>
-      <c r="J26" s="8">
+        <v>0.18146718146718147</v>
+      </c>
+      <c r="Y26" s="8">
         <f t="shared" si="64"/>
-        <v>0.15177797051170858</v>
-      </c>
-      <c r="K26" s="8">
+        <v>0.18058690744920994</v>
+      </c>
+      <c r="Z26" s="8">
         <f t="shared" si="64"/>
-        <v>0.10967144840351689</v>
-      </c>
-      <c r="L26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.11225389362327358</v>
-      </c>
-      <c r="M26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.16330704060765411</v>
-      </c>
-      <c r="N26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.1684951916565082</v>
-      </c>
-      <c r="O26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.14190340909090909</v>
-      </c>
-      <c r="P26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.15548236585700562</v>
-      </c>
-      <c r="Q26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.15745483957940146</v>
-      </c>
-      <c r="R26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.21530027410914529</v>
-      </c>
-      <c r="S26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.15170801402779582</v>
-      </c>
-      <c r="T26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.16804058338617628</v>
-      </c>
-      <c r="U26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.17726519689053141</v>
-      </c>
-      <c r="V26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.17224480038250059</v>
-      </c>
-      <c r="W26" s="8">
-        <f t="shared" ref="W26:Z26" si="65">W13/W3</f>
-        <v>0.19638043896804006</v>
-      </c>
-      <c r="X26" s="8">
-        <f t="shared" si="65"/>
-        <v>0.18146718146718147</v>
-      </c>
-      <c r="Y26" s="8">
-        <f t="shared" si="65"/>
-        <v>0.17702768886323489</v>
-      </c>
-      <c r="Z26" s="8">
-        <f t="shared" si="65"/>
-        <v>0.18279208867575736</v>
+        <v>0.16913276983925979</v>
       </c>
       <c r="AA26" s="8"/>
       <c r="AC26" s="8">
-        <f t="shared" ref="AC26:AD26" si="66">AC13/AC3</f>
+        <f t="shared" ref="AC26:AD26" si="65">AC13/AC3</f>
         <v>0.1419972817293379</v>
       </c>
       <c r="AD26" s="8">
+        <f t="shared" si="65"/>
+        <v>0.15299347287868556</v>
+      </c>
+      <c r="AE26" s="8">
+        <f t="shared" ref="AE26:AT26" si="66">AE13/AE3</f>
+        <v>0.15330474503589075</v>
+      </c>
+      <c r="AF26" s="8">
         <f t="shared" si="66"/>
-        <v>0.15299347287868556</v>
-      </c>
-      <c r="AE26" s="8">
-        <f t="shared" ref="AE26:AT26" si="67">AE13/AE3</f>
-        <v>0.15330474503589075</v>
-      </c>
-      <c r="AF26" s="8">
-        <f t="shared" si="67"/>
         <v>0.16798707185369122</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0.13943600552365723</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0.16888918746431092</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>0.16746862911595434</v>
       </c>
       <c r="AJ26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.18429052704056867</v>
+        <f t="shared" si="66"/>
+        <v>0.18160554076014884</v>
       </c>
       <c r="AK26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.19993442836765971</v>
+        <f t="shared" si="66"/>
+        <v>0.19918046309244603</v>
       </c>
       <c r="AL26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.21153324346612337</v>
+        <f t="shared" si="66"/>
+        <v>0.20985156176046083</v>
       </c>
       <c r="AM26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.21311580459718363</v>
+        <f t="shared" si="66"/>
+        <v>0.21145024680904662</v>
       </c>
       <c r="AN26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.21468228247247337</v>
+        <f t="shared" si="66"/>
+        <v>0.21303269764498453</v>
       </c>
       <c r="AO26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.21471039883703108</v>
+        <f t="shared" si="66"/>
+        <v>0.21306046149738911</v>
       </c>
       <c r="AP26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.2147382368217417</v>
+        <f t="shared" si="66"/>
+        <v>0.21308795046016585</v>
       </c>
       <c r="AQ26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.21476579918284133</v>
+        <f t="shared" si="66"/>
+        <v>0.21311516725499435</v>
       </c>
       <c r="AR26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.21479308864927657</v>
+        <f t="shared" si="66"/>
+        <v>0.21314211457660673</v>
       </c>
       <c r="AS26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.21482010792297487</v>
+        <f t="shared" si="66"/>
+        <v>0.21316879509305464</v>
       </c>
       <c r="AT26" s="8">
-        <f t="shared" si="67"/>
-        <v>0.21484685967911182</v>
+        <f t="shared" si="66"/>
+        <v>0.21319521144597331</v>
       </c>
       <c r="AW26" t="s">
         <v>57</v>
       </c>
       <c r="AX26" s="1">
         <f>AX24+AX25</f>
-        <v>84106.837904463639</v>
+        <v>85230.990424357398</v>
       </c>
     </row>
     <row r="27" spans="1:146" x14ac:dyDescent="0.3">
@@ -4947,19 +4948,19 @@
         <v>34</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:F27" si="68">C16/C15</f>
+        <f t="shared" ref="C27:F27" si="67">C16/C15</f>
         <v>0.68060836501901145</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0.14952751528627015</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0.10751748251748251</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0.15707369553523401</v>
       </c>
       <c r="G27" s="8">
@@ -4967,152 +4968,152 @@
         <v>-0.2580275229357798</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" ref="H27:V27" si="69">H16/H15</f>
+        <f t="shared" ref="H27:V27" si="68">H16/H15</f>
         <v>0.12684365781710916</v>
       </c>
       <c r="I27" s="8">
+        <f t="shared" si="68"/>
+        <v>6.6952789699570817E-2</v>
+      </c>
+      <c r="J27" s="8">
+        <f t="shared" si="68"/>
+        <v>-0.13456090651558072</v>
+      </c>
+      <c r="K27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.19077901430842609</v>
+      </c>
+      <c r="L27" s="8">
+        <f t="shared" si="68"/>
+        <v>7.9591836734693882</v>
+      </c>
+      <c r="M27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.15716096324461343</v>
+      </c>
+      <c r="N27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.17027027027027028</v>
+      </c>
+      <c r="O27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.25977653631284914</v>
+      </c>
+      <c r="P27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.21028396009209516</v>
+      </c>
+      <c r="Q27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.17808219178082191</v>
+      </c>
+      <c r="R27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.2180702732849972</v>
+      </c>
+      <c r="S27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.26550868486352358</v>
+      </c>
+      <c r="T27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.1937097927090779</v>
+      </c>
+      <c r="U27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.2295957284515637</v>
+      </c>
+      <c r="V27" s="8">
+        <f t="shared" si="68"/>
+        <v>0.20496453900709219</v>
+      </c>
+      <c r="W27" s="8">
+        <f t="shared" ref="W27:Z27" si="69">W16/W15</f>
+        <v>0.19713038053649407</v>
+      </c>
+      <c r="X27" s="8">
         <f t="shared" si="69"/>
-        <v>6.6952789699570817E-2</v>
-      </c>
-      <c r="J27" s="8">
+        <v>0.17527795945062133</v>
+      </c>
+      <c r="Y27" s="8">
         <f t="shared" si="69"/>
-        <v>-0.13456090651558072</v>
-      </c>
-      <c r="K27" s="8">
+        <v>0.18590998043052837</v>
+      </c>
+      <c r="Z27" s="8">
         <f t="shared" si="69"/>
-        <v>0.19077901430842609</v>
-      </c>
-      <c r="L27" s="8">
-        <f t="shared" si="69"/>
-        <v>7.9591836734693882</v>
-      </c>
-      <c r="M27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.15716096324461343</v>
-      </c>
-      <c r="N27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.17027027027027028</v>
-      </c>
-      <c r="O27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.25977653631284914</v>
-      </c>
-      <c r="P27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.21028396009209516</v>
-      </c>
-      <c r="Q27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.17808219178082191</v>
-      </c>
-      <c r="R27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.2180702732849972</v>
-      </c>
-      <c r="S27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.26550868486352358</v>
-      </c>
-      <c r="T27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.1937097927090779</v>
-      </c>
-      <c r="U27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.2295957284515637</v>
-      </c>
-      <c r="V27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.20496453900709219</v>
-      </c>
-      <c r="W27" s="8">
-        <f t="shared" ref="W27:Z27" si="70">W16/W15</f>
-        <v>0.19713038053649407</v>
-      </c>
-      <c r="X27" s="8">
-        <f t="shared" si="70"/>
-        <v>0.17527795945062133</v>
-      </c>
-      <c r="Y27" s="8">
-        <f t="shared" si="70"/>
-        <v>0.2</v>
-      </c>
-      <c r="Z27" s="8">
-        <f t="shared" si="70"/>
         <v>0.2</v>
       </c>
       <c r="AA27" s="8"/>
       <c r="AC27" s="8">
-        <f t="shared" ref="AC27:AD27" si="71">AC16/AC15</f>
+        <f t="shared" ref="AC27:AD27" si="70">AC16/AC15</f>
         <v>0.13425925925925927</v>
       </c>
       <c r="AD27" s="8">
+        <f t="shared" si="70"/>
+        <v>0.17978652434956638</v>
+      </c>
+      <c r="AE27" s="8">
+        <f t="shared" ref="AE27:AT27" si="71">AE16/AE15</f>
+        <v>0.17038499506416585</v>
+      </c>
+      <c r="AF27" s="8">
         <f t="shared" si="71"/>
-        <v>0.17978652434956638</v>
-      </c>
-      <c r="AE27" s="8">
-        <f t="shared" ref="AE27:AT27" si="72">AE16/AE15</f>
-        <v>0.17038499506416585</v>
-      </c>
-      <c r="AF27" s="8">
-        <f t="shared" si="72"/>
         <v>-1.7077335935594046E-2</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>0.28134284016636957</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>0.21530216226205878</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>0.22180521673860012</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.19308708801734736</v>
+        <f t="shared" si="71"/>
+        <v>0.18953241699239368</v>
       </c>
       <c r="AK27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AL27" s="8">
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
-      <c r="AL27" s="8">
-        <f t="shared" si="72"/>
+      <c r="AM27" s="8">
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
-      <c r="AM27" s="8">
-        <f t="shared" si="72"/>
+      <c r="AN27" s="8">
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
-      <c r="AN27" s="8">
-        <f t="shared" si="72"/>
+      <c r="AO27" s="8">
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
-      <c r="AO27" s="8">
-        <f t="shared" si="72"/>
+      <c r="AP27" s="8">
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
-      <c r="AP27" s="8">
-        <f t="shared" si="72"/>
+      <c r="AQ27" s="8">
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
-      <c r="AQ27" s="8">
-        <f t="shared" si="72"/>
+      <c r="AR27" s="8">
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
-      <c r="AR27" s="8">
-        <f t="shared" si="72"/>
+      <c r="AS27" s="8">
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
-      <c r="AS27" s="8">
-        <f t="shared" si="72"/>
-        <v>0.2</v>
-      </c>
       <c r="AT27" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>0.2</v>
       </c>
       <c r="AW27" t="s">
@@ -5120,7 +5121,7 @@
       </c>
       <c r="AX27" s="9">
         <f>AX26/AT18</f>
-        <v>83.897095166547274</v>
+        <v>91.087945307638549</v>
       </c>
     </row>
     <row r="28" spans="1:146" x14ac:dyDescent="0.3">
@@ -5132,175 +5133,175 @@
         <v>1.8189692507579038E-2</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" ref="D28:V28" si="73">D17/D3</f>
+        <f t="shared" ref="D28:V28" si="72">D17/D3</f>
         <v>0.29081923588671355</v>
       </c>
       <c r="E28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.18703059168345851</v>
+      </c>
+      <c r="F28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.25621321124918245</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.1818332504558263</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.18980442449503046</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.17583306373341961</v>
+      </c>
+      <c r="J28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.11578490893321769</v>
+      </c>
+      <c r="K28" s="8">
+        <f t="shared" si="72"/>
+        <v>7.8513034089156261E-2</v>
+      </c>
+      <c r="L28" s="8">
+        <f t="shared" si="72"/>
+        <v>-5.0102850426094622E-2</v>
+      </c>
+      <c r="M28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.19427402862985685</v>
+      </c>
+      <c r="N28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.12474603819585535</v>
+      </c>
+      <c r="O28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.11292613636363637</v>
+      </c>
+      <c r="P28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.14121037463976946</v>
+      </c>
+      <c r="Q28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.13750337018064168</v>
+      </c>
+      <c r="R28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.17468228258160975</v>
+      </c>
+      <c r="S28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.11533965450058449</v>
+      </c>
+      <c r="T28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.14305643627140138</v>
+      </c>
+      <c r="U28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.12871160953230534</v>
+      </c>
+      <c r="V28" s="8">
+        <f t="shared" si="72"/>
+        <v>0.13399474061678221</v>
+      </c>
+      <c r="W28" s="8">
+        <f t="shared" ref="W28:Z28" si="73">W17/W3</f>
+        <v>0.16519060454370427</v>
+      </c>
+      <c r="X28" s="8">
         <f t="shared" si="73"/>
-        <v>0.18703059168345851</v>
-      </c>
-      <c r="F28" s="8">
+        <v>0.15214768339768339</v>
+      </c>
+      <c r="Y28" s="8">
         <f t="shared" si="73"/>
-        <v>0.25621321124918245</v>
-      </c>
-      <c r="G28" s="8">
+        <v>0.14827135558987764</v>
+      </c>
+      <c r="Z28" s="8">
         <f t="shared" si="73"/>
-        <v>0.1818332504558263</v>
-      </c>
-      <c r="H28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.18980442449503046</v>
-      </c>
-      <c r="I28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.17583306373341961</v>
-      </c>
-      <c r="J28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.11578490893321769</v>
-      </c>
-      <c r="K28" s="8">
-        <f t="shared" si="73"/>
-        <v>7.8513034089156261E-2</v>
-      </c>
-      <c r="L28" s="8">
-        <f t="shared" si="73"/>
-        <v>-5.0102850426094622E-2</v>
-      </c>
-      <c r="M28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.19427402862985685</v>
-      </c>
-      <c r="N28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.12474603819585535</v>
-      </c>
-      <c r="O28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.11292613636363637</v>
-      </c>
-      <c r="P28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.14121037463976946</v>
-      </c>
-      <c r="Q28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.13750337018064168</v>
-      </c>
-      <c r="R28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.17468228258160975</v>
-      </c>
-      <c r="S28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.11533965450058449</v>
-      </c>
-      <c r="T28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.14305643627140138</v>
-      </c>
-      <c r="U28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.12871160953230534</v>
-      </c>
-      <c r="V28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.13399474061678221</v>
-      </c>
-      <c r="W28" s="8">
-        <f t="shared" ref="W28:Z28" si="74">W17/W3</f>
-        <v>0.16519060454370427</v>
-      </c>
-      <c r="X28" s="8">
+        <v>0.13719978318654241</v>
+      </c>
+      <c r="AC28" s="8">
+        <f t="shared" ref="AC28:AT28" si="74">AC17/AC3</f>
+        <v>0.13313054171251051</v>
+      </c>
+      <c r="AD28" s="8">
         <f t="shared" si="74"/>
-        <v>0.15214768339768339</v>
-      </c>
-      <c r="Y28" s="8">
+        <v>0.13836371820841772</v>
+      </c>
+      <c r="AE28" s="8">
         <f t="shared" si="74"/>
-        <v>0.14362116657546162</v>
-      </c>
-      <c r="Z28" s="8">
+        <v>0.19586091171809453</v>
+      </c>
+      <c r="AF28" s="8">
         <f t="shared" si="74"/>
-        <v>0.14812723825574048</v>
-      </c>
-      <c r="AC28" s="8">
-        <f t="shared" ref="AC28:AT28" si="75">AC17/AC3</f>
-        <v>0.13313054171251051</v>
-      </c>
-      <c r="AD28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.13836371820841772</v>
-      </c>
-      <c r="AE28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.19586091171809453</v>
-      </c>
-      <c r="AF28" s="8">
-        <f t="shared" si="75"/>
         <v>0.16432146939419021</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>8.7906097826876958E-2</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0.14262201471230393</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>0.13042110890964556</v>
       </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.1521292488150349</v>
+        <f t="shared" si="74"/>
+        <v>0.15040802096543235</v>
       </c>
       <c r="AK28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.15994754269412778</v>
+        <f t="shared" si="74"/>
+        <v>0.1593443704739568</v>
       </c>
       <c r="AL28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.1692265947728987</v>
+        <f t="shared" si="74"/>
+        <v>0.16788124940836865</v>
       </c>
       <c r="AM28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.17049264367774691</v>
+        <f t="shared" si="74"/>
+        <v>0.16916019744723731</v>
       </c>
       <c r="AN28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.17174582597797872</v>
+        <f t="shared" si="74"/>
+        <v>0.17042615811598763</v>
       </c>
       <c r="AO28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.17176831906962489</v>
+        <f t="shared" si="74"/>
+        <v>0.17044836919791129</v>
       </c>
       <c r="AP28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.17179058945739334</v>
+        <f t="shared" si="74"/>
+        <v>0.17047036036813268</v>
       </c>
       <c r="AQ28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.17181263934627306</v>
+        <f t="shared" si="74"/>
+        <v>0.17049213380399547</v>
       </c>
       <c r="AR28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.17183447091942125</v>
+        <f t="shared" si="74"/>
+        <v>0.17051369166128538</v>
       </c>
       <c r="AS28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.1718560863383799</v>
+        <f t="shared" si="74"/>
+        <v>0.1705350360744437</v>
       </c>
       <c r="AT28" s="8">
-        <f t="shared" si="75"/>
-        <v>0.17187748774328945</v>
+        <f t="shared" si="74"/>
+        <v>0.17055616915677865</v>
       </c>
       <c r="AW28" t="s">
         <v>59</v>
       </c>
       <c r="AX28" s="9">
         <f>Main!D3</f>
-        <v>74.84</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="29" spans="1:146" x14ac:dyDescent="0.3">
@@ -5309,7 +5310,7 @@
       </c>
       <c r="AX29" s="10">
         <f>AX27/AX28-1</f>
-        <v>0.12101944370052475</v>
+        <v>0.24743830878716189</v>
       </c>
     </row>
     <row r="30" spans="1:146" x14ac:dyDescent="0.3">
@@ -5317,7 +5318,7 @@
         <v>61</v>
       </c>
       <c r="AX30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/PYPL.xlsx
+++ b/Financial Analysis/PYPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957C3C14-2D1A-4208-8E85-50EDF8CF4193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340367F9-1A0D-4955-B346-3259EF8D58B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7B33BECD-2B6A-465C-BF18-30C78DC6ADF8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t>Price</t>
   </si>
@@ -226,7 +226,19 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
+    <t>Heavily undervalued</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -326,14 +338,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
@@ -350,7 +362,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15803880" y="0"/>
+          <a:off x="17015460" y="0"/>
           <a:ext cx="0" cy="5920740"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -376,13 +388,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -400,7 +412,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22517100" y="7620"/>
+          <a:off x="25565100" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -748,17 +760,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="9">
-        <v>73.02</v>
+        <v>42.32</v>
       </c>
       <c r="E3" s="4">
-        <v>45959</v>
+        <v>46057</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45959</v>
+        <v>46057</v>
       </c>
       <c r="G3" s="4">
-        <v>46064</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -766,11 +778,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
+        <v>920.7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -779,7 +790,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>68324.813999999998</v>
+        <v>38964.024000000005</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -787,11 +798,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <f>8995+1760+3601</f>
-        <v>14356</v>
+        <f>8049+2373+4330</f>
+        <v>14752</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -799,11 +810,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="1">
-        <f>11276</f>
-        <v>11276</v>
+        <f>9987</f>
+        <v>9987</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -812,7 +823,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>3080</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -821,7 +832,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>65244.813999999998</v>
+        <v>34199.024000000005</v>
       </c>
     </row>
   </sheetData>
@@ -832,16 +843,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5B879B-268F-4A69-A6A0-7E602E68C6CD}">
-  <dimension ref="A2:EP30"/>
+  <dimension ref="A2:ET30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="8.88671875" customWidth="1"/>
-    <col min="49" max="49" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
         <v>45</v>
       </c>
@@ -914,63 +925,75 @@
       <c r="Z2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AA2" s="2"/>
-      <c r="AC2">
+      <c r="AA2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE2" s="2"/>
+      <c r="AG2">
         <v>2018</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2019</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2020</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2021</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2022</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2023</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2024</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2025</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2026</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2027</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2028</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2029</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2030</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2031</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2032</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2033</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2034</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:46" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:50" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3"/>
       <c r="B3" s="6" t="s">
         <v>7</v>
@@ -1045,81 +1068,84 @@
         <v>8417</v>
       </c>
       <c r="Z3" s="7">
-        <f>V3*1.01</f>
-        <v>8449.66</v>
-      </c>
-      <c r="AC3" s="7">
+        <v>8676</v>
+      </c>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AG3" s="7">
         <v>15451</v>
       </c>
-      <c r="AD3" s="7">
+      <c r="AH3" s="7">
         <v>17772</v>
       </c>
-      <c r="AE3" s="7">
+      <c r="AI3" s="7">
         <f>SUM(C3:F3)</f>
         <v>21454</v>
       </c>
-      <c r="AF3" s="7">
+      <c r="AJ3" s="7">
         <f>SUM(G3:J3)</f>
         <v>25371</v>
       </c>
-      <c r="AG3" s="7">
+      <c r="AK3" s="7">
         <f>SUM(K3:N3)</f>
         <v>27518</v>
       </c>
-      <c r="AH3" s="7">
+      <c r="AL3" s="7">
         <f>SUM(O3:R3)</f>
         <v>29771</v>
       </c>
-      <c r="AI3" s="7">
+      <c r="AM3" s="7">
         <f>SUM(S3:V3)</f>
         <v>31797</v>
       </c>
-      <c r="AJ3" s="7">
+      <c r="AN3" s="7">
         <f>SUM(W3:Z3)</f>
-        <v>32945.660000000003</v>
-      </c>
-      <c r="AK3" s="7">
-        <f>AJ3*1.02</f>
-        <v>33604.573200000006</v>
-      </c>
-      <c r="AL3" s="7">
-        <f>AK3*1.02</f>
-        <v>34276.664664000004</v>
-      </c>
-      <c r="AM3" s="7">
-        <f>AL3*1.02</f>
-        <v>34962.197957280005</v>
-      </c>
-      <c r="AN3" s="7">
-        <f t="shared" ref="AN3" si="0">AM3*1.02</f>
-        <v>35661.441916425603</v>
+        <v>33172</v>
       </c>
       <c r="AO3" s="7">
-        <f>AN3*1.01</f>
-        <v>36018.056335589863</v>
+        <f>AN3*0.95</f>
+        <v>31513.399999999998</v>
       </c>
       <c r="AP3" s="7">
-        <f t="shared" ref="AP3:AT3" si="1">AO3*1.01</f>
-        <v>36378.236898945761</v>
+        <f>AO3*1.02</f>
+        <v>32143.667999999998</v>
       </c>
       <c r="AQ3" s="7">
+        <f>AP3*1.02</f>
+        <v>32786.541359999996</v>
+      </c>
+      <c r="AR3" s="7">
+        <f t="shared" ref="AR3" si="0">AQ3*1.02</f>
+        <v>33442.272187199997</v>
+      </c>
+      <c r="AS3" s="7">
+        <f>AR3*1.01</f>
+        <v>33776.694909071994</v>
+      </c>
+      <c r="AT3" s="7">
+        <f t="shared" ref="AT3:AX3" si="1">AS3*1.01</f>
+        <v>34114.461858162715</v>
+      </c>
+      <c r="AU3" s="7">
         <f t="shared" si="1"/>
-        <v>36742.019267935219</v>
-      </c>
-      <c r="AR3" s="7">
+        <v>34455.606476744339</v>
+      </c>
+      <c r="AV3" s="7">
         <f t="shared" si="1"/>
-        <v>37109.439460614572</v>
-      </c>
-      <c r="AS3" s="7">
+        <v>34800.162541511781</v>
+      </c>
+      <c r="AW3" s="7">
         <f t="shared" si="1"/>
-        <v>37480.533855220718</v>
-      </c>
-      <c r="AT3" s="7">
+        <v>35148.164166926901</v>
+      </c>
+      <c r="AX3" s="7">
         <f t="shared" si="1"/>
-        <v>37855.339193772925</v>
+        <v>35499.645808596171</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>20</v>
       </c>
@@ -1192,37 +1218,39 @@
       <c r="Y4" s="1">
         <v>4063</v>
       </c>
-      <c r="Z4" s="1"/>
-      <c r="AC4" s="1">
+      <c r="Z4" s="1">
+        <v>4252</v>
+      </c>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AG4" s="1">
         <v>5581</v>
       </c>
-      <c r="AD4" s="1">
+      <c r="AH4" s="1">
         <v>6790</v>
       </c>
-      <c r="AE4" s="1">
+      <c r="AI4" s="1">
         <f>SUM(C4:F4)</f>
         <v>7934</v>
       </c>
-      <c r="AF4" s="1">
+      <c r="AJ4" s="1">
         <f>SUM(G4:J4)</f>
         <v>10315</v>
       </c>
-      <c r="AG4" s="1">
+      <c r="AK4" s="1">
         <f>SUM(K4:N4)</f>
         <v>12173</v>
       </c>
-      <c r="AH4" s="1">
+      <c r="AL4" s="1">
         <f>SUM(O4:R4)</f>
         <v>14385</v>
       </c>
-      <c r="AI4" s="1">
+      <c r="AM4" s="1">
         <f>SUM(S4:V4)</f>
         <v>15697</v>
       </c>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="1"/>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1"/>
@@ -1230,8 +1258,12 @@
       <c r="AR4" s="1"/>
       <c r="AS4" s="1"/>
       <c r="AT4" s="1"/>
+      <c r="AU4" s="1"/>
+      <c r="AV4" s="1"/>
+      <c r="AW4" s="1"/>
+      <c r="AX4" s="1"/>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>21</v>
       </c>
@@ -1304,37 +1336,39 @@
       <c r="Y5" s="1">
         <v>483</v>
       </c>
-      <c r="Z5" s="1"/>
-      <c r="AC5" s="1">
+      <c r="Z5" s="1">
+        <v>390</v>
+      </c>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AG5" s="1">
         <v>1274</v>
       </c>
-      <c r="AD5" s="1">
+      <c r="AH5" s="1">
         <v>1380</v>
       </c>
-      <c r="AE5" s="1">
+      <c r="AI5" s="1">
         <f>SUM(C5:F5)</f>
         <v>1741</v>
       </c>
-      <c r="AF5" s="1">
+      <c r="AJ5" s="1">
         <f>SUM(G5:J5)</f>
         <v>1060</v>
       </c>
-      <c r="AG5" s="1">
+      <c r="AK5" s="1">
         <f>SUM(K5:N5)</f>
         <v>1572</v>
       </c>
-      <c r="AH5" s="1">
+      <c r="AL5" s="1">
         <f>SUM(O5:R5)</f>
         <v>1682</v>
       </c>
-      <c r="AI5" s="1">
+      <c r="AM5" s="1">
         <f>SUM(S5:V5)</f>
         <v>1442</v>
       </c>
-      <c r="AJ5" s="1"/>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
@@ -1342,8 +1376,12 @@
       <c r="AR5" s="1"/>
       <c r="AS5" s="1"/>
       <c r="AT5" s="1"/>
+      <c r="AU5" s="1"/>
+      <c r="AV5" s="1"/>
+      <c r="AW5" s="1"/>
+      <c r="AX5" s="1"/>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -1416,37 +1454,39 @@
       <c r="Y6" s="1">
         <v>447</v>
       </c>
-      <c r="Z6" s="1"/>
-      <c r="AC6" s="1">
+      <c r="Z6" s="1">
+        <v>446</v>
+      </c>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AG6" s="1">
         <v>1407</v>
       </c>
-      <c r="AD6" s="1">
+      <c r="AH6" s="1">
         <v>1615</v>
       </c>
-      <c r="AE6" s="1">
+      <c r="AI6" s="1">
         <f>SUM(C6:F6)</f>
         <v>1778</v>
       </c>
-      <c r="AF6" s="1">
+      <c r="AJ6" s="1">
         <f>SUM(G6:J6)</f>
         <v>2075</v>
       </c>
-      <c r="AG6" s="1">
+      <c r="AK6" s="1">
         <f>SUM(K6:N6)</f>
         <v>2120</v>
       </c>
-      <c r="AH6" s="1">
+      <c r="AL6" s="1">
         <f>SUM(O6:R6)</f>
         <v>1919</v>
       </c>
-      <c r="AI6" s="1">
+      <c r="AM6" s="1">
         <f>SUM(S6:V6)</f>
         <v>1768</v>
       </c>
-      <c r="AJ6" s="1"/>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="1"/>
-      <c r="AM6" s="1"/>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
@@ -1454,13 +1494,17 @@
       <c r="AR6" s="1"/>
       <c r="AS6" s="1"/>
       <c r="AT6" s="1"/>
+      <c r="AU6" s="1"/>
+      <c r="AV6" s="1"/>
+      <c r="AW6" s="1"/>
+      <c r="AX6" s="1"/>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" ref="C7:Y7" si="2">SUM(C4:C6)</f>
+        <f t="shared" ref="C7:Z7" si="2">SUM(C4:C6)</f>
         <v>2729</v>
       </c>
       <c r="D7" s="1">
@@ -1552,257 +1596,265 @@
         <v>4993</v>
       </c>
       <c r="Z7" s="1">
-        <f t="shared" ref="Y7:Z7" si="3">Z3-Z8</f>
-        <v>4900.8027999999995</v>
-      </c>
-      <c r="AC7" s="1">
-        <f t="shared" ref="AC7:AH7" si="4">SUM(AC4:AC6)</f>
+        <f t="shared" si="2"/>
+        <v>5088</v>
+      </c>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AG7" s="1">
+        <f t="shared" ref="AG7:AL7" si="3">SUM(AG4:AG6)</f>
         <v>8262</v>
       </c>
-      <c r="AD7" s="1">
-        <f t="shared" si="4"/>
+      <c r="AH7" s="1">
+        <f t="shared" si="3"/>
         <v>9785</v>
       </c>
-      <c r="AE7" s="1">
-        <f t="shared" si="4"/>
+      <c r="AI7" s="1">
+        <f t="shared" si="3"/>
         <v>11453</v>
       </c>
-      <c r="AF7" s="1">
-        <f t="shared" si="4"/>
+      <c r="AJ7" s="1">
+        <f t="shared" si="3"/>
         <v>13450</v>
       </c>
-      <c r="AG7" s="1">
-        <f t="shared" si="4"/>
+      <c r="AK7" s="1">
+        <f t="shared" si="3"/>
         <v>15865</v>
       </c>
-      <c r="AH7" s="1">
-        <f t="shared" si="4"/>
+      <c r="AL7" s="1">
+        <f t="shared" si="3"/>
         <v>17986</v>
       </c>
-      <c r="AI7" s="1">
+      <c r="AM7" s="1">
         <f>SUM(S7:V7)</f>
         <v>18907</v>
       </c>
-      <c r="AJ7" s="1">
+      <c r="AN7" s="1">
         <f>SUM(W7:Z7)</f>
-        <v>19223.802799999998</v>
-      </c>
-      <c r="AK7" s="1">
-        <f t="shared" ref="AK7:AT7" si="5">AK3-AK8</f>
-        <v>19154.606724000005</v>
-      </c>
-      <c r="AL7" s="1">
-        <f t="shared" si="5"/>
-        <v>19194.932211840001</v>
-      </c>
-      <c r="AM7" s="1">
-        <f t="shared" si="5"/>
-        <v>19578.830856076802</v>
-      </c>
-      <c r="AN7" s="1">
-        <f t="shared" si="5"/>
-        <v>19970.407473198338</v>
+        <v>19411</v>
       </c>
       <c r="AO7" s="1">
-        <f t="shared" si="5"/>
-        <v>20170.111547930323</v>
+        <f t="shared" ref="AO7:AX7" si="4">AO3-AO8</f>
+        <v>18592.905999999999</v>
       </c>
       <c r="AP7" s="1">
-        <f t="shared" si="5"/>
-        <v>20371.812663409626</v>
+        <f t="shared" si="4"/>
+        <v>18964.76412</v>
       </c>
       <c r="AQ7" s="1">
-        <f t="shared" si="5"/>
-        <v>20575.530790043722</v>
+        <f t="shared" si="4"/>
+        <v>19344.059402399998</v>
       </c>
       <c r="AR7" s="1">
-        <f t="shared" si="5"/>
-        <v>20781.286097944161</v>
+        <f t="shared" si="4"/>
+        <v>19730.940590448001</v>
       </c>
       <c r="AS7" s="1">
-        <f t="shared" si="5"/>
-        <v>20989.098958923601</v>
+        <f t="shared" si="4"/>
+        <v>19928.249996352475</v>
       </c>
       <c r="AT7" s="1">
-        <f t="shared" si="5"/>
-        <v>21198.989948512837</v>
+        <f t="shared" si="4"/>
+        <v>20127.532496316002</v>
+      </c>
+      <c r="AU7" s="1">
+        <f t="shared" si="4"/>
+        <v>20328.807821279159</v>
+      </c>
+      <c r="AV7" s="1">
+        <f t="shared" si="4"/>
+        <v>20532.095899491949</v>
+      </c>
+      <c r="AW7" s="1">
+        <f t="shared" si="4"/>
+        <v>20737.416858486875</v>
+      </c>
+      <c r="AX7" s="1">
+        <f t="shared" si="4"/>
+        <v>20944.79102707174</v>
       </c>
     </row>
-    <row r="8" spans="1:46" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:50" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8"/>
       <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="7">
-        <f t="shared" ref="C8:Y8" si="6">C3-C7</f>
+        <f t="shared" ref="C8:Z8" si="5">C3-C7</f>
         <v>1889</v>
       </c>
       <c r="D8" s="7">
+        <f t="shared" si="5"/>
+        <v>2555</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="5"/>
+        <v>2644</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="5"/>
+        <v>2913</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="5"/>
+        <v>2967</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="5"/>
+        <v>3024</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="5"/>
+        <v>2846</v>
+      </c>
+      <c r="J8" s="7">
+        <f t="shared" si="5"/>
+        <v>3084</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="5"/>
+        <v>2763</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="5"/>
+        <v>2778</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="5"/>
+        <v>2982</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="5"/>
+        <v>3130</v>
+      </c>
+      <c r="O8" s="7">
+        <f t="shared" si="5"/>
+        <v>2827</v>
+      </c>
+      <c r="P8" s="7">
+        <f t="shared" si="5"/>
+        <v>2856</v>
+      </c>
+      <c r="Q8" s="7">
+        <f t="shared" si="5"/>
+        <v>2895</v>
+      </c>
+      <c r="R8" s="7">
+        <f t="shared" si="5"/>
+        <v>3207</v>
+      </c>
+      <c r="S8" s="7">
+        <f t="shared" si="5"/>
+        <v>3007</v>
+      </c>
+      <c r="T8" s="7">
+        <f t="shared" si="5"/>
+        <v>3172</v>
+      </c>
+      <c r="U8" s="7">
+        <f t="shared" si="5"/>
+        <v>3227</v>
+      </c>
+      <c r="V8" s="7">
+        <f t="shared" si="5"/>
+        <v>3484</v>
+      </c>
+      <c r="W8" s="7">
+        <f t="shared" si="5"/>
+        <v>3318</v>
+      </c>
+      <c r="X8" s="7">
+        <f t="shared" si="5"/>
+        <v>3431</v>
+      </c>
+      <c r="Y8" s="7">
+        <f t="shared" si="5"/>
+        <v>3424</v>
+      </c>
+      <c r="Z8" s="7">
+        <f t="shared" si="5"/>
+        <v>3588</v>
+      </c>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AG8" s="7">
+        <f t="shared" ref="AG8:AN8" si="6">AG3-AG7</f>
+        <v>7189</v>
+      </c>
+      <c r="AH8" s="7">
         <f t="shared" si="6"/>
-        <v>2555</v>
-      </c>
-      <c r="E8" s="7">
+        <v>7987</v>
+      </c>
+      <c r="AI8" s="7">
         <f t="shared" si="6"/>
-        <v>2644</v>
-      </c>
-      <c r="F8" s="7">
+        <v>10001</v>
+      </c>
+      <c r="AJ8" s="7">
         <f t="shared" si="6"/>
-        <v>2913</v>
-      </c>
-      <c r="G8" s="7">
+        <v>11921</v>
+      </c>
+      <c r="AK8" s="7">
         <f t="shared" si="6"/>
-        <v>2967</v>
-      </c>
-      <c r="H8" s="7">
+        <v>11653</v>
+      </c>
+      <c r="AL8" s="7">
         <f t="shared" si="6"/>
-        <v>3024</v>
-      </c>
-      <c r="I8" s="7">
+        <v>11785</v>
+      </c>
+      <c r="AM8" s="7">
         <f t="shared" si="6"/>
-        <v>2846</v>
-      </c>
-      <c r="J8" s="7">
+        <v>12890</v>
+      </c>
+      <c r="AN8" s="7">
         <f t="shared" si="6"/>
-        <v>3084</v>
-      </c>
-      <c r="K8" s="7">
-        <f t="shared" si="6"/>
-        <v>2763</v>
-      </c>
-      <c r="L8" s="7">
-        <f t="shared" si="6"/>
-        <v>2778</v>
-      </c>
-      <c r="M8" s="7">
-        <f t="shared" si="6"/>
-        <v>2982</v>
-      </c>
-      <c r="N8" s="7">
-        <f t="shared" si="6"/>
-        <v>3130</v>
-      </c>
-      <c r="O8" s="7">
-        <f t="shared" si="6"/>
-        <v>2827</v>
-      </c>
-      <c r="P8" s="7">
-        <f t="shared" si="6"/>
-        <v>2856</v>
-      </c>
-      <c r="Q8" s="7">
-        <f t="shared" si="6"/>
-        <v>2895</v>
-      </c>
-      <c r="R8" s="7">
-        <f t="shared" si="6"/>
-        <v>3207</v>
-      </c>
-      <c r="S8" s="7">
-        <f t="shared" si="6"/>
-        <v>3007</v>
-      </c>
-      <c r="T8" s="7">
-        <f t="shared" si="6"/>
-        <v>3172</v>
-      </c>
-      <c r="U8" s="7">
-        <f t="shared" si="6"/>
-        <v>3227</v>
-      </c>
-      <c r="V8" s="7">
-        <f t="shared" si="6"/>
-        <v>3484</v>
-      </c>
-      <c r="W8" s="7">
-        <f t="shared" si="6"/>
-        <v>3318</v>
-      </c>
-      <c r="X8" s="7">
-        <f t="shared" si="6"/>
-        <v>3431</v>
-      </c>
-      <c r="Y8" s="7">
-        <f t="shared" si="6"/>
-        <v>3424</v>
-      </c>
-      <c r="Z8" s="7">
-        <f>Z3*0.42</f>
-        <v>3548.8571999999999</v>
-      </c>
-      <c r="AC8" s="7">
-        <f t="shared" ref="AC8:AJ8" si="7">AC3-AC7</f>
-        <v>7189</v>
-      </c>
-      <c r="AD8" s="7">
+        <v>13761</v>
+      </c>
+      <c r="AO8" s="7">
+        <f>AO3*0.41</f>
+        <v>12920.493999999999</v>
+      </c>
+      <c r="AP8" s="7">
+        <f t="shared" ref="AP8:AX8" si="7">AP3*0.41</f>
+        <v>13178.903879999998</v>
+      </c>
+      <c r="AQ8" s="7">
         <f t="shared" si="7"/>
-        <v>7987</v>
-      </c>
-      <c r="AE8" s="7">
+        <v>13442.481957599997</v>
+      </c>
+      <c r="AR8" s="7">
         <f t="shared" si="7"/>
-        <v>10001</v>
-      </c>
-      <c r="AF8" s="7">
+        <v>13711.331596751997</v>
+      </c>
+      <c r="AS8" s="7">
         <f t="shared" si="7"/>
-        <v>11921</v>
-      </c>
-      <c r="AG8" s="7">
+        <v>13848.444912719517</v>
+      </c>
+      <c r="AT8" s="7">
         <f t="shared" si="7"/>
-        <v>11653</v>
-      </c>
-      <c r="AH8" s="7">
+        <v>13986.929361846713</v>
+      </c>
+      <c r="AU8" s="7">
         <f t="shared" si="7"/>
-        <v>11785</v>
-      </c>
-      <c r="AI8" s="7">
+        <v>14126.798655465178</v>
+      </c>
+      <c r="AV8" s="7">
         <f t="shared" si="7"/>
-        <v>12890</v>
-      </c>
-      <c r="AJ8" s="7">
+        <v>14268.06664201983</v>
+      </c>
+      <c r="AW8" s="7">
         <f t="shared" si="7"/>
-        <v>13721.857200000006</v>
-      </c>
-      <c r="AK8" s="7">
-        <f>AK3*0.43</f>
-        <v>14449.966476000003</v>
-      </c>
-      <c r="AL8" s="7">
-        <f>AL3*0.44</f>
-        <v>15081.732452160002</v>
-      </c>
-      <c r="AM8" s="7">
-        <f t="shared" ref="AM8:AT8" si="8">AM3*0.44</f>
-        <v>15383.367101203203</v>
-      </c>
-      <c r="AN8" s="7">
-        <f t="shared" si="8"/>
-        <v>15691.034443227265</v>
-      </c>
-      <c r="AO8" s="7">
-        <f t="shared" si="8"/>
-        <v>15847.94478765954</v>
-      </c>
-      <c r="AP8" s="7">
-        <f t="shared" si="8"/>
-        <v>16006.424235536135</v>
-      </c>
-      <c r="AQ8" s="7">
-        <f t="shared" si="8"/>
-        <v>16166.488477891497</v>
-      </c>
-      <c r="AR8" s="7">
-        <f t="shared" si="8"/>
-        <v>16328.153362670411</v>
-      </c>
-      <c r="AS8" s="7">
-        <f t="shared" si="8"/>
-        <v>16491.434896297116</v>
-      </c>
-      <c r="AT8" s="7">
-        <f t="shared" si="8"/>
-        <v>16656.349245260088</v>
+        <v>14410.747308440028</v>
+      </c>
+      <c r="AX8" s="7">
+        <f t="shared" si="7"/>
+        <v>14554.854781524429</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>27</v>
       </c>
@@ -1876,81 +1928,84 @@
         <v>521</v>
       </c>
       <c r="Z9" s="1">
-        <f>Z3*0.08</f>
-        <v>675.97280000000001</v>
-      </c>
-      <c r="AC9" s="1">
+        <v>691</v>
+      </c>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AG9" s="1">
         <v>1314</v>
       </c>
-      <c r="AD9" s="1">
+      <c r="AH9" s="1">
         <v>1401</v>
       </c>
-      <c r="AE9" s="1">
+      <c r="AI9" s="1">
         <f>SUM(C9:F9)</f>
         <v>1861</v>
       </c>
-      <c r="AF9" s="1">
+      <c r="AJ9" s="1">
         <f>SUM(G9:J9)</f>
         <v>2445</v>
       </c>
-      <c r="AG9" s="1">
+      <c r="AK9" s="1">
         <f>SUM(K9:N9)</f>
         <v>2257</v>
       </c>
-      <c r="AH9" s="1">
+      <c r="AL9" s="1">
         <f>SUM(O9:R9)</f>
         <v>1809</v>
       </c>
-      <c r="AI9" s="1">
+      <c r="AM9" s="1">
         <f>SUM(S9:V9)</f>
         <v>2001</v>
       </c>
-      <c r="AJ9" s="1">
-        <f t="shared" ref="AJ9:AJ12" si="9">SUM(W9:Z9)</f>
-        <v>2267.9728</v>
-      </c>
-      <c r="AK9" s="1">
-        <f>AK3*0.07</f>
-        <v>2352.3201240000008</v>
-      </c>
-      <c r="AL9" s="1">
-        <f t="shared" ref="AL9:AT9" si="10">AL3*0.07</f>
-        <v>2399.3665264800006</v>
-      </c>
-      <c r="AM9" s="1">
-        <f t="shared" si="10"/>
-        <v>2447.3538570096007</v>
-      </c>
       <c r="AN9" s="1">
-        <f t="shared" si="10"/>
-        <v>2496.3009341497923</v>
+        <f t="shared" ref="AN9:AN12" si="8">SUM(W9:Z9)</f>
+        <v>2283</v>
       </c>
       <c r="AO9" s="1">
-        <f t="shared" si="10"/>
-        <v>2521.2639434912908</v>
+        <f>AO3*0.07</f>
+        <v>2205.9380000000001</v>
       </c>
       <c r="AP9" s="1">
-        <f t="shared" si="10"/>
-        <v>2546.4765829262037</v>
+        <f t="shared" ref="AP9:AX9" si="9">AP3*0.07</f>
+        <v>2250.0567599999999</v>
       </c>
       <c r="AQ9" s="1">
-        <f t="shared" si="10"/>
-        <v>2571.9413487554657</v>
+        <f t="shared" si="9"/>
+        <v>2295.0578952000001</v>
       </c>
       <c r="AR9" s="1">
-        <f t="shared" si="10"/>
-        <v>2597.6607622430201</v>
+        <f t="shared" si="9"/>
+        <v>2340.9590531039998</v>
       </c>
       <c r="AS9" s="1">
-        <f t="shared" si="10"/>
-        <v>2623.6373698654506</v>
+        <f t="shared" si="9"/>
+        <v>2364.3686436350399</v>
       </c>
       <c r="AT9" s="1">
-        <f t="shared" si="10"/>
-        <v>2649.8737435641051</v>
+        <f t="shared" si="9"/>
+        <v>2388.0123300713904</v>
+      </c>
+      <c r="AU9" s="1">
+        <f t="shared" si="9"/>
+        <v>2411.8924533721038</v>
+      </c>
+      <c r="AV9" s="1">
+        <f t="shared" si="9"/>
+        <v>2436.0113779058252</v>
+      </c>
+      <c r="AW9" s="1">
+        <f t="shared" si="9"/>
+        <v>2460.3714916848835</v>
+      </c>
+      <c r="AX9" s="1">
+        <f t="shared" si="9"/>
+        <v>2484.9752066017322</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>28</v>
       </c>
@@ -2024,81 +2079,84 @@
         <v>801</v>
       </c>
       <c r="Z10" s="1">
-        <f>V10*1.05</f>
-        <v>811.65000000000009</v>
-      </c>
-      <c r="AC10" s="1">
+        <v>804</v>
+      </c>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AG10" s="1">
         <v>1831</v>
       </c>
-      <c r="AD10" s="1">
+      <c r="AH10" s="1">
         <v>2085</v>
       </c>
-      <c r="AE10" s="1">
+      <c r="AI10" s="1">
         <f>SUM(C10:F10)</f>
         <v>2642</v>
       </c>
-      <c r="AF10" s="1">
+      <c r="AJ10" s="1">
         <f>SUM(G10:J10)</f>
         <v>3038</v>
       </c>
-      <c r="AG10" s="1">
+      <c r="AK10" s="1">
         <f>SUM(K10:N10)</f>
         <v>3253</v>
       </c>
-      <c r="AH10" s="1">
+      <c r="AL10" s="1">
         <f>SUM(O10:R10)</f>
         <v>2973</v>
       </c>
-      <c r="AI10" s="1">
+      <c r="AM10" s="1">
         <f>SUM(S10:V10)</f>
         <v>2979</v>
       </c>
-      <c r="AJ10" s="1">
-        <f t="shared" si="9"/>
-        <v>3110.65</v>
-      </c>
-      <c r="AK10" s="1">
-        <f>AJ10*1.03</f>
-        <v>3203.9695000000002</v>
-      </c>
-      <c r="AL10" s="1">
-        <f>AK10*1.02</f>
-        <v>3268.04889</v>
-      </c>
-      <c r="AM10" s="1">
-        <f t="shared" ref="AM10:AT10" si="11">AL10*1.01</f>
-        <v>3300.7293789</v>
-      </c>
       <c r="AN10" s="1">
-        <f t="shared" si="11"/>
-        <v>3333.736672689</v>
+        <f t="shared" si="8"/>
+        <v>3103</v>
       </c>
       <c r="AO10" s="1">
-        <f t="shared" si="11"/>
-        <v>3367.0740394158902</v>
+        <f>AN10*1.03</f>
+        <v>3196.09</v>
       </c>
       <c r="AP10" s="1">
-        <f t="shared" si="11"/>
-        <v>3400.7447798100493</v>
+        <f>AO10*1.02</f>
+        <v>3260.0118000000002</v>
       </c>
       <c r="AQ10" s="1">
-        <f t="shared" si="11"/>
-        <v>3434.75222760815</v>
+        <f t="shared" ref="AQ10:AX10" si="10">AP10*1.01</f>
+        <v>3292.6119180000001</v>
       </c>
       <c r="AR10" s="1">
-        <f t="shared" si="11"/>
-        <v>3469.0997498842316</v>
+        <f t="shared" si="10"/>
+        <v>3325.5380371800002</v>
       </c>
       <c r="AS10" s="1">
-        <f t="shared" si="11"/>
-        <v>3503.7907473830742</v>
+        <f t="shared" si="10"/>
+        <v>3358.7934175518003</v>
       </c>
       <c r="AT10" s="1">
-        <f t="shared" si="11"/>
-        <v>3538.8286548569049</v>
+        <f t="shared" si="10"/>
+        <v>3392.3813517273184</v>
+      </c>
+      <c r="AU10" s="1">
+        <f t="shared" si="10"/>
+        <v>3426.3051652445915</v>
+      </c>
+      <c r="AV10" s="1">
+        <f t="shared" si="10"/>
+        <v>3460.5682168970375</v>
+      </c>
+      <c r="AW10" s="1">
+        <f t="shared" si="10"/>
+        <v>3495.1738990660078</v>
+      </c>
+      <c r="AX10" s="1">
+        <f t="shared" si="10"/>
+        <v>3530.1256380566679</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>29</v>
       </c>
@@ -2172,81 +2230,84 @@
         <v>513</v>
       </c>
       <c r="Z11" s="1">
-        <f t="shared" ref="Z11" si="12">V11*0.98</f>
-        <v>582.12</v>
-      </c>
-      <c r="AC11" s="1">
+        <v>502</v>
+      </c>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AG11" s="1">
         <v>1541</v>
       </c>
-      <c r="AD11" s="1">
+      <c r="AH11" s="1">
         <v>1711</v>
       </c>
-      <c r="AE11" s="1">
+      <c r="AI11" s="1">
         <f>SUM(C11:F11)</f>
         <v>2070</v>
       </c>
-      <c r="AF11" s="1">
+      <c r="AJ11" s="1">
         <f>SUM(G11:J11)</f>
         <v>2114</v>
       </c>
-      <c r="AG11" s="1">
+      <c r="AK11" s="1">
         <f>SUM(K11:N11)</f>
         <v>2099</v>
       </c>
-      <c r="AH11" s="1">
+      <c r="AL11" s="1">
         <f>SUM(O11:R11)</f>
         <v>2059</v>
       </c>
-      <c r="AI11" s="1">
+      <c r="AM11" s="1">
         <f>SUM(S11:V11)</f>
         <v>2147</v>
       </c>
-      <c r="AJ11" s="1">
-        <f t="shared" si="9"/>
-        <v>2059.12</v>
-      </c>
-      <c r="AK11" s="1">
-        <f>AJ11*1.02</f>
-        <v>2100.3024</v>
-      </c>
-      <c r="AL11" s="1">
-        <f t="shared" ref="AL11:AT11" si="13">AK11*1.01</f>
-        <v>2121.3054240000001</v>
-      </c>
-      <c r="AM11" s="1">
-        <f t="shared" si="13"/>
-        <v>2142.5184782400001</v>
-      </c>
       <c r="AN11" s="1">
-        <f t="shared" si="13"/>
-        <v>2163.9436630224</v>
+        <f t="shared" si="8"/>
+        <v>1979</v>
       </c>
       <c r="AO11" s="1">
-        <f t="shared" si="13"/>
-        <v>2185.5830996526238</v>
+        <f>AN11*1.02</f>
+        <v>2018.58</v>
       </c>
       <c r="AP11" s="1">
-        <f t="shared" si="13"/>
-        <v>2207.4389306491498</v>
+        <f t="shared" ref="AP11:AX11" si="11">AO11*1.01</f>
+        <v>2038.7657999999999</v>
       </c>
       <c r="AQ11" s="1">
-        <f t="shared" si="13"/>
-        <v>2229.5133199556412</v>
+        <f t="shared" si="11"/>
+        <v>2059.1534579999998</v>
       </c>
       <c r="AR11" s="1">
-        <f t="shared" si="13"/>
-        <v>2251.8084531551976</v>
+        <f t="shared" si="11"/>
+        <v>2079.7449925799997</v>
       </c>
       <c r="AS11" s="1">
-        <f t="shared" si="13"/>
-        <v>2274.3265376867498</v>
+        <f t="shared" si="11"/>
+        <v>2100.5424425057995</v>
       </c>
       <c r="AT11" s="1">
-        <f t="shared" si="13"/>
-        <v>2297.0698030636172</v>
+        <f t="shared" si="11"/>
+        <v>2121.5478669308577</v>
+      </c>
+      <c r="AU11" s="1">
+        <f t="shared" si="11"/>
+        <v>2142.7633456001663</v>
+      </c>
+      <c r="AV11" s="1">
+        <f t="shared" si="11"/>
+        <v>2164.1909790561681</v>
+      </c>
+      <c r="AW11" s="1">
+        <f t="shared" si="11"/>
+        <v>2185.8328888467299</v>
+      </c>
+      <c r="AX11" s="1">
+        <f t="shared" si="11"/>
+        <v>2207.6912177351974</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>30</v>
       </c>
@@ -2320,49 +2381,41 @@
         <v>69</v>
       </c>
       <c r="Z12" s="1">
-        <v>50</v>
-      </c>
-      <c r="AC12" s="1">
+        <v>80</v>
+      </c>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AG12" s="1">
         <v>309</v>
       </c>
-      <c r="AD12" s="1">
+      <c r="AH12" s="1">
         <v>71</v>
       </c>
-      <c r="AE12" s="1">
+      <c r="AI12" s="1">
         <f>SUM(C12:F12)</f>
         <v>139</v>
       </c>
-      <c r="AF12" s="1">
+      <c r="AJ12" s="1">
         <f>SUM(G12:J12)</f>
         <v>62</v>
       </c>
-      <c r="AG12" s="1">
+      <c r="AK12" s="1">
         <f>SUM(K12:N12)</f>
         <v>207</v>
       </c>
-      <c r="AH12" s="1">
+      <c r="AL12" s="1">
         <f>SUM(O12:R12)</f>
         <v>-84</v>
       </c>
-      <c r="AI12" s="1">
+      <c r="AM12" s="1">
         <f>SUM(S12:V12)</f>
         <v>438</v>
       </c>
-      <c r="AJ12" s="1">
-        <f t="shared" si="9"/>
-        <v>301</v>
-      </c>
-      <c r="AK12" s="1">
-        <v>100</v>
-      </c>
-      <c r="AL12" s="1">
-        <v>100</v>
-      </c>
-      <c r="AM12" s="1">
-        <v>100</v>
-      </c>
       <c r="AN12" s="1">
-        <v>100</v>
+        <f t="shared" si="8"/>
+        <v>331</v>
       </c>
       <c r="AO12" s="1">
         <v>100</v>
@@ -2382,182 +2435,198 @@
       <c r="AT12" s="1">
         <v>100</v>
       </c>
+      <c r="AU12" s="1">
+        <v>100</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>100</v>
+      </c>
+      <c r="AW12" s="1">
+        <v>100</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>100</v>
+      </c>
     </row>
-    <row r="13" spans="1:46" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:50" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13"/>
       <c r="B13" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:S13" si="14">C8-SUM(C9:C12)</f>
+        <f t="shared" ref="C13:S13" si="12">C8-SUM(C9:C12)</f>
         <v>398</v>
       </c>
       <c r="D13" s="7">
+        <f t="shared" si="12"/>
+        <v>951</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="12"/>
+        <v>977</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="12"/>
+        <v>963</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="12"/>
+        <v>1042</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="12"/>
+        <v>1127</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="12"/>
+        <v>1043</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="12"/>
+        <v>1050</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="12"/>
+        <v>711</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="12"/>
+        <v>764</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="12"/>
+        <v>1118</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="12"/>
+        <v>1244</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" si="12"/>
+        <v>999</v>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" si="12"/>
+        <v>1133</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="12"/>
+        <v>1168</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="12"/>
+        <v>1728</v>
+      </c>
+      <c r="S13" s="7">
+        <f t="shared" si="12"/>
+        <v>1168</v>
+      </c>
+      <c r="T13" s="7">
+        <f t="shared" ref="T13:Z13" si="13">T8-SUM(T9:T12)</f>
+        <v>1325</v>
+      </c>
+      <c r="U13" s="7">
+        <f t="shared" si="13"/>
+        <v>1391</v>
+      </c>
+      <c r="V13" s="7">
+        <f t="shared" si="13"/>
+        <v>1441</v>
+      </c>
+      <c r="W13" s="7">
+        <f t="shared" si="13"/>
+        <v>1530</v>
+      </c>
+      <c r="X13" s="7">
+        <f t="shared" si="13"/>
+        <v>1504</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="13"/>
+        <v>1520</v>
+      </c>
+      <c r="Z13" s="7">
+        <f t="shared" si="13"/>
+        <v>1511</v>
+      </c>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AG13" s="7">
+        <f t="shared" ref="AG13:AN13" si="14">AG8-SUM(AG9:AG12)</f>
+        <v>2194</v>
+      </c>
+      <c r="AH13" s="7">
         <f t="shared" si="14"/>
-        <v>951</v>
-      </c>
-      <c r="E13" s="7">
+        <v>2719</v>
+      </c>
+      <c r="AI13" s="7">
         <f t="shared" si="14"/>
-        <v>977</v>
-      </c>
-      <c r="F13" s="7">
+        <v>3289</v>
+      </c>
+      <c r="AJ13" s="7">
         <f t="shared" si="14"/>
-        <v>963</v>
-      </c>
-      <c r="G13" s="7">
+        <v>4262</v>
+      </c>
+      <c r="AK13" s="7">
         <f t="shared" si="14"/>
-        <v>1042</v>
-      </c>
-      <c r="H13" s="7">
+        <v>3837</v>
+      </c>
+      <c r="AL13" s="7">
         <f t="shared" si="14"/>
-        <v>1127</v>
-      </c>
-      <c r="I13" s="7">
+        <v>5028</v>
+      </c>
+      <c r="AM13" s="7">
         <f t="shared" si="14"/>
-        <v>1043</v>
-      </c>
-      <c r="J13" s="7">
+        <v>5325</v>
+      </c>
+      <c r="AN13" s="7">
         <f t="shared" si="14"/>
-        <v>1050</v>
-      </c>
-      <c r="K13" s="7">
-        <f t="shared" si="14"/>
-        <v>711</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="14"/>
-        <v>764</v>
-      </c>
-      <c r="M13" s="7">
-        <f t="shared" si="14"/>
-        <v>1118</v>
-      </c>
-      <c r="N13" s="7">
-        <f t="shared" si="14"/>
-        <v>1244</v>
-      </c>
-      <c r="O13" s="7">
-        <f t="shared" si="14"/>
-        <v>999</v>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="14"/>
-        <v>1133</v>
-      </c>
-      <c r="Q13" s="7">
-        <f t="shared" si="14"/>
-        <v>1168</v>
-      </c>
-      <c r="R13" s="7">
-        <f t="shared" si="14"/>
-        <v>1728</v>
-      </c>
-      <c r="S13" s="7">
-        <f t="shared" si="14"/>
-        <v>1168</v>
-      </c>
-      <c r="T13" s="7">
-        <f t="shared" ref="T13:Z13" si="15">T8-SUM(T9:T12)</f>
-        <v>1325</v>
-      </c>
-      <c r="U13" s="7">
+        <v>6065</v>
+      </c>
+      <c r="AO13" s="7">
+        <f t="shared" ref="AO13:AX13" si="15">AO8-SUM(AO9:AO12)</f>
+        <v>5399.8859999999986</v>
+      </c>
+      <c r="AP13" s="7">
         <f t="shared" si="15"/>
-        <v>1391</v>
-      </c>
-      <c r="V13" s="7">
+        <v>5530.0695199999982</v>
+      </c>
+      <c r="AQ13" s="7">
         <f t="shared" si="15"/>
-        <v>1441</v>
-      </c>
-      <c r="W13" s="7">
+        <v>5695.6586863999974</v>
+      </c>
+      <c r="AR13" s="7">
         <f t="shared" si="15"/>
-        <v>1530</v>
-      </c>
-      <c r="X13" s="7">
+        <v>5865.0895138879987</v>
+      </c>
+      <c r="AS13" s="7">
         <f t="shared" si="15"/>
-        <v>1504</v>
-      </c>
-      <c r="Y13" s="7">
+        <v>5924.7404090268774</v>
+      </c>
+      <c r="AT13" s="7">
         <f t="shared" si="15"/>
-        <v>1520</v>
-      </c>
-      <c r="Z13" s="7">
+        <v>5984.9878131171463</v>
+      </c>
+      <c r="AU13" s="7">
         <f t="shared" si="15"/>
-        <v>1429.1143999999999</v>
-      </c>
-      <c r="AC13" s="7">
-        <f t="shared" ref="AC13:AJ13" si="16">AC8-SUM(AC9:AC12)</f>
-        <v>2194</v>
-      </c>
-      <c r="AD13" s="7">
-        <f t="shared" si="16"/>
-        <v>2719</v>
-      </c>
-      <c r="AE13" s="7">
-        <f t="shared" si="16"/>
-        <v>3289</v>
-      </c>
-      <c r="AF13" s="7">
-        <f t="shared" si="16"/>
-        <v>4262</v>
-      </c>
-      <c r="AG13" s="7">
-        <f t="shared" si="16"/>
-        <v>3837</v>
-      </c>
-      <c r="AH13" s="7">
-        <f t="shared" si="16"/>
-        <v>5028</v>
-      </c>
-      <c r="AI13" s="7">
-        <f t="shared" si="16"/>
-        <v>5325</v>
-      </c>
-      <c r="AJ13" s="7">
-        <f t="shared" si="16"/>
-        <v>5983.1144000000058</v>
-      </c>
-      <c r="AK13" s="7">
-        <f t="shared" ref="AK13:AT13" si="17">AK8-SUM(AK9:AK12)</f>
-        <v>6693.3744520000018</v>
-      </c>
-      <c r="AL13" s="7">
-        <f t="shared" si="17"/>
-        <v>7193.0116116800018</v>
-      </c>
-      <c r="AM13" s="7">
-        <f t="shared" si="17"/>
-        <v>7392.7653870536024</v>
-      </c>
-      <c r="AN13" s="7">
-        <f t="shared" si="17"/>
-        <v>7597.0531733660728</v>
-      </c>
-      <c r="AO13" s="7">
-        <f t="shared" si="17"/>
-        <v>7674.0237050997357</v>
-      </c>
-      <c r="AP13" s="7">
-        <f t="shared" si="17"/>
-        <v>7751.763942150732</v>
-      </c>
-      <c r="AQ13" s="7">
-        <f t="shared" si="17"/>
-        <v>7830.2815815722388</v>
-      </c>
-      <c r="AR13" s="7">
-        <f t="shared" si="17"/>
-        <v>7909.5843973879619</v>
-      </c>
-      <c r="AS13" s="7">
-        <f t="shared" si="17"/>
-        <v>7989.6802413618425</v>
-      </c>
-      <c r="AT13" s="7">
-        <f t="shared" si="17"/>
-        <v>8070.57704377546</v>
+        <v>6045.8376912483163</v>
+      </c>
+      <c r="AV13" s="7">
+        <f t="shared" si="15"/>
+        <v>6107.2960681608001</v>
+      </c>
+      <c r="AW13" s="7">
+        <f t="shared" si="15"/>
+        <v>6169.3690288424077</v>
+      </c>
+      <c r="AX13" s="7">
+        <f t="shared" si="15"/>
+        <v>6232.0627191308322</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>32</v>
       </c>
@@ -2631,49 +2700,41 @@
         <v>-13</v>
       </c>
       <c r="Z14" s="1">
-        <v>-20</v>
-      </c>
-      <c r="AC14" s="1">
+        <v>-116</v>
+      </c>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AG14" s="1">
         <v>-182</v>
       </c>
-      <c r="AD14" s="1">
+      <c r="AH14" s="1">
         <v>-279</v>
       </c>
-      <c r="AE14" s="1">
+      <c r="AI14" s="1">
         <f>SUM(C14:F14)</f>
         <v>-1776</v>
       </c>
-      <c r="AF14" s="1">
+      <c r="AJ14" s="1">
         <f>SUM(G14:J14)</f>
         <v>163</v>
       </c>
-      <c r="AG14" s="1">
+      <c r="AK14" s="1">
         <f>SUM(K14:N14)</f>
         <v>471</v>
       </c>
-      <c r="AH14" s="1">
+      <c r="AL14" s="1">
         <f>SUM(O14:R14)</f>
         <v>-383</v>
       </c>
-      <c r="AI14" s="1">
+      <c r="AM14" s="1">
         <f>SUM(S14:V14)</f>
         <v>-4</v>
       </c>
-      <c r="AJ14" s="1">
+      <c r="AN14" s="1">
         <f>SUM(W14:Z14)</f>
-        <v>-131</v>
-      </c>
-      <c r="AK14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="1">
-        <v>0</v>
+        <v>-227</v>
       </c>
       <c r="AO14" s="1">
         <v>0</v>
@@ -2693,182 +2754,198 @@
       <c r="AT14" s="1">
         <v>0</v>
       </c>
+      <c r="AU14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:46" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:50" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15"/>
       <c r="B15" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:S15" si="18">C13-C14</f>
+        <f t="shared" ref="C15:S15" si="16">C13-C14</f>
         <v>263</v>
       </c>
       <c r="D15" s="7">
+        <f t="shared" si="16"/>
+        <v>1799</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="16"/>
+        <v>1144</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="16"/>
+        <v>1859</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="16"/>
+        <v>872</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="16"/>
+        <v>1356</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="16"/>
+        <v>1165</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="16"/>
+        <v>706</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="16"/>
+        <v>629</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="16"/>
+        <v>49</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="16"/>
+        <v>1578</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="16"/>
+        <v>1110</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" si="16"/>
+        <v>1074</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" si="16"/>
+        <v>1303</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="16"/>
+        <v>1241</v>
+      </c>
+      <c r="R15" s="7">
+        <f t="shared" si="16"/>
+        <v>1793</v>
+      </c>
+      <c r="S15" s="7">
+        <f t="shared" si="16"/>
+        <v>1209</v>
+      </c>
+      <c r="T15" s="7">
+        <f t="shared" ref="T15:Z15" si="17">T13-T14</f>
+        <v>1399</v>
+      </c>
+      <c r="U15" s="7">
+        <f t="shared" si="17"/>
+        <v>1311</v>
+      </c>
+      <c r="V15" s="7">
+        <f t="shared" si="17"/>
+        <v>1410</v>
+      </c>
+      <c r="W15" s="7">
+        <f t="shared" si="17"/>
+        <v>1603</v>
+      </c>
+      <c r="X15" s="7">
+        <f t="shared" si="17"/>
+        <v>1529</v>
+      </c>
+      <c r="Y15" s="7">
+        <f t="shared" si="17"/>
+        <v>1533</v>
+      </c>
+      <c r="Z15" s="7">
+        <f t="shared" si="17"/>
+        <v>1627</v>
+      </c>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AG15" s="7">
+        <f t="shared" ref="AG15:AN15" si="18">AG13-AG14</f>
+        <v>2376</v>
+      </c>
+      <c r="AH15" s="7">
         <f t="shared" si="18"/>
-        <v>1799</v>
-      </c>
-      <c r="E15" s="7">
+        <v>2998</v>
+      </c>
+      <c r="AI15" s="7">
         <f t="shared" si="18"/>
-        <v>1144</v>
-      </c>
-      <c r="F15" s="7">
+        <v>5065</v>
+      </c>
+      <c r="AJ15" s="7">
         <f t="shared" si="18"/>
-        <v>1859</v>
-      </c>
-      <c r="G15" s="7">
+        <v>4099</v>
+      </c>
+      <c r="AK15" s="7">
         <f t="shared" si="18"/>
-        <v>872</v>
-      </c>
-      <c r="H15" s="7">
+        <v>3366</v>
+      </c>
+      <c r="AL15" s="7">
         <f t="shared" si="18"/>
-        <v>1356</v>
-      </c>
-      <c r="I15" s="7">
+        <v>5411</v>
+      </c>
+      <c r="AM15" s="7">
         <f t="shared" si="18"/>
-        <v>1165</v>
-      </c>
-      <c r="J15" s="7">
+        <v>5329</v>
+      </c>
+      <c r="AN15" s="7">
         <f t="shared" si="18"/>
-        <v>706</v>
-      </c>
-      <c r="K15" s="7">
-        <f t="shared" si="18"/>
-        <v>629</v>
-      </c>
-      <c r="L15" s="7">
-        <f t="shared" si="18"/>
-        <v>49</v>
-      </c>
-      <c r="M15" s="7">
-        <f t="shared" si="18"/>
-        <v>1578</v>
-      </c>
-      <c r="N15" s="7">
-        <f t="shared" si="18"/>
-        <v>1110</v>
-      </c>
-      <c r="O15" s="7">
-        <f t="shared" si="18"/>
-        <v>1074</v>
-      </c>
-      <c r="P15" s="7">
-        <f t="shared" si="18"/>
-        <v>1303</v>
-      </c>
-      <c r="Q15" s="7">
-        <f t="shared" si="18"/>
-        <v>1241</v>
-      </c>
-      <c r="R15" s="7">
-        <f t="shared" si="18"/>
-        <v>1793</v>
-      </c>
-      <c r="S15" s="7">
-        <f t="shared" si="18"/>
-        <v>1209</v>
-      </c>
-      <c r="T15" s="7">
-        <f t="shared" ref="T15:Z15" si="19">T13-T14</f>
-        <v>1399</v>
-      </c>
-      <c r="U15" s="7">
+        <v>6292</v>
+      </c>
+      <c r="AO15" s="7">
+        <f t="shared" ref="AO15:AX15" si="19">AO13-AO14</f>
+        <v>5399.8859999999986</v>
+      </c>
+      <c r="AP15" s="7">
         <f t="shared" si="19"/>
-        <v>1311</v>
-      </c>
-      <c r="V15" s="7">
+        <v>5530.0695199999982</v>
+      </c>
+      <c r="AQ15" s="7">
         <f t="shared" si="19"/>
-        <v>1410</v>
-      </c>
-      <c r="W15" s="7">
+        <v>5695.6586863999974</v>
+      </c>
+      <c r="AR15" s="7">
         <f t="shared" si="19"/>
-        <v>1603</v>
-      </c>
-      <c r="X15" s="7">
+        <v>5865.0895138879987</v>
+      </c>
+      <c r="AS15" s="7">
         <f t="shared" si="19"/>
-        <v>1529</v>
-      </c>
-      <c r="Y15" s="7">
+        <v>5924.7404090268774</v>
+      </c>
+      <c r="AT15" s="7">
         <f t="shared" si="19"/>
-        <v>1533</v>
-      </c>
-      <c r="Z15" s="7">
+        <v>5984.9878131171463</v>
+      </c>
+      <c r="AU15" s="7">
         <f t="shared" si="19"/>
-        <v>1449.1143999999999</v>
-      </c>
-      <c r="AC15" s="7">
-        <f t="shared" ref="AC15:AJ15" si="20">AC13-AC14</f>
-        <v>2376</v>
-      </c>
-      <c r="AD15" s="7">
-        <f t="shared" si="20"/>
-        <v>2998</v>
-      </c>
-      <c r="AE15" s="7">
-        <f t="shared" si="20"/>
-        <v>5065</v>
-      </c>
-      <c r="AF15" s="7">
-        <f t="shared" si="20"/>
-        <v>4099</v>
-      </c>
-      <c r="AG15" s="7">
-        <f t="shared" si="20"/>
-        <v>3366</v>
-      </c>
-      <c r="AH15" s="7">
-        <f t="shared" si="20"/>
-        <v>5411</v>
-      </c>
-      <c r="AI15" s="7">
-        <f t="shared" si="20"/>
-        <v>5329</v>
-      </c>
-      <c r="AJ15" s="7">
-        <f t="shared" si="20"/>
-        <v>6114.1144000000058</v>
-      </c>
-      <c r="AK15" s="7">
-        <f t="shared" ref="AK15:AT15" si="21">AK13-AK14</f>
-        <v>6693.3744520000018</v>
-      </c>
-      <c r="AL15" s="7">
-        <f t="shared" si="21"/>
-        <v>7193.0116116800018</v>
-      </c>
-      <c r="AM15" s="7">
-        <f t="shared" si="21"/>
-        <v>7392.7653870536024</v>
-      </c>
-      <c r="AN15" s="7">
-        <f t="shared" si="21"/>
-        <v>7597.0531733660728</v>
-      </c>
-      <c r="AO15" s="7">
-        <f t="shared" si="21"/>
-        <v>7674.0237050997357</v>
-      </c>
-      <c r="AP15" s="7">
-        <f t="shared" si="21"/>
-        <v>7751.763942150732</v>
-      </c>
-      <c r="AQ15" s="7">
-        <f t="shared" si="21"/>
-        <v>7830.2815815722388</v>
-      </c>
-      <c r="AR15" s="7">
-        <f t="shared" si="21"/>
-        <v>7909.5843973879619</v>
-      </c>
-      <c r="AS15" s="7">
-        <f t="shared" si="21"/>
-        <v>7989.6802413618425</v>
-      </c>
-      <c r="AT15" s="7">
-        <f t="shared" si="21"/>
-        <v>8070.57704377546</v>
+        <v>6045.8376912483163</v>
+      </c>
+      <c r="AV15" s="7">
+        <f t="shared" si="19"/>
+        <v>6107.2960681608001</v>
+      </c>
+      <c r="AW15" s="7">
+        <f t="shared" si="19"/>
+        <v>6169.3690288424077</v>
+      </c>
+      <c r="AX15" s="7">
+        <f t="shared" si="19"/>
+        <v>6232.0627191308322</v>
       </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>34</v>
       </c>
@@ -2942,655 +3019,662 @@
         <v>285</v>
       </c>
       <c r="Z16" s="1">
-        <f t="shared" ref="Z16" si="22">Z15*0.2</f>
-        <v>289.82288</v>
-      </c>
-      <c r="AC16" s="1">
+        <v>190</v>
+      </c>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AG16" s="1">
         <v>319</v>
       </c>
-      <c r="AD16" s="1">
+      <c r="AH16" s="1">
         <v>539</v>
       </c>
-      <c r="AE16" s="1">
+      <c r="AI16" s="1">
         <f>SUM(C16:F16)</f>
         <v>863</v>
       </c>
-      <c r="AF16" s="1">
+      <c r="AJ16" s="1">
         <f>SUM(G16:J16)</f>
         <v>-70</v>
       </c>
-      <c r="AG16" s="1">
+      <c r="AK16" s="1">
         <f>SUM(K16:N16)</f>
         <v>947</v>
       </c>
-      <c r="AH16" s="1">
+      <c r="AL16" s="1">
         <f>SUM(O16:R16)</f>
         <v>1165</v>
       </c>
-      <c r="AI16" s="1">
+      <c r="AM16" s="1">
         <f>SUM(S16:V16)</f>
         <v>1182</v>
       </c>
-      <c r="AJ16" s="1">
+      <c r="AN16" s="1">
         <f>SUM(W16:Z16)</f>
-        <v>1158.8228799999999</v>
-      </c>
-      <c r="AK16" s="1">
-        <f>AK15*0.2</f>
-        <v>1338.6748904000005</v>
-      </c>
-      <c r="AL16" s="1">
-        <f t="shared" ref="AL16:AT16" si="23">AL15*0.2</f>
-        <v>1438.6023223360005</v>
-      </c>
-      <c r="AM16" s="1">
-        <f t="shared" si="23"/>
-        <v>1478.5530774107206</v>
-      </c>
-      <c r="AN16" s="1">
-        <f t="shared" si="23"/>
-        <v>1519.4106346732146</v>
+        <v>1059</v>
       </c>
       <c r="AO16" s="1">
-        <f t="shared" si="23"/>
-        <v>1534.8047410199472</v>
+        <f>AO15*0.2</f>
+        <v>1079.9771999999998</v>
       </c>
       <c r="AP16" s="1">
-        <f t="shared" si="23"/>
-        <v>1550.3527884301466</v>
+        <f t="shared" ref="AP16:AX16" si="20">AP15*0.2</f>
+        <v>1106.0139039999997</v>
       </c>
       <c r="AQ16" s="1">
-        <f t="shared" si="23"/>
-        <v>1566.0563163144479</v>
+        <f t="shared" si="20"/>
+        <v>1139.1317372799995</v>
       </c>
       <c r="AR16" s="1">
-        <f t="shared" si="23"/>
-        <v>1581.9168794775924</v>
+        <f t="shared" si="20"/>
+        <v>1173.0179027775998</v>
       </c>
       <c r="AS16" s="1">
-        <f t="shared" si="23"/>
-        <v>1597.9360482723687</v>
+        <f t="shared" si="20"/>
+        <v>1184.9480818053755</v>
       </c>
       <c r="AT16" s="1">
-        <f t="shared" si="23"/>
-        <v>1614.1154087550922</v>
+        <f t="shared" si="20"/>
+        <v>1196.9975626234293</v>
+      </c>
+      <c r="AU16" s="1">
+        <f t="shared" si="20"/>
+        <v>1209.1675382496633</v>
+      </c>
+      <c r="AV16" s="1">
+        <f t="shared" si="20"/>
+        <v>1221.4592136321601</v>
+      </c>
+      <c r="AW16" s="1">
+        <f t="shared" si="20"/>
+        <v>1233.8738057684816</v>
+      </c>
+      <c r="AX16" s="1">
+        <f t="shared" si="20"/>
+        <v>1246.4125438261665</v>
       </c>
     </row>
-    <row r="17" spans="1:146" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:150" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17"/>
       <c r="B17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:S17" si="24">C15-C16</f>
+        <f t="shared" ref="C17:S17" si="21">C15-C16</f>
         <v>84</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="21"/>
+        <v>1530</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="21"/>
+        <v>1021</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="21"/>
+        <v>1567</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="21"/>
+        <v>1097</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="21"/>
+        <v>1184</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="21"/>
+        <v>1087</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="21"/>
+        <v>801</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="21"/>
+        <v>509</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="21"/>
+        <v>-341</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" si="21"/>
+        <v>1330</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="21"/>
+        <v>921</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="21"/>
+        <v>795</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="21"/>
+        <v>1029</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="21"/>
+        <v>1020</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="21"/>
+        <v>1402</v>
+      </c>
+      <c r="S17" s="7">
+        <f t="shared" si="21"/>
+        <v>888</v>
+      </c>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:V17" si="22">T15-T16</f>
+        <v>1128</v>
+      </c>
+      <c r="U17" s="7">
+        <f t="shared" si="22"/>
+        <v>1010</v>
+      </c>
+      <c r="V17" s="7">
+        <f t="shared" si="22"/>
+        <v>1121</v>
+      </c>
+      <c r="W17" s="7">
+        <f t="shared" ref="W17:Z17" si="23">W15-W16</f>
+        <v>1287</v>
+      </c>
+      <c r="X17" s="7">
+        <f t="shared" si="23"/>
+        <v>1261</v>
+      </c>
+      <c r="Y17" s="7">
+        <f t="shared" si="23"/>
+        <v>1248</v>
+      </c>
+      <c r="Z17" s="7">
+        <f t="shared" si="23"/>
+        <v>1437</v>
+      </c>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AG17" s="7">
+        <f t="shared" ref="AG17:AN17" si="24">AG15-AG16</f>
+        <v>2057</v>
+      </c>
+      <c r="AH17" s="7">
         <f t="shared" si="24"/>
-        <v>1530</v>
-      </c>
-      <c r="E17" s="7">
+        <v>2459</v>
+      </c>
+      <c r="AI17" s="7">
         <f t="shared" si="24"/>
-        <v>1021</v>
-      </c>
-      <c r="F17" s="7">
+        <v>4202</v>
+      </c>
+      <c r="AJ17" s="7">
         <f t="shared" si="24"/>
-        <v>1567</v>
-      </c>
-      <c r="G17" s="7">
+        <v>4169</v>
+      </c>
+      <c r="AK17" s="7">
         <f t="shared" si="24"/>
-        <v>1097</v>
-      </c>
-      <c r="H17" s="7">
+        <v>2419</v>
+      </c>
+      <c r="AL17" s="7">
         <f t="shared" si="24"/>
-        <v>1184</v>
-      </c>
-      <c r="I17" s="7">
+        <v>4246</v>
+      </c>
+      <c r="AM17" s="7">
         <f t="shared" si="24"/>
-        <v>1087</v>
-      </c>
-      <c r="J17" s="7">
+        <v>4147</v>
+      </c>
+      <c r="AN17" s="7">
         <f t="shared" si="24"/>
-        <v>801</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" si="24"/>
-        <v>509</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="24"/>
-        <v>-341</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" si="24"/>
-        <v>1330</v>
-      </c>
-      <c r="N17" s="7">
-        <f t="shared" si="24"/>
-        <v>921</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" si="24"/>
-        <v>795</v>
-      </c>
-      <c r="P17" s="7">
-        <f t="shared" si="24"/>
-        <v>1029</v>
-      </c>
-      <c r="Q17" s="7">
-        <f t="shared" si="24"/>
-        <v>1020</v>
-      </c>
-      <c r="R17" s="7">
-        <f t="shared" si="24"/>
-        <v>1402</v>
-      </c>
-      <c r="S17" s="7">
-        <f t="shared" si="24"/>
-        <v>888</v>
-      </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:V17" si="25">T15-T16</f>
-        <v>1128</v>
-      </c>
-      <c r="U17" s="7">
+        <v>5233</v>
+      </c>
+      <c r="AO17" s="7">
+        <f t="shared" ref="AO17:AX17" si="25">AO15-AO16</f>
+        <v>4319.9087999999992</v>
+      </c>
+      <c r="AP17" s="7">
         <f t="shared" si="25"/>
-        <v>1010</v>
-      </c>
-      <c r="V17" s="7">
+        <v>4424.0556159999987</v>
+      </c>
+      <c r="AQ17" s="7">
         <f t="shared" si="25"/>
-        <v>1121</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" ref="W17:Z17" si="26">W15-W16</f>
-        <v>1287</v>
-      </c>
-      <c r="X17" s="7">
-        <f t="shared" si="26"/>
-        <v>1261</v>
-      </c>
-      <c r="Y17" s="7">
-        <f t="shared" si="26"/>
-        <v>1248</v>
-      </c>
-      <c r="Z17" s="7">
-        <f t="shared" si="26"/>
-        <v>1159.29152</v>
-      </c>
-      <c r="AC17" s="7">
-        <f t="shared" ref="AC17:AJ17" si="27">AC15-AC16</f>
-        <v>2057</v>
-      </c>
-      <c r="AD17" s="7">
+        <v>4556.5269491199979</v>
+      </c>
+      <c r="AR17" s="7">
+        <f t="shared" si="25"/>
+        <v>4692.0716111103993</v>
+      </c>
+      <c r="AS17" s="7">
+        <f t="shared" si="25"/>
+        <v>4739.7923272215021</v>
+      </c>
+      <c r="AT17" s="7">
+        <f t="shared" si="25"/>
+        <v>4787.9902504937172</v>
+      </c>
+      <c r="AU17" s="7">
+        <f t="shared" si="25"/>
+        <v>4836.6701529986531</v>
+      </c>
+      <c r="AV17" s="7">
+        <f t="shared" si="25"/>
+        <v>4885.8368545286403</v>
+      </c>
+      <c r="AW17" s="7">
+        <f t="shared" si="25"/>
+        <v>4935.4952230739264</v>
+      </c>
+      <c r="AX17" s="7">
+        <f t="shared" si="25"/>
+        <v>4985.6501753046659</v>
+      </c>
+      <c r="AY17" s="6">
+        <f>AX17*(1+$BB$22)</f>
+        <v>4935.7936735516196</v>
+      </c>
+      <c r="AZ17" s="6">
+        <f t="shared" ref="AZ17:DK17" si="26">AY17*(1+$BB$22)</f>
+        <v>4886.4357368161036</v>
+      </c>
+      <c r="BA17" s="6">
+        <f t="shared" si="26"/>
+        <v>4837.5713794479425</v>
+      </c>
+      <c r="BB17" s="6">
+        <f t="shared" si="26"/>
+        <v>4789.195665653463</v>
+      </c>
+      <c r="BC17" s="6">
+        <f t="shared" si="26"/>
+        <v>4741.3037089969284</v>
+      </c>
+      <c r="BD17" s="6">
+        <f t="shared" si="26"/>
+        <v>4693.8906719069591</v>
+      </c>
+      <c r="BE17" s="6">
+        <f t="shared" si="26"/>
+        <v>4646.9517651878896</v>
+      </c>
+      <c r="BF17" s="6">
+        <f t="shared" si="26"/>
+        <v>4600.4822475360106</v>
+      </c>
+      <c r="BG17" s="6">
+        <f t="shared" si="26"/>
+        <v>4554.4774250606506</v>
+      </c>
+      <c r="BH17" s="6">
+        <f t="shared" si="26"/>
+        <v>4508.9326508100439</v>
+      </c>
+      <c r="BI17" s="6">
+        <f t="shared" si="26"/>
+        <v>4463.8433243019435</v>
+      </c>
+      <c r="BJ17" s="6">
+        <f t="shared" si="26"/>
+        <v>4419.2048910589237</v>
+      </c>
+      <c r="BK17" s="6">
+        <f t="shared" si="26"/>
+        <v>4375.0128421483341</v>
+      </c>
+      <c r="BL17" s="6">
+        <f t="shared" si="26"/>
+        <v>4331.262713726851</v>
+      </c>
+      <c r="BM17" s="6">
+        <f t="shared" si="26"/>
+        <v>4287.9500865895825</v>
+      </c>
+      <c r="BN17" s="6">
+        <f t="shared" si="26"/>
+        <v>4245.0705857236862</v>
+      </c>
+      <c r="BO17" s="6">
+        <f t="shared" si="26"/>
+        <v>4202.6198798664491</v>
+      </c>
+      <c r="BP17" s="6">
+        <f t="shared" si="26"/>
+        <v>4160.5936810677849</v>
+      </c>
+      <c r="BQ17" s="6">
+        <f t="shared" si="26"/>
+        <v>4118.9877442571069</v>
+      </c>
+      <c r="BR17" s="6">
+        <f t="shared" si="26"/>
+        <v>4077.7978668145356</v>
+      </c>
+      <c r="BS17" s="6">
+        <f t="shared" si="26"/>
+        <v>4037.0198881463903</v>
+      </c>
+      <c r="BT17" s="6">
+        <f t="shared" si="26"/>
+        <v>3996.6496892649261</v>
+      </c>
+      <c r="BU17" s="6">
+        <f t="shared" si="26"/>
+        <v>3956.6831923722766</v>
+      </c>
+      <c r="BV17" s="6">
+        <f t="shared" si="26"/>
+        <v>3917.1163604485537</v>
+      </c>
+      <c r="BW17" s="6">
+        <f t="shared" si="26"/>
+        <v>3877.9451968440681</v>
+      </c>
+      <c r="BX17" s="6">
+        <f t="shared" si="26"/>
+        <v>3839.1657448756273</v>
+      </c>
+      <c r="BY17" s="6">
+        <f t="shared" si="26"/>
+        <v>3800.7740874268711</v>
+      </c>
+      <c r="BZ17" s="6">
+        <f t="shared" si="26"/>
+        <v>3762.7663465526025</v>
+      </c>
+      <c r="CA17" s="6">
+        <f t="shared" si="26"/>
+        <v>3725.1386830870765</v>
+      </c>
+      <c r="CB17" s="6">
+        <f t="shared" si="26"/>
+        <v>3687.8872962562059</v>
+      </c>
+      <c r="CC17" s="6">
+        <f t="shared" si="26"/>
+        <v>3651.0084232936438</v>
+      </c>
+      <c r="CD17" s="6">
+        <f t="shared" si="26"/>
+        <v>3614.4983390607072</v>
+      </c>
+      <c r="CE17" s="6">
+        <f t="shared" si="26"/>
+        <v>3578.3533556701</v>
+      </c>
+      <c r="CF17" s="6">
+        <f t="shared" si="26"/>
+        <v>3542.5698221133989</v>
+      </c>
+      <c r="CG17" s="6">
+        <f t="shared" si="26"/>
+        <v>3507.1441238922648</v>
+      </c>
+      <c r="CH17" s="6">
+        <f t="shared" si="26"/>
+        <v>3472.0726826533423</v>
+      </c>
+      <c r="CI17" s="6">
+        <f t="shared" si="26"/>
+        <v>3437.351955826809</v>
+      </c>
+      <c r="CJ17" s="6">
+        <f t="shared" si="26"/>
+        <v>3402.9784362685409</v>
+      </c>
+      <c r="CK17" s="6">
+        <f t="shared" si="26"/>
+        <v>3368.9486519058555</v>
+      </c>
+      <c r="CL17" s="6">
+        <f t="shared" si="26"/>
+        <v>3335.2591653867971</v>
+      </c>
+      <c r="CM17" s="6">
+        <f t="shared" si="26"/>
+        <v>3301.9065737329292</v>
+      </c>
+      <c r="CN17" s="6">
+        <f t="shared" si="26"/>
+        <v>3268.8875079956001</v>
+      </c>
+      <c r="CO17" s="6">
+        <f t="shared" si="26"/>
+        <v>3236.1986329156439</v>
+      </c>
+      <c r="CP17" s="6">
+        <f t="shared" si="26"/>
+        <v>3203.8366465864874</v>
+      </c>
+      <c r="CQ17" s="6">
+        <f t="shared" si="26"/>
+        <v>3171.7982801206226</v>
+      </c>
+      <c r="CR17" s="6">
+        <f t="shared" si="26"/>
+        <v>3140.0802973194163</v>
+      </c>
+      <c r="CS17" s="6">
+        <f t="shared" si="26"/>
+        <v>3108.6794943462223</v>
+      </c>
+      <c r="CT17" s="6">
+        <f t="shared" si="26"/>
+        <v>3077.59269940276</v>
+      </c>
+      <c r="CU17" s="6">
+        <f t="shared" si="26"/>
+        <v>3046.8167724087325</v>
+      </c>
+      <c r="CV17" s="6">
+        <f t="shared" si="26"/>
+        <v>3016.3486046846451</v>
+      </c>
+      <c r="CW17" s="6">
+        <f t="shared" si="26"/>
+        <v>2986.1851186377985</v>
+      </c>
+      <c r="CX17" s="6">
+        <f t="shared" si="26"/>
+        <v>2956.3232674514206</v>
+      </c>
+      <c r="CY17" s="6">
+        <f t="shared" si="26"/>
+        <v>2926.7600347769062</v>
+      </c>
+      <c r="CZ17" s="6">
+        <f t="shared" si="26"/>
+        <v>2897.4924344291371</v>
+      </c>
+      <c r="DA17" s="6">
+        <f t="shared" si="26"/>
+        <v>2868.5175100848455</v>
+      </c>
+      <c r="DB17" s="6">
+        <f t="shared" si="26"/>
+        <v>2839.832334983997</v>
+      </c>
+      <c r="DC17" s="6">
+        <f t="shared" si="26"/>
+        <v>2811.4340116341568</v>
+      </c>
+      <c r="DD17" s="6">
+        <f t="shared" si="26"/>
+        <v>2783.3196715178151</v>
+      </c>
+      <c r="DE17" s="6">
+        <f t="shared" si="26"/>
+        <v>2755.4864748026371</v>
+      </c>
+      <c r="DF17" s="6">
+        <f t="shared" si="26"/>
+        <v>2727.9316100546107</v>
+      </c>
+      <c r="DG17" s="6">
+        <f t="shared" si="26"/>
+        <v>2700.6522939540646</v>
+      </c>
+      <c r="DH17" s="6">
+        <f t="shared" si="26"/>
+        <v>2673.6457710145241</v>
+      </c>
+      <c r="DI17" s="6">
+        <f t="shared" si="26"/>
+        <v>2646.9093133043789</v>
+      </c>
+      <c r="DJ17" s="6">
+        <f t="shared" si="26"/>
+        <v>2620.4402201713351</v>
+      </c>
+      <c r="DK17" s="6">
+        <f t="shared" si="26"/>
+        <v>2594.2358179696216</v>
+      </c>
+      <c r="DL17" s="6">
+        <f t="shared" ref="DL17:ET17" si="27">DK17*(1+$BB$22)</f>
+        <v>2568.2934597899252</v>
+      </c>
+      <c r="DM17" s="6">
         <f t="shared" si="27"/>
-        <v>2459</v>
-      </c>
-      <c r="AE17" s="7">
+        <v>2542.6105251920258</v>
+      </c>
+      <c r="DN17" s="6">
         <f t="shared" si="27"/>
-        <v>4202</v>
-      </c>
-      <c r="AF17" s="7">
+        <v>2517.1844199401053</v>
+      </c>
+      <c r="DO17" s="6">
         <f t="shared" si="27"/>
-        <v>4169</v>
-      </c>
-      <c r="AG17" s="7">
+        <v>2492.0125757407041</v>
+      </c>
+      <c r="DP17" s="6">
         <f t="shared" si="27"/>
-        <v>2419</v>
-      </c>
-      <c r="AH17" s="7">
+        <v>2467.0924499832968</v>
+      </c>
+      <c r="DQ17" s="6">
         <f t="shared" si="27"/>
-        <v>4246</v>
-      </c>
-      <c r="AI17" s="7">
+        <v>2442.4215254834639</v>
+      </c>
+      <c r="DR17" s="6">
         <f t="shared" si="27"/>
-        <v>4147</v>
-      </c>
-      <c r="AJ17" s="7">
+        <v>2417.9973102286294</v>
+      </c>
+      <c r="DS17" s="6">
         <f t="shared" si="27"/>
-        <v>4955.2915200000061</v>
-      </c>
-      <c r="AK17" s="7">
-        <f t="shared" ref="AK17:AT17" si="28">AK15-AK16</f>
-        <v>5354.6995616000013</v>
-      </c>
-      <c r="AL17" s="7">
-        <f t="shared" si="28"/>
-        <v>5754.4092893440011</v>
-      </c>
-      <c r="AM17" s="7">
-        <f t="shared" si="28"/>
-        <v>5914.2123096428822</v>
-      </c>
-      <c r="AN17" s="7">
-        <f t="shared" si="28"/>
-        <v>6077.6425386928586</v>
-      </c>
-      <c r="AO17" s="7">
-        <f t="shared" si="28"/>
-        <v>6139.2189640797887</v>
-      </c>
-      <c r="AP17" s="7">
-        <f t="shared" si="28"/>
-        <v>6201.4111537205854</v>
-      </c>
-      <c r="AQ17" s="7">
-        <f t="shared" si="28"/>
-        <v>6264.2252652577909</v>
-      </c>
-      <c r="AR17" s="7">
-        <f t="shared" si="28"/>
-        <v>6327.6675179103695</v>
-      </c>
-      <c r="AS17" s="7">
-        <f t="shared" si="28"/>
-        <v>6391.7441930894738</v>
-      </c>
-      <c r="AT17" s="7">
-        <f t="shared" si="28"/>
-        <v>6456.4616350203678</v>
-      </c>
-      <c r="AU17" s="6">
-        <f>AT17*(1+$AX$22)</f>
-        <v>6391.8970186701645</v>
-      </c>
-      <c r="AV17" s="6">
-        <f t="shared" ref="AV17:DG17" si="29">AU17*(1+$AX$22)</f>
-        <v>6327.9780484834628</v>
-      </c>
-      <c r="AW17" s="6">
-        <f t="shared" si="29"/>
-        <v>6264.6982679986277</v>
-      </c>
-      <c r="AX17" s="6">
-        <f t="shared" si="29"/>
-        <v>6202.051285318641</v>
-      </c>
-      <c r="AY17" s="6">
-        <f t="shared" si="29"/>
-        <v>6140.0307724654549</v>
-      </c>
-      <c r="AZ17" s="6">
-        <f t="shared" si="29"/>
-        <v>6078.6304647408006</v>
-      </c>
-      <c r="BA17" s="6">
-        <f t="shared" si="29"/>
-        <v>6017.8441600933929</v>
-      </c>
-      <c r="BB17" s="6">
-        <f t="shared" si="29"/>
-        <v>5957.6657184924588</v>
-      </c>
-      <c r="BC17" s="6">
-        <f t="shared" si="29"/>
-        <v>5898.0890613075344</v>
-      </c>
-      <c r="BD17" s="6">
-        <f t="shared" si="29"/>
-        <v>5839.1081706944587</v>
-      </c>
-      <c r="BE17" s="6">
-        <f t="shared" si="29"/>
-        <v>5780.7170889875142</v>
-      </c>
-      <c r="BF17" s="6">
-        <f t="shared" si="29"/>
-        <v>5722.9099180976391</v>
-      </c>
-      <c r="BG17" s="6">
-        <f t="shared" si="29"/>
-        <v>5665.6808189166622</v>
-      </c>
-      <c r="BH17" s="6">
-        <f t="shared" si="29"/>
-        <v>5609.0240107274958</v>
-      </c>
-      <c r="BI17" s="6">
-        <f t="shared" si="29"/>
-        <v>5552.9337706202205</v>
-      </c>
-      <c r="BJ17" s="6">
-        <f t="shared" si="29"/>
-        <v>5497.4044329140179</v>
-      </c>
-      <c r="BK17" s="6">
-        <f t="shared" si="29"/>
-        <v>5442.4303885848776</v>
-      </c>
-      <c r="BL17" s="6">
-        <f t="shared" si="29"/>
-        <v>5388.0060846990291</v>
-      </c>
-      <c r="BM17" s="6">
-        <f t="shared" si="29"/>
-        <v>5334.126023852039</v>
-      </c>
-      <c r="BN17" s="6">
-        <f t="shared" si="29"/>
-        <v>5280.7847636135184</v>
-      </c>
-      <c r="BO17" s="6">
-        <f t="shared" si="29"/>
-        <v>5227.9769159773832</v>
-      </c>
-      <c r="BP17" s="6">
-        <f t="shared" si="29"/>
-        <v>5175.6971468176089</v>
-      </c>
-      <c r="BQ17" s="6">
-        <f t="shared" si="29"/>
-        <v>5123.940175349433</v>
-      </c>
-      <c r="BR17" s="6">
-        <f t="shared" si="29"/>
-        <v>5072.7007735959387</v>
-      </c>
-      <c r="BS17" s="6">
-        <f t="shared" si="29"/>
-        <v>5021.9737658599797</v>
-      </c>
-      <c r="BT17" s="6">
-        <f t="shared" si="29"/>
-        <v>4971.7540282013797</v>
-      </c>
-      <c r="BU17" s="6">
-        <f t="shared" si="29"/>
-        <v>4922.0364879193658</v>
-      </c>
-      <c r="BV17" s="6">
-        <f t="shared" si="29"/>
-        <v>4872.816123040172</v>
-      </c>
-      <c r="BW17" s="6">
-        <f t="shared" si="29"/>
-        <v>4824.0879618097706</v>
-      </c>
-      <c r="BX17" s="6">
-        <f t="shared" si="29"/>
-        <v>4775.8470821916726</v>
-      </c>
-      <c r="BY17" s="6">
-        <f t="shared" si="29"/>
-        <v>4728.0886113697561</v>
-      </c>
-      <c r="BZ17" s="6">
-        <f t="shared" si="29"/>
-        <v>4680.8077252560588</v>
-      </c>
-      <c r="CA17" s="6">
-        <f t="shared" si="29"/>
-        <v>4633.9996480034979</v>
-      </c>
-      <c r="CB17" s="6">
-        <f t="shared" si="29"/>
-        <v>4587.6596515234633</v>
-      </c>
-      <c r="CC17" s="6">
-        <f t="shared" si="29"/>
-        <v>4541.783055008229</v>
-      </c>
-      <c r="CD17" s="6">
-        <f t="shared" si="29"/>
-        <v>4496.3652244581463</v>
-      </c>
-      <c r="CE17" s="6">
-        <f t="shared" si="29"/>
-        <v>4451.4015722135646</v>
-      </c>
-      <c r="CF17" s="6">
-        <f t="shared" si="29"/>
-        <v>4406.8875564914288</v>
-      </c>
-      <c r="CG17" s="6">
-        <f t="shared" si="29"/>
-        <v>4362.8186809265144</v>
-      </c>
-      <c r="CH17" s="6">
-        <f t="shared" si="29"/>
-        <v>4319.1904941172488</v>
-      </c>
-      <c r="CI17" s="6">
-        <f t="shared" si="29"/>
-        <v>4275.9985891760762</v>
-      </c>
-      <c r="CJ17" s="6">
-        <f t="shared" si="29"/>
-        <v>4233.2386032843151</v>
-      </c>
-      <c r="CK17" s="6">
-        <f t="shared" si="29"/>
-        <v>4190.9062172514723</v>
-      </c>
-      <c r="CL17" s="6">
-        <f t="shared" si="29"/>
-        <v>4148.9971550789578</v>
-      </c>
-      <c r="CM17" s="6">
-        <f t="shared" si="29"/>
-        <v>4107.5071835281678</v>
-      </c>
-      <c r="CN17" s="6">
-        <f t="shared" si="29"/>
-        <v>4066.4321116928863</v>
-      </c>
-      <c r="CO17" s="6">
-        <f t="shared" si="29"/>
-        <v>4025.7677905759574</v>
-      </c>
-      <c r="CP17" s="6">
-        <f t="shared" si="29"/>
-        <v>3985.5101126701979</v>
-      </c>
-      <c r="CQ17" s="6">
-        <f t="shared" si="29"/>
-        <v>3945.6550115434961</v>
-      </c>
-      <c r="CR17" s="6">
-        <f t="shared" si="29"/>
-        <v>3906.1984614280609</v>
-      </c>
-      <c r="CS17" s="6">
-        <f t="shared" si="29"/>
-        <v>3867.1364768137801</v>
-      </c>
-      <c r="CT17" s="6">
-        <f t="shared" si="29"/>
-        <v>3828.4651120456424</v>
-      </c>
-      <c r="CU17" s="6">
-        <f t="shared" si="29"/>
-        <v>3790.1804609251858</v>
-      </c>
-      <c r="CV17" s="6">
-        <f t="shared" si="29"/>
-        <v>3752.2786563159339</v>
-      </c>
-      <c r="CW17" s="6">
-        <f t="shared" si="29"/>
-        <v>3714.7558697527743</v>
-      </c>
-      <c r="CX17" s="6">
-        <f t="shared" si="29"/>
-        <v>3677.6083110552463</v>
-      </c>
-      <c r="CY17" s="6">
-        <f t="shared" si="29"/>
-        <v>3640.8322279446938</v>
-      </c>
-      <c r="CZ17" s="6">
-        <f t="shared" si="29"/>
-        <v>3604.4239056652468</v>
-      </c>
-      <c r="DA17" s="6">
-        <f t="shared" si="29"/>
-        <v>3568.3796666085941</v>
-      </c>
-      <c r="DB17" s="6">
-        <f t="shared" si="29"/>
-        <v>3532.6958699425081</v>
-      </c>
-      <c r="DC17" s="6">
-        <f t="shared" si="29"/>
-        <v>3497.3689112430829</v>
-      </c>
-      <c r="DD17" s="6">
-        <f t="shared" si="29"/>
-        <v>3462.3952221306522</v>
-      </c>
-      <c r="DE17" s="6">
-        <f t="shared" si="29"/>
-        <v>3427.7712699093458</v>
-      </c>
-      <c r="DF17" s="6">
-        <f t="shared" si="29"/>
-        <v>3393.4935572102522</v>
-      </c>
-      <c r="DG17" s="6">
-        <f t="shared" si="29"/>
-        <v>3359.5586216381498</v>
-      </c>
-      <c r="DH17" s="6">
-        <f t="shared" ref="DH17:EP17" si="30">DG17*(1+$AX$22)</f>
-        <v>3325.9630354217684</v>
-      </c>
-      <c r="DI17" s="6">
-        <f t="shared" si="30"/>
-        <v>3292.7034050675506</v>
-      </c>
-      <c r="DJ17" s="6">
-        <f t="shared" si="30"/>
-        <v>3259.7763710168751</v>
-      </c>
-      <c r="DK17" s="6">
-        <f t="shared" si="30"/>
-        <v>3227.1786073067065</v>
-      </c>
-      <c r="DL17" s="6">
-        <f t="shared" si="30"/>
-        <v>3194.9068212336392</v>
-      </c>
-      <c r="DM17" s="6">
-        <f t="shared" si="30"/>
-        <v>3162.9577530213028</v>
-      </c>
-      <c r="DN17" s="6">
-        <f t="shared" si="30"/>
-        <v>3131.3281754910895</v>
-      </c>
-      <c r="DO17" s="6">
-        <f t="shared" si="30"/>
-        <v>3100.0148937361787</v>
-      </c>
-      <c r="DP17" s="6">
-        <f t="shared" si="30"/>
-        <v>3069.014744798817</v>
-      </c>
-      <c r="DQ17" s="6">
-        <f t="shared" si="30"/>
-        <v>3038.3245973508288</v>
-      </c>
-      <c r="DR17" s="6">
-        <f t="shared" si="30"/>
-        <v>3007.9413513773206</v>
-      </c>
-      <c r="DS17" s="6">
-        <f t="shared" si="30"/>
-        <v>2977.8619378635476</v>
+        <v>2393.8173371263433</v>
       </c>
       <c r="DT17" s="6">
-        <f t="shared" si="30"/>
-        <v>2948.0833184849121</v>
+        <f t="shared" si="27"/>
+        <v>2369.8791637550798</v>
       </c>
       <c r="DU17" s="6">
-        <f t="shared" si="30"/>
-        <v>2918.6024853000631</v>
+        <f t="shared" si="27"/>
+        <v>2346.1803721175288</v>
       </c>
       <c r="DV17" s="6">
-        <f t="shared" si="30"/>
-        <v>2889.4164604470625</v>
+        <f t="shared" si="27"/>
+        <v>2322.7185683963535</v>
       </c>
       <c r="DW17" s="6">
-        <f t="shared" si="30"/>
-        <v>2860.522295842592</v>
+        <f t="shared" si="27"/>
+        <v>2299.4913827123901</v>
       </c>
       <c r="DX17" s="6">
-        <f t="shared" si="30"/>
-        <v>2831.9170728841659</v>
+        <f t="shared" si="27"/>
+        <v>2276.496468885266</v>
       </c>
       <c r="DY17" s="6">
-        <f t="shared" si="30"/>
-        <v>2803.5979021553244</v>
+        <f t="shared" si="27"/>
+        <v>2253.7315041964134</v>
       </c>
       <c r="DZ17" s="6">
-        <f t="shared" si="30"/>
-        <v>2775.561923133771</v>
+        <f t="shared" si="27"/>
+        <v>2231.1941891544493</v>
       </c>
       <c r="EA17" s="6">
-        <f t="shared" si="30"/>
-        <v>2747.8063039024332</v>
+        <f t="shared" si="27"/>
+        <v>2208.8822472629049</v>
       </c>
       <c r="EB17" s="6">
-        <f t="shared" si="30"/>
-        <v>2720.3282408634091</v>
+        <f t="shared" si="27"/>
+        <v>2186.7934247902758</v>
       </c>
       <c r="EC17" s="6">
-        <f t="shared" si="30"/>
-        <v>2693.124958454775</v>
+        <f t="shared" si="27"/>
+        <v>2164.9254905423732</v>
       </c>
       <c r="ED17" s="6">
-        <f t="shared" si="30"/>
-        <v>2666.1937088702271</v>
+        <f t="shared" si="27"/>
+        <v>2143.2762356369494</v>
       </c>
       <c r="EE17" s="6">
-        <f t="shared" si="30"/>
-        <v>2639.5317717815246</v>
+        <f t="shared" si="27"/>
+        <v>2121.8434732805799</v>
       </c>
       <c r="EF17" s="6">
-        <f t="shared" si="30"/>
-        <v>2613.1364540637092</v>
+        <f t="shared" si="27"/>
+        <v>2100.6250385477742</v>
       </c>
       <c r="EG17" s="6">
-        <f t="shared" si="30"/>
-        <v>2587.005089523072</v>
+        <f t="shared" si="27"/>
+        <v>2079.6187881622964</v>
       </c>
       <c r="EH17" s="6">
-        <f t="shared" si="30"/>
-        <v>2561.1350386278414</v>
+        <f t="shared" si="27"/>
+        <v>2058.8226002806732</v>
       </c>
       <c r="EI17" s="6">
-        <f t="shared" si="30"/>
-        <v>2535.5236882415629</v>
+        <f t="shared" si="27"/>
+        <v>2038.2343742778664</v>
       </c>
       <c r="EJ17" s="6">
-        <f t="shared" si="30"/>
-        <v>2510.1684513591472</v>
+        <f t="shared" si="27"/>
+        <v>2017.8520305350878</v>
       </c>
       <c r="EK17" s="6">
-        <f t="shared" si="30"/>
-        <v>2485.0667668455558</v>
+        <f t="shared" si="27"/>
+        <v>1997.6735102297368</v>
       </c>
       <c r="EL17" s="6">
-        <f t="shared" si="30"/>
-        <v>2460.2160991771002</v>
+        <f t="shared" si="27"/>
+        <v>1977.6967751274394</v>
       </c>
       <c r="EM17" s="6">
-        <f t="shared" si="30"/>
-        <v>2435.6139381853291</v>
+        <f t="shared" si="27"/>
+        <v>1957.919807376165</v>
       </c>
       <c r="EN17" s="6">
-        <f t="shared" si="30"/>
-        <v>2411.2577988034759</v>
+        <f t="shared" si="27"/>
+        <v>1938.3406093024032</v>
       </c>
       <c r="EO17" s="6">
-        <f t="shared" si="30"/>
-        <v>2387.145220815441</v>
+        <f t="shared" si="27"/>
+        <v>1918.9572032093793</v>
       </c>
       <c r="EP17" s="6">
-        <f t="shared" si="30"/>
-        <v>2363.2737686072865</v>
+        <f t="shared" si="27"/>
+        <v>1899.7676311772855</v>
+      </c>
+      <c r="EQ17" s="6">
+        <f t="shared" si="27"/>
+        <v>1880.7699548655125</v>
+      </c>
+      <c r="ER17" s="6">
+        <f t="shared" si="27"/>
+        <v>1861.9622553168574</v>
+      </c>
+      <c r="ES17" s="6">
+        <f t="shared" si="27"/>
+        <v>1843.3426327636889</v>
+      </c>
+      <c r="ET17" s="6">
+        <f t="shared" si="27"/>
+        <v>1824.909206436052</v>
       </c>
     </row>
-    <row r="18" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>1</v>
       </c>
@@ -3657,7 +3741,7 @@
         <v>989.2</v>
       </c>
       <c r="W18" s="1">
-        <f t="shared" ref="W18" si="31">989.2</f>
+        <f t="shared" ref="W18" si="28">989.2</f>
         <v>989.2</v>
       </c>
       <c r="X18" s="1">
@@ -3668,21 +3752,12 @@
         <v>935.7</v>
       </c>
       <c r="Z18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
-      </c>
-      <c r="AC18" s="1">
-        <v>1064</v>
-      </c>
-      <c r="AD18" s="1">
-        <v>1064</v>
-      </c>
-      <c r="AE18" s="1">
-        <v>1064</v>
-      </c>
-      <c r="AF18" s="1">
-        <v>1064</v>
-      </c>
+        <v>920.7</v>
+      </c>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
       <c r="AG18" s="1">
         <v>1064</v>
       </c>
@@ -3690,228 +3765,233 @@
         <v>1064</v>
       </c>
       <c r="AI18" s="1">
-        <f t="shared" ref="AI18:AT18" si="32">1002.5</f>
+        <v>1064</v>
+      </c>
+      <c r="AJ18" s="1">
+        <v>1064</v>
+      </c>
+      <c r="AK18" s="1">
+        <v>1064</v>
+      </c>
+      <c r="AL18" s="1">
+        <v>1064</v>
+      </c>
+      <c r="AM18" s="1">
+        <f t="shared" ref="AM18" si="29">1002.5</f>
         <v>1002.5</v>
       </c>
-      <c r="AJ18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
-      </c>
-      <c r="AK18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
-      </c>
-      <c r="AL18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
-      </c>
-      <c r="AM18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
-      </c>
       <c r="AN18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
+        <v>920.7</v>
       </c>
       <c r="AO18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
+        <v>920.7</v>
       </c>
       <c r="AP18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
+        <v>920.7</v>
       </c>
       <c r="AQ18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
+        <v>920.7</v>
       </c>
       <c r="AR18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
+        <v>920.7</v>
       </c>
       <c r="AS18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
+        <v>920.7</v>
       </c>
       <c r="AT18" s="1">
-        <f>935.7</f>
-        <v>935.7</v>
+        <v>920.7</v>
+      </c>
+      <c r="AU18" s="1">
+        <v>920.7</v>
+      </c>
+      <c r="AV18" s="1">
+        <v>920.7</v>
+      </c>
+      <c r="AW18" s="1">
+        <v>920.7</v>
+      </c>
+      <c r="AX18" s="1">
+        <v>920.7</v>
       </c>
     </row>
-    <row r="19" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:S19" si="33">C17/C18</f>
+        <f t="shared" ref="C19:S19" si="30">C17/C18</f>
         <v>7.3748902546093065E-2</v>
       </c>
       <c r="D19" s="5">
+        <f t="shared" si="30"/>
+        <v>1.3432835820895523</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.89640035118525019</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="30"/>
+        <v>1.3757682177348551</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.96312554872695344</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="30"/>
+        <v>1.0395083406496928</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.95434591747146624</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.7032484635645303</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.44688323090430204</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="30"/>
+        <v>-0.29938542581211591</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" si="30"/>
+        <v>1.1676909569798068</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.80860403863037755</v>
+      </c>
+      <c r="O19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.70416297608503098</v>
+      </c>
+      <c r="P19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.90342405618964006</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.89552238805970152</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="30"/>
+        <v>1.3017641597028784</v>
+      </c>
+      <c r="S19" s="5">
+        <f t="shared" si="30"/>
+        <v>0.83458646616541354</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" ref="T19:V19" si="31">T17/T18</f>
+        <v>1.1033943069549057</v>
+      </c>
+      <c r="U19" s="5">
+        <f t="shared" si="31"/>
+        <v>1.0074812967581048</v>
+      </c>
+      <c r="V19" s="5">
+        <f t="shared" si="31"/>
+        <v>1.1332389809947432</v>
+      </c>
+      <c r="W19" s="5">
+        <f t="shared" ref="W19:Z19" si="32">W17/W18</f>
+        <v>1.301051354630004</v>
+      </c>
+      <c r="X19" s="5">
+        <f t="shared" si="32"/>
+        <v>1.3013415892672859</v>
+      </c>
+      <c r="Y19" s="5">
+        <f t="shared" si="32"/>
+        <v>1.3337608207758895</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="32"/>
+        <v>1.5607689801238187</v>
+      </c>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+      <c r="AG19" s="5">
+        <f t="shared" ref="AG19:AN19" si="33">AG17/AG18</f>
+        <v>1.9332706766917294</v>
+      </c>
+      <c r="AH19" s="5">
         <f t="shared" si="33"/>
-        <v>1.3432835820895523</v>
-      </c>
-      <c r="E19" s="5">
+        <v>2.3110902255639099</v>
+      </c>
+      <c r="AI19" s="5">
         <f t="shared" si="33"/>
-        <v>0.89640035118525019</v>
-      </c>
-      <c r="F19" s="5">
+        <v>3.9492481203007519</v>
+      </c>
+      <c r="AJ19" s="5">
         <f t="shared" si="33"/>
-        <v>1.3757682177348551</v>
-      </c>
-      <c r="G19" s="5">
+        <v>3.9182330827067671</v>
+      </c>
+      <c r="AK19" s="5">
         <f t="shared" si="33"/>
-        <v>0.96312554872695344</v>
-      </c>
-      <c r="H19" s="5">
+        <v>2.2734962406015038</v>
+      </c>
+      <c r="AL19" s="5">
         <f t="shared" si="33"/>
-        <v>1.0395083406496928</v>
-      </c>
-      <c r="I19" s="5">
+        <v>3.9906015037593985</v>
+      </c>
+      <c r="AM19" s="5">
         <f t="shared" si="33"/>
-        <v>0.95434591747146624</v>
-      </c>
-      <c r="J19" s="5">
+        <v>4.1366583541147133</v>
+      </c>
+      <c r="AN19" s="5">
         <f t="shared" si="33"/>
-        <v>0.7032484635645303</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="33"/>
-        <v>0.44688323090430204</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="33"/>
-        <v>-0.29938542581211591</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" si="33"/>
-        <v>1.1676909569798068</v>
-      </c>
-      <c r="N19" s="5">
-        <f t="shared" si="33"/>
-        <v>0.80860403863037755</v>
-      </c>
-      <c r="O19" s="5">
-        <f t="shared" si="33"/>
-        <v>0.70416297608503098</v>
-      </c>
-      <c r="P19" s="5">
-        <f t="shared" si="33"/>
-        <v>0.90342405618964006</v>
-      </c>
-      <c r="Q19" s="5">
-        <f t="shared" si="33"/>
-        <v>0.89552238805970152</v>
-      </c>
-      <c r="R19" s="5">
-        <f t="shared" si="33"/>
-        <v>1.3017641597028784</v>
-      </c>
-      <c r="S19" s="5">
-        <f t="shared" si="33"/>
-        <v>0.83458646616541354</v>
-      </c>
-      <c r="T19" s="5">
-        <f t="shared" ref="T19:V19" si="34">T17/T18</f>
-        <v>1.1033943069549057</v>
-      </c>
-      <c r="U19" s="5">
+        <v>5.6837189095253606</v>
+      </c>
+      <c r="AO19" s="5">
+        <f t="shared" ref="AO19:AX19" si="34">AO17/AO18</f>
+        <v>4.6919830563701517</v>
+      </c>
+      <c r="AP19" s="5">
         <f t="shared" si="34"/>
-        <v>1.0074812967581048</v>
-      </c>
-      <c r="V19" s="5">
+        <v>4.8051000499619843</v>
+      </c>
+      <c r="AQ19" s="5">
         <f t="shared" si="34"/>
-        <v>1.1332389809947432</v>
-      </c>
-      <c r="W19" s="5">
-        <f t="shared" ref="W19:Z19" si="35">W17/W18</f>
-        <v>1.301051354630004</v>
-      </c>
-      <c r="X19" s="5">
-        <f t="shared" si="35"/>
-        <v>1.3013415892672859</v>
-      </c>
-      <c r="Y19" s="5">
-        <f t="shared" si="35"/>
-        <v>1.3337608207758895</v>
-      </c>
-      <c r="Z19" s="5">
-        <f t="shared" si="35"/>
-        <v>1.2389564176552312</v>
-      </c>
-      <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AJ19" si="36">AC17/AC18</f>
-        <v>1.9332706766917294</v>
-      </c>
-      <c r="AD19" s="5">
-        <f t="shared" si="36"/>
-        <v>2.3110902255639099</v>
-      </c>
-      <c r="AE19" s="5">
-        <f t="shared" si="36"/>
-        <v>3.9492481203007519</v>
-      </c>
-      <c r="AF19" s="5">
-        <f t="shared" si="36"/>
-        <v>3.9182330827067671</v>
-      </c>
-      <c r="AG19" s="5">
-        <f t="shared" si="36"/>
-        <v>2.2734962406015038</v>
-      </c>
-      <c r="AH19" s="5">
-        <f t="shared" si="36"/>
-        <v>3.9906015037593985</v>
-      </c>
-      <c r="AI19" s="5">
-        <f t="shared" si="36"/>
-        <v>4.1366583541147133</v>
-      </c>
-      <c r="AJ19" s="5">
-        <f t="shared" si="36"/>
-        <v>5.2958122475152356</v>
-      </c>
-      <c r="AK19" s="5">
-        <f t="shared" ref="AK19:AT19" si="37">AK17/AK18</f>
-        <v>5.7226670531153161</v>
-      </c>
-      <c r="AL19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.1498442763107839</v>
-      </c>
-      <c r="AM19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.320628737461667</v>
-      </c>
-      <c r="AN19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.4952896640941091</v>
-      </c>
-      <c r="AO19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.5610975356201653</v>
-      </c>
-      <c r="AP19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.6275634858614785</v>
-      </c>
-      <c r="AQ19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.6946940956052057</v>
+        <v>4.9489811546866491</v>
       </c>
       <c r="AR19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.7624960114463706</v>
+        <f t="shared" si="34"/>
+        <v>5.0962002944611697</v>
       </c>
       <c r="AS19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.8309759464459479</v>
+        <f t="shared" si="34"/>
+        <v>5.1480312015004905</v>
       </c>
       <c r="AT19" s="5">
-        <f t="shared" si="37"/>
-        <v>6.900140680795519</v>
+        <f t="shared" si="34"/>
+        <v>5.200380417610206</v>
+      </c>
+      <c r="AU19" s="5">
+        <f t="shared" si="34"/>
+        <v>5.2532531258810176</v>
+      </c>
+      <c r="AV19" s="5">
+        <f t="shared" si="34"/>
+        <v>5.3066545612345388</v>
+      </c>
+      <c r="AW19" s="5">
+        <f t="shared" si="34"/>
+        <v>5.3605900109415945</v>
+      </c>
+      <c r="AX19" s="5">
+        <f t="shared" si="34"/>
+        <v>5.4150648151457217</v>
       </c>
     </row>
-    <row r="21" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>46</v>
       </c>
@@ -3924,170 +4004,174 @@
         <v>0.30640970116933741</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" ref="H21:V21" si="38">H3/D3-1</f>
+        <f t="shared" ref="H21:V21" si="35">H3/D3-1</f>
         <v>0.18570613951720216</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>0.13244183916468222</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>0.13113145846958796</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>7.458975634012921E-2</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>9.105482526450781E-2</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>0.10740860562924626</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>6.7215958369470918E-2</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>8.5917013728212144E-2</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>7.0672935645019086E-2</v>
       </c>
       <c r="Q21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>8.3552439380660148E-2</v>
       </c>
       <c r="R21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>8.7091968034674228E-2</v>
       </c>
       <c r="S21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>9.3607954545454453E-2</v>
       </c>
       <c r="T21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>8.2063949499108002E-2</v>
       </c>
       <c r="U21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>5.7832299811269916E-2</v>
       </c>
       <c r="V21" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>4.2362322452030865E-2</v>
       </c>
       <c r="W21" s="8">
-        <f t="shared" ref="W21" si="39">W3/S3-1</f>
+        <f t="shared" ref="W21" si="36">W3/S3-1</f>
         <v>1.1949603844655154E-2</v>
       </c>
       <c r="X21" s="8">
-        <f t="shared" ref="X21" si="40">X3/T3-1</f>
+        <f t="shared" ref="X21" si="37">X3/T3-1</f>
         <v>5.1109701965757814E-2</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" ref="Y21" si="41">Y3/U3-1</f>
+        <f t="shared" ref="Y21" si="38">Y3/U3-1</f>
         <v>7.2639225181598155E-2</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" ref="Z21" si="42">Z3/V3-1</f>
+        <f t="shared" ref="Z21" si="39">Z3/V3-1</f>
+        <v>3.7054745398039657E-2</v>
+      </c>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AD21" s="8"/>
+      <c r="AE21" s="8"/>
+      <c r="AG21" s="8"/>
+      <c r="AH21" s="8">
+        <f>AH3/AG3-1</f>
+        <v>0.15021681444566704</v>
+      </c>
+      <c r="AI21" s="8">
+        <f t="shared" ref="AI21:AX21" si="40">AI3/AH3-1</f>
+        <v>0.20717983344586988</v>
+      </c>
+      <c r="AJ21" s="8">
+        <f t="shared" si="40"/>
+        <v>0.18257667567819524</v>
+      </c>
+      <c r="AK21" s="8">
+        <f t="shared" si="40"/>
+        <v>8.4624177210200546E-2</v>
+      </c>
+      <c r="AL21" s="8">
+        <f t="shared" si="40"/>
+        <v>8.1873682680427384E-2</v>
+      </c>
+      <c r="AM21" s="8">
+        <f t="shared" si="40"/>
+        <v>6.8052803063383793E-2</v>
+      </c>
+      <c r="AN21" s="8">
+        <f t="shared" si="40"/>
+        <v>4.3243073245903707E-2</v>
+      </c>
+      <c r="AO21" s="8">
+        <f t="shared" si="40"/>
+        <v>-5.0000000000000044E-2</v>
+      </c>
+      <c r="AP21" s="8">
+        <f t="shared" si="40"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AQ21" s="8">
+        <f t="shared" si="40"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AR21" s="8">
+        <f t="shared" si="40"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AS21" s="8">
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AA21" s="8"/>
-      <c r="AC21" s="8"/>
-      <c r="AD21" s="8">
-        <f>AD3/AC3-1</f>
-        <v>0.15021681444566704</v>
-      </c>
-      <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AT21" si="43">AE3/AD3-1</f>
-        <v>0.20717983344586988</v>
-      </c>
-      <c r="AF21" s="8">
-        <f t="shared" si="43"/>
-        <v>0.18257667567819524</v>
-      </c>
-      <c r="AG21" s="8">
-        <f t="shared" si="43"/>
-        <v>8.4624177210200546E-2</v>
-      </c>
-      <c r="AH21" s="8">
-        <f t="shared" si="43"/>
-        <v>8.1873682680427384E-2</v>
-      </c>
-      <c r="AI21" s="8">
-        <f t="shared" si="43"/>
-        <v>6.8052803063383793E-2</v>
-      </c>
-      <c r="AJ21" s="8">
-        <f t="shared" si="43"/>
-        <v>3.6124791647010879E-2</v>
-      </c>
-      <c r="AK21" s="8">
-        <f t="shared" si="43"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AL21" s="8">
-        <f t="shared" si="43"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AM21" s="8">
-        <f t="shared" si="43"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AN21" s="8">
-        <f t="shared" si="43"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AO21" s="8">
-        <f t="shared" si="43"/>
+      <c r="AT21" s="8">
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP21" s="8">
-        <f t="shared" si="43"/>
+      <c r="AU21" s="8">
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ21" s="8">
-        <f t="shared" si="43"/>
+      <c r="AV21" s="8">
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR21" s="8">
-        <f t="shared" si="43"/>
+      <c r="AW21" s="8">
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS21" s="8">
-        <f t="shared" si="43"/>
+      <c r="AX21" s="8">
+        <f t="shared" si="40"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT21" s="8">
-        <f t="shared" si="43"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
     </row>
-    <row r="22" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>50</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:F22" si="44">C8/C3</f>
+        <f t="shared" ref="C22:F22" si="41">C8/C3</f>
         <v>0.40905153746210482</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.48564911613761641</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.4843377908041766</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>0.47629169391759318</v>
       </c>
       <c r="G22" s="8">
@@ -4095,179 +4179,183 @@
         <v>0.4917951268025858</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" ref="H22:V22" si="45">H8/H3</f>
+        <f t="shared" ref="H22:V22" si="42">H8/H3</f>
         <v>0.48477075985892915</v>
       </c>
       <c r="I22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.46036881268197993</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.4457935819601041</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.4261915779731606</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.40816926241551571</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.43558282208588955</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.42394690505214683</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.40156249999999999</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.39193083573487031</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.39026691830682125</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.39957637677547969</v>
+      </c>
+      <c r="S22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.39057020392258734</v>
+      </c>
+      <c r="T22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.40228281547241596</v>
+      </c>
+      <c r="U22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.41123996431757359</v>
+      </c>
+      <c r="V22" s="8">
+        <f t="shared" si="42"/>
+        <v>0.41644752569925891</v>
+      </c>
+      <c r="W22" s="8">
+        <f t="shared" ref="W22:Z22" si="43">W8/W3</f>
+        <v>0.42587601078167114</v>
+      </c>
+      <c r="X22" s="8">
+        <f t="shared" si="43"/>
+        <v>0.41397200772200771</v>
+      </c>
+      <c r="Y22" s="8">
+        <f t="shared" si="43"/>
+        <v>0.40679577046453608</v>
+      </c>
+      <c r="Z22" s="8">
+        <f t="shared" si="43"/>
+        <v>0.41355463347164589</v>
+      </c>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8"/>
+      <c r="AD22" s="8"/>
+      <c r="AE22" s="8"/>
+      <c r="AG22" s="8">
+        <f t="shared" ref="AG22:AH22" si="44">AG8/AG3</f>
+        <v>0.46527732832826352</v>
+      </c>
+      <c r="AH22" s="8">
+        <f t="shared" si="44"/>
+        <v>0.44941480981318926</v>
+      </c>
+      <c r="AI22" s="8">
+        <f t="shared" ref="AI22:AX22" si="45">AI8/AI3</f>
+        <v>0.46616015661415122</v>
+      </c>
+      <c r="AJ22" s="8">
         <f t="shared" si="45"/>
-        <v>0.46036881268197993</v>
-      </c>
-      <c r="J22" s="8">
+        <v>0.46986717117969334</v>
+      </c>
+      <c r="AK22" s="8">
         <f t="shared" si="45"/>
-        <v>0.4457935819601041</v>
-      </c>
-      <c r="K22" s="8">
+        <v>0.42346827531070574</v>
+      </c>
+      <c r="AL22" s="8">
         <f t="shared" si="45"/>
-        <v>0.4261915779731606</v>
-      </c>
-      <c r="L22" s="8">
+        <v>0.39585502670383932</v>
+      </c>
+      <c r="AM22" s="8">
         <f t="shared" si="45"/>
-        <v>0.40816926241551571</v>
-      </c>
-      <c r="M22" s="8">
+        <v>0.40538415573796271</v>
+      </c>
+      <c r="AN22" s="8">
         <f t="shared" si="45"/>
-        <v>0.43558282208588955</v>
-      </c>
-      <c r="N22" s="8">
+        <v>0.41483781502471967</v>
+      </c>
+      <c r="AO22" s="8">
         <f t="shared" si="45"/>
-        <v>0.42394690505214683</v>
-      </c>
-      <c r="O22" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="AP22" s="8">
         <f t="shared" si="45"/>
-        <v>0.40156249999999999</v>
-      </c>
-      <c r="P22" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="AQ22" s="8">
         <f t="shared" si="45"/>
-        <v>0.39193083573487031</v>
-      </c>
-      <c r="Q22" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="AR22" s="8">
         <f t="shared" si="45"/>
-        <v>0.39026691830682125</v>
-      </c>
-      <c r="R22" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="AS22" s="8">
         <f t="shared" si="45"/>
-        <v>0.39957637677547969</v>
-      </c>
-      <c r="S22" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="AT22" s="8">
         <f t="shared" si="45"/>
-        <v>0.39057020392258734</v>
-      </c>
-      <c r="T22" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="AU22" s="8">
         <f t="shared" si="45"/>
-        <v>0.40228281547241596</v>
-      </c>
-      <c r="U22" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="AV22" s="8">
         <f t="shared" si="45"/>
-        <v>0.41123996431757359</v>
-      </c>
-      <c r="V22" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="AW22" s="8">
         <f t="shared" si="45"/>
-        <v>0.41644752569925891</v>
-      </c>
-      <c r="W22" s="8">
-        <f t="shared" ref="W22:Z22" si="46">W8/W3</f>
-        <v>0.42587601078167114</v>
-      </c>
-      <c r="X22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.41397200772200771</v>
-      </c>
-      <c r="Y22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.40679577046453608</v>
-      </c>
-      <c r="Z22" s="8">
-        <f t="shared" si="46"/>
-        <v>0.42</v>
-      </c>
-      <c r="AA22" s="8"/>
-      <c r="AC22" s="8">
-        <f t="shared" ref="AC22:AD22" si="47">AC8/AC3</f>
-        <v>0.46527732832826352</v>
-      </c>
-      <c r="AD22" s="8">
-        <f t="shared" si="47"/>
-        <v>0.44941480981318926</v>
-      </c>
-      <c r="AE22" s="8">
-        <f t="shared" ref="AE22:AT22" si="48">AE8/AE3</f>
-        <v>0.46616015661415122</v>
-      </c>
-      <c r="AF22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.46986717117969334</v>
-      </c>
-      <c r="AG22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.42346827531070574</v>
-      </c>
-      <c r="AH22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.39585502670383932</v>
-      </c>
-      <c r="AI22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.40538415573796271</v>
-      </c>
-      <c r="AJ22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.41649969070281195</v>
-      </c>
-      <c r="AK22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.43</v>
-      </c>
-      <c r="AL22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AM22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AN22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AO22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AP22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AQ22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AR22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AS22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AT22" s="8">
-        <f t="shared" si="48"/>
-        <v>0.44</v>
-      </c>
-      <c r="AW22" t="s">
+        <v>0.41</v>
+      </c>
+      <c r="AX22" s="8">
+        <f t="shared" si="45"/>
+        <v>0.41</v>
+      </c>
+      <c r="BA22" t="s">
         <v>53</v>
       </c>
-      <c r="AX22" s="8">
+      <c r="BB22" s="8">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="23" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" ref="C23:F23" si="49">C9/C3</f>
+        <f t="shared" ref="C23:F23" si="46">C9/C3</f>
         <v>8.0337808575140751E-2</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>7.8692263828169545E-2</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>8.6279538376992121E-2</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>9.8920863309352514E-2</v>
       </c>
       <c r="G23" s="8">
@@ -4275,162 +4363,166 @@
         <v>9.978451848168407E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" ref="H23:V23" si="50">H9/H3</f>
+        <f t="shared" ref="H23:V23" si="47">H9/H3</f>
         <v>0.10067329272202628</v>
       </c>
       <c r="I23" s="8">
+        <f t="shared" si="47"/>
+        <v>8.8806211582012295E-2</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="47"/>
+        <v>9.6270598438855159E-2</v>
+      </c>
+      <c r="K23" s="8">
+        <f t="shared" si="47"/>
+        <v>9.1624248033317909E-2</v>
+      </c>
+      <c r="L23" s="8">
+        <f t="shared" si="47"/>
+        <v>8.7422862180429037E-2</v>
+      </c>
+      <c r="M23" s="8">
+        <f t="shared" si="47"/>
+        <v>7.9462459830557997E-2</v>
+      </c>
+      <c r="N23" s="8">
+        <f t="shared" si="47"/>
+        <v>7.0973858864960049E-2</v>
+      </c>
+      <c r="O23" s="8">
+        <f t="shared" si="47"/>
+        <v>6.1931818181818185E-2</v>
+      </c>
+      <c r="P23" s="8">
+        <f t="shared" si="47"/>
+        <v>6.3812268423219437E-2</v>
+      </c>
+      <c r="Q23" s="8">
+        <f t="shared" si="47"/>
+        <v>5.9584793744944728E-2</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="47"/>
+        <v>5.8061300772489409E-2</v>
+      </c>
+      <c r="S23" s="8">
+        <f t="shared" si="47"/>
+        <v>5.4682426289128457E-2</v>
+      </c>
+      <c r="T23" s="8">
+        <f t="shared" si="47"/>
+        <v>5.6563094483195943E-2</v>
+      </c>
+      <c r="U23" s="8">
+        <f t="shared" si="47"/>
+        <v>6.4738116477634763E-2</v>
+      </c>
+      <c r="V23" s="8">
+        <f t="shared" si="47"/>
+        <v>7.4826679416686595E-2</v>
+      </c>
+      <c r="W23" s="8">
+        <f t="shared" ref="W23:Z23" si="48">W9/W3</f>
+        <v>6.2636375304838912E-2</v>
+      </c>
+      <c r="X23" s="8">
+        <f t="shared" si="48"/>
+        <v>7.0342664092664098E-2</v>
+      </c>
+      <c r="Y23" s="8">
+        <f t="shared" si="48"/>
+        <v>6.1898538671735774E-2</v>
+      </c>
+      <c r="Z23" s="8">
+        <f t="shared" si="48"/>
+        <v>7.9644997694790221E-2</v>
+      </c>
+      <c r="AA23" s="8"/>
+      <c r="AB23" s="8"/>
+      <c r="AC23" s="8"/>
+      <c r="AD23" s="8"/>
+      <c r="AE23" s="8"/>
+      <c r="AG23" s="8">
+        <f t="shared" ref="AG23:AH23" si="49">AG9/AG3</f>
+        <v>8.5043039285483138E-2</v>
+      </c>
+      <c r="AH23" s="8">
+        <f t="shared" si="49"/>
+        <v>7.8831870357866304E-2</v>
+      </c>
+      <c r="AI23" s="8">
+        <f t="shared" ref="AI23:AX23" si="50">AI9/AI3</f>
+        <v>8.674373077281626E-2</v>
+      </c>
+      <c r="AJ23" s="8">
         <f t="shared" si="50"/>
-        <v>8.8806211582012295E-2</v>
-      </c>
-      <c r="J23" s="8">
+        <v>9.6369871112687716E-2</v>
+      </c>
+      <c r="AK23" s="8">
         <f t="shared" si="50"/>
-        <v>9.6270598438855159E-2</v>
-      </c>
-      <c r="K23" s="8">
+        <v>8.2019042081546631E-2</v>
+      </c>
+      <c r="AL23" s="8">
         <f t="shared" si="50"/>
-        <v>9.1624248033317909E-2</v>
-      </c>
-      <c r="L23" s="8">
+        <v>6.0763830573376774E-2</v>
+      </c>
+      <c r="AM23" s="8">
         <f t="shared" si="50"/>
-        <v>8.7422862180429037E-2</v>
-      </c>
-      <c r="M23" s="8">
+        <v>6.2930465138220593E-2</v>
+      </c>
+      <c r="AN23" s="8">
         <f t="shared" si="50"/>
-        <v>7.9462459830557997E-2</v>
-      </c>
-      <c r="N23" s="8">
+        <v>6.8823103822500911E-2</v>
+      </c>
+      <c r="AO23" s="8">
         <f t="shared" si="50"/>
-        <v>7.0973858864960049E-2</v>
-      </c>
-      <c r="O23" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AP23" s="8">
         <f t="shared" si="50"/>
-        <v>6.1931818181818185E-2</v>
-      </c>
-      <c r="P23" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AQ23" s="8">
         <f t="shared" si="50"/>
-        <v>6.3812268423219437E-2</v>
-      </c>
-      <c r="Q23" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AR23" s="8">
         <f t="shared" si="50"/>
-        <v>5.9584793744944728E-2</v>
-      </c>
-      <c r="R23" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AS23" s="8">
         <f t="shared" si="50"/>
-        <v>5.8061300772489409E-2</v>
-      </c>
-      <c r="S23" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AT23" s="8">
         <f t="shared" si="50"/>
-        <v>5.4682426289128457E-2</v>
-      </c>
-      <c r="T23" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AU23" s="8">
         <f t="shared" si="50"/>
-        <v>5.6563094483195943E-2</v>
-      </c>
-      <c r="U23" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AV23" s="8">
         <f t="shared" si="50"/>
-        <v>6.4738116477634763E-2</v>
-      </c>
-      <c r="V23" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AW23" s="8">
         <f t="shared" si="50"/>
-        <v>7.4826679416686595E-2</v>
-      </c>
-      <c r="W23" s="8">
-        <f t="shared" ref="W23:Z23" si="51">W9/W3</f>
-        <v>6.2636375304838912E-2</v>
-      </c>
-      <c r="X23" s="8">
-        <f t="shared" si="51"/>
-        <v>7.0342664092664098E-2</v>
-      </c>
-      <c r="Y23" s="8">
-        <f t="shared" si="51"/>
-        <v>6.1898538671735774E-2</v>
-      </c>
-      <c r="Z23" s="8">
-        <f t="shared" si="51"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AX23" s="8">
+        <f t="shared" si="50"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BA23" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB23" s="8">
         <v>0.08</v>
       </c>
-      <c r="AA23" s="8"/>
-      <c r="AC23" s="8">
-        <f t="shared" ref="AC23:AD23" si="52">AC9/AC3</f>
-        <v>8.5043039285483138E-2</v>
-      </c>
-      <c r="AD23" s="8">
-        <f t="shared" si="52"/>
-        <v>7.8831870357866304E-2</v>
-      </c>
-      <c r="AE23" s="8">
-        <f t="shared" ref="AE23:AT23" si="53">AE9/AE3</f>
-        <v>8.674373077281626E-2</v>
-      </c>
-      <c r="AF23" s="8">
-        <f t="shared" si="53"/>
-        <v>9.6369871112687716E-2</v>
-      </c>
-      <c r="AG23" s="8">
-        <f t="shared" si="53"/>
-        <v>8.2019042081546631E-2</v>
-      </c>
-      <c r="AH23" s="8">
-        <f t="shared" si="53"/>
-        <v>6.0763830573376774E-2</v>
-      </c>
-      <c r="AI23" s="8">
-        <f t="shared" si="53"/>
-        <v>6.2930465138220593E-2</v>
-      </c>
-      <c r="AJ23" s="8">
-        <f t="shared" si="53"/>
-        <v>6.8839804696582185E-2</v>
-      </c>
-      <c r="AK23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AL23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AM23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AN23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AO23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AP23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AQ23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AR23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AS23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AT23" s="8">
-        <f t="shared" si="53"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AW23" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX23" s="8">
-        <v>7.0000000000000007E-2</v>
-      </c>
     </row>
-    <row r="24" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>48</v>
       </c>
@@ -4443,160 +4535,164 @@
         <v>0.22479338842975216</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" ref="H24:V24" si="54">H10/D10-1</f>
+        <f t="shared" ref="H24:V24" si="51">H10/D10-1</f>
         <v>0.1822503961965134</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>0.12017804154302669</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>8.7431693989071135E-2</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>9.986504723346834E-2</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>9.2493297587131318E-2</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>6.0927152317880706E-2</v>
       </c>
       <c r="N24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>3.2663316582914659E-2</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-0.11533742331288344</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-8.8343558282208634E-2</v>
       </c>
       <c r="Q24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-7.7403245942571752E-2</v>
       </c>
       <c r="R24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-6.326034063260344E-2</v>
       </c>
       <c r="S24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>2.9126213592232997E-2</v>
       </c>
       <c r="T24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>-3.3647375504710642E-2</v>
       </c>
       <c r="U24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>9.4722598105547728E-3</v>
       </c>
       <c r="V24" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v>3.8961038961038419E-3</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" ref="W24:W25" si="55">W10/S10-1</f>
+        <f t="shared" ref="W24:W25" si="52">W10/S10-1</f>
         <v>-1.4824797843665749E-2</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" ref="X24:X25" si="56">X10/T10-1</f>
+        <f t="shared" ref="X24:X25" si="53">X10/T10-1</f>
         <v>6.8245125348189495E-2</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" ref="Y24:Y25" si="57">Y10/U10-1</f>
+        <f t="shared" ref="Y24:Y25" si="54">Y10/U10-1</f>
         <v>7.3726541554959724E-2</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" ref="Z24:Z25" si="58">Z10/V10-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="Z24:Z25" si="55">Z10/V10-1</f>
+        <v>4.0103492884864256E-2</v>
       </c>
       <c r="AA24" s="8"/>
+      <c r="AB24" s="8"/>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8">
-        <f>AD10/AC10-1</f>
+      <c r="AD24" s="8"/>
+      <c r="AE24" s="8"/>
+      <c r="AG24" s="8"/>
+      <c r="AH24" s="8">
+        <f>AH10/AG10-1</f>
         <v>0.1387220098306936</v>
       </c>
-      <c r="AE24" s="8">
-        <f t="shared" ref="AE24:AT24" si="59">AE10/AD10-1</f>
+      <c r="AI24" s="8">
+        <f t="shared" ref="AI24:AX24" si="56">AI10/AH10-1</f>
         <v>0.26714628297362109</v>
       </c>
-      <c r="AF24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AJ24" s="8">
+        <f t="shared" si="56"/>
         <v>0.14988644965934905</v>
       </c>
-      <c r="AG24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AK24" s="8">
+        <f t="shared" si="56"/>
         <v>7.0770243581303571E-2</v>
       </c>
-      <c r="AH24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AL24" s="8">
+        <f t="shared" si="56"/>
         <v>-8.6074392868121685E-2</v>
       </c>
-      <c r="AI24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AM24" s="8">
+        <f t="shared" si="56"/>
         <v>2.0181634712410634E-3</v>
       </c>
-      <c r="AJ24" s="8">
-        <f t="shared" si="59"/>
-        <v>4.419268210809002E-2</v>
-      </c>
-      <c r="AK24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AN24" s="8">
+        <f t="shared" si="56"/>
+        <v>4.1624706277274326E-2</v>
+      </c>
+      <c r="AO24" s="8">
+        <f t="shared" si="56"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AL24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AP24" s="8">
+        <f t="shared" si="56"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AM24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AQ24" s="8">
+        <f t="shared" si="56"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AR24" s="8">
+        <f t="shared" si="56"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AO24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AS24" s="8">
+        <f t="shared" si="56"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AT24" s="8">
+        <f t="shared" si="56"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AU24" s="8">
+        <f t="shared" si="56"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AV24" s="8">
+        <f t="shared" si="56"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AW24" s="8">
+        <f t="shared" si="56"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT24" s="8">
-        <f t="shared" si="59"/>
+      <c r="AX24" s="8">
+        <f t="shared" si="56"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW24" t="s">
+      <c r="BA24" t="s">
         <v>55</v>
       </c>
-      <c r="AX24" s="1">
-        <f>NPV(AX23,AJ17:EP17)</f>
-        <v>82150.990424357398</v>
+      <c r="BB24" s="1">
+        <f>NPV(BB23,AN17:ET17)</f>
+        <v>57382.633309521392</v>
       </c>
     </row>
-    <row r="25" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>49</v>
       </c>
@@ -4609,177 +4705,181 @@
         <v>7.8189300411522611E-2</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" ref="H25:V25" si="60">H11/D11-1</f>
+        <f t="shared" ref="H25:V25" si="57">H11/D11-1</f>
         <v>1.953125E-2</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>-9.9403578528827197E-3</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>1.7574692442883233E-3</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>0.15839694656488557</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>-1.5325670498084309E-2</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>-7.0281124497991954E-2</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>-9.6491228070175405E-2</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>-0.16474464579901149</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>-4.4747081712062209E-2</v>
       </c>
       <c r="Q25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>9.5032397408207236E-2</v>
       </c>
       <c r="R25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>7.5728155339805925E-2</v>
       </c>
       <c r="S25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>-8.4812623274161725E-2</v>
       </c>
       <c r="T25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>0.16089613034623218</v>
       </c>
       <c r="U25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>2.3668639053254337E-2</v>
       </c>
       <c r="V25" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v>7.2202166064981865E-2</v>
       </c>
       <c r="W25" s="8">
+        <f t="shared" si="52"/>
+        <v>8.405172413793105E-2</v>
+      </c>
+      <c r="X25" s="8">
+        <f t="shared" si="53"/>
+        <v>-0.19122807017543864</v>
+      </c>
+      <c r="Y25" s="8">
+        <f t="shared" si="54"/>
+        <v>-1.1560693641618491E-2</v>
+      </c>
+      <c r="Z25" s="8">
         <f t="shared" si="55"/>
-        <v>8.405172413793105E-2</v>
-      </c>
-      <c r="X25" s="8">
-        <f t="shared" si="56"/>
-        <v>-0.19122807017543864</v>
-      </c>
-      <c r="Y25" s="8">
-        <f t="shared" si="57"/>
-        <v>-1.1560693641618491E-2</v>
-      </c>
-      <c r="Z25" s="8">
+        <v>-0.15488215488215484</v>
+      </c>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8"/>
+      <c r="AD25" s="8"/>
+      <c r="AE25" s="8"/>
+      <c r="AG25" s="8"/>
+      <c r="AH25" s="8">
+        <f>AH11/AG11-1</f>
+        <v>0.11031797534068777</v>
+      </c>
+      <c r="AI25" s="8">
+        <f t="shared" ref="AI25:AX25" si="58">AI11/AH11-1</f>
+        <v>0.20981881940385749</v>
+      </c>
+      <c r="AJ25" s="8">
         <f t="shared" si="58"/>
-        <v>-2.0000000000000018E-2</v>
-      </c>
-      <c r="AA25" s="8"/>
-      <c r="AC25" s="8"/>
-      <c r="AD25" s="8">
-        <f>AD11/AC11-1</f>
-        <v>0.11031797534068777</v>
-      </c>
-      <c r="AE25" s="8">
-        <f t="shared" ref="AE25:AT25" si="61">AE11/AD11-1</f>
-        <v>0.20981881940385749</v>
-      </c>
-      <c r="AF25" s="8">
-        <f t="shared" si="61"/>
         <v>2.1256038647343045E-2</v>
       </c>
-      <c r="AG25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AK25" s="8">
+        <f t="shared" si="58"/>
         <v>-7.0955534531693676E-3</v>
       </c>
-      <c r="AH25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AL25" s="8">
+        <f t="shared" si="58"/>
         <v>-1.9056693663649371E-2</v>
       </c>
-      <c r="AI25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AM25" s="8">
+        <f t="shared" si="58"/>
         <v>4.2739193783390084E-2</v>
       </c>
-      <c r="AJ25" s="8">
-        <f t="shared" si="61"/>
-        <v>-4.0931532370749979E-2</v>
-      </c>
-      <c r="AK25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AN25" s="8">
+        <f t="shared" si="58"/>
+        <v>-7.8248719142990253E-2</v>
+      </c>
+      <c r="AO25" s="8">
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AP25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AQ25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AR25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AO25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AS25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AT25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AQ25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AU25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AV25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AW25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT25" s="8">
-        <f t="shared" si="61"/>
+      <c r="AX25" s="8">
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW25" t="s">
+      <c r="BA25" t="s">
         <v>56</v>
       </c>
-      <c r="AX25" s="1">
+      <c r="BB25" s="1">
         <f>Main!D8</f>
-        <v>3080</v>
+        <v>4765</v>
       </c>
     </row>
-    <row r="26" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" ref="C26:F26" si="62">C13/C3</f>
+        <f t="shared" ref="C26:F26" si="59">C13/C3</f>
         <v>8.6184495452576879E-2</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>0.18076411328644745</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>0.17897050741894119</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>0.15745585349901897</v>
       </c>
       <c r="G26" s="8">
@@ -4787,180 +4887,184 @@
         <v>0.17271672468092159</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:V26" si="63">H13/H3</f>
+        <f t="shared" ref="H26:V26" si="60">H13/H3</f>
         <v>0.18066688041038795</v>
       </c>
       <c r="I26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.16871562601099968</v>
+      </c>
+      <c r="J26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.15177797051170858</v>
+      </c>
+      <c r="K26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.10967144840351689</v>
+      </c>
+      <c r="L26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.11225389362327358</v>
+      </c>
+      <c r="M26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.16330704060765411</v>
+      </c>
+      <c r="N26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.1684951916565082</v>
+      </c>
+      <c r="O26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.14190340909090909</v>
+      </c>
+      <c r="P26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.15548236585700562</v>
+      </c>
+      <c r="Q26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.15745483957940146</v>
+      </c>
+      <c r="R26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.21530027410914529</v>
+      </c>
+      <c r="S26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.15170801402779582</v>
+      </c>
+      <c r="T26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.16804058338617628</v>
+      </c>
+      <c r="U26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.17726519689053141</v>
+      </c>
+      <c r="V26" s="8">
+        <f t="shared" si="60"/>
+        <v>0.17224480038250059</v>
+      </c>
+      <c r="W26" s="8">
+        <f t="shared" ref="W26:Z26" si="61">W13/W3</f>
+        <v>0.19638043896804006</v>
+      </c>
+      <c r="X26" s="8">
+        <f t="shared" si="61"/>
+        <v>0.18146718146718147</v>
+      </c>
+      <c r="Y26" s="8">
+        <f t="shared" si="61"/>
+        <v>0.18058690744920994</v>
+      </c>
+      <c r="Z26" s="8">
+        <f t="shared" si="61"/>
+        <v>0.17415859843245735</v>
+      </c>
+      <c r="AA26" s="8"/>
+      <c r="AB26" s="8"/>
+      <c r="AC26" s="8"/>
+      <c r="AD26" s="8"/>
+      <c r="AE26" s="8"/>
+      <c r="AG26" s="8">
+        <f t="shared" ref="AG26:AH26" si="62">AG13/AG3</f>
+        <v>0.1419972817293379</v>
+      </c>
+      <c r="AH26" s="8">
+        <f t="shared" si="62"/>
+        <v>0.15299347287868556</v>
+      </c>
+      <c r="AI26" s="8">
+        <f t="shared" ref="AI26:AX26" si="63">AI13/AI3</f>
+        <v>0.15330474503589075</v>
+      </c>
+      <c r="AJ26" s="8">
         <f t="shared" si="63"/>
-        <v>0.16871562601099968</v>
-      </c>
-      <c r="J26" s="8">
+        <v>0.16798707185369122</v>
+      </c>
+      <c r="AK26" s="8">
         <f t="shared" si="63"/>
-        <v>0.15177797051170858</v>
-      </c>
-      <c r="K26" s="8">
+        <v>0.13943600552365723</v>
+      </c>
+      <c r="AL26" s="8">
         <f t="shared" si="63"/>
-        <v>0.10967144840351689</v>
-      </c>
-      <c r="L26" s="8">
+        <v>0.16888918746431092</v>
+      </c>
+      <c r="AM26" s="8">
         <f t="shared" si="63"/>
-        <v>0.11225389362327358</v>
-      </c>
-      <c r="M26" s="8">
+        <v>0.16746862911595434</v>
+      </c>
+      <c r="AN26" s="8">
         <f t="shared" si="63"/>
-        <v>0.16330704060765411</v>
-      </c>
-      <c r="N26" s="8">
+        <v>0.1828349210177258</v>
+      </c>
+      <c r="AO26" s="8">
         <f t="shared" si="63"/>
-        <v>0.1684951916565082</v>
-      </c>
-      <c r="O26" s="8">
+        <v>0.17135205975870579</v>
+      </c>
+      <c r="AP26" s="8">
         <f t="shared" si="63"/>
-        <v>0.14190340909090909</v>
-      </c>
-      <c r="P26" s="8">
+        <v>0.17204226723596069</v>
+      </c>
+      <c r="AQ26" s="8">
         <f t="shared" si="63"/>
-        <v>0.15548236585700562</v>
-      </c>
-      <c r="Q26" s="8">
+        <v>0.17371941199472704</v>
+      </c>
+      <c r="AR26" s="8">
         <f t="shared" si="63"/>
-        <v>0.15745483957940146</v>
-      </c>
-      <c r="R26" s="8">
+        <v>0.17537951611233094</v>
+      </c>
+      <c r="AS26" s="8">
         <f t="shared" si="63"/>
-        <v>0.21530027410914529</v>
-      </c>
-      <c r="S26" s="8">
+        <v>0.17540912232462291</v>
+      </c>
+      <c r="AT26" s="8">
         <f t="shared" si="63"/>
-        <v>0.15170801402779582</v>
-      </c>
-      <c r="T26" s="8">
+        <v>0.17543843540610013</v>
+      </c>
+      <c r="AU26" s="8">
         <f t="shared" si="63"/>
-        <v>0.16804058338617628</v>
-      </c>
-      <c r="U26" s="8">
+        <v>0.17546745825904786</v>
+      </c>
+      <c r="AV26" s="8">
         <f t="shared" si="63"/>
-        <v>0.17726519689053141</v>
-      </c>
-      <c r="V26" s="8">
+        <v>0.17549619375701594</v>
+      </c>
+      <c r="AW26" s="8">
         <f t="shared" si="63"/>
-        <v>0.17224480038250059</v>
-      </c>
-      <c r="W26" s="8">
-        <f t="shared" ref="W26:Z26" si="64">W13/W3</f>
-        <v>0.19638043896804006</v>
-      </c>
-      <c r="X26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.18146718146718147</v>
-      </c>
-      <c r="Y26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.18058690744920994</v>
-      </c>
-      <c r="Z26" s="8">
-        <f t="shared" si="64"/>
-        <v>0.16913276983925979</v>
-      </c>
-      <c r="AA26" s="8"/>
-      <c r="AC26" s="8">
-        <f t="shared" ref="AC26:AD26" si="65">AC13/AC3</f>
-        <v>0.1419972817293379</v>
-      </c>
-      <c r="AD26" s="8">
-        <f t="shared" si="65"/>
-        <v>0.15299347287868556</v>
-      </c>
-      <c r="AE26" s="8">
-        <f t="shared" ref="AE26:AT26" si="66">AE13/AE3</f>
-        <v>0.15330474503589075</v>
-      </c>
-      <c r="AF26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.16798707185369122</v>
-      </c>
-      <c r="AG26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.13943600552365723</v>
-      </c>
-      <c r="AH26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.16888918746431092</v>
-      </c>
-      <c r="AI26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.16746862911595434</v>
-      </c>
-      <c r="AJ26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.18160554076014884</v>
-      </c>
-      <c r="AK26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.19918046309244603</v>
-      </c>
-      <c r="AL26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.20985156176046083</v>
-      </c>
-      <c r="AM26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.21145024680904662</v>
-      </c>
-      <c r="AN26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.21303269764498453</v>
-      </c>
-      <c r="AO26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.21306046149738911</v>
-      </c>
-      <c r="AP26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.21308795046016585</v>
-      </c>
-      <c r="AQ26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.21311516725499435</v>
-      </c>
-      <c r="AR26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.21314211457660673</v>
-      </c>
-      <c r="AS26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.21316879509305464</v>
-      </c>
-      <c r="AT26" s="8">
-        <f t="shared" si="66"/>
-        <v>0.21319521144597331</v>
-      </c>
-      <c r="AW26" t="s">
+        <v>0.17552464474510313</v>
+      </c>
+      <c r="AX26" s="8">
+        <f t="shared" si="63"/>
+        <v>0.17555281404023895</v>
+      </c>
+      <c r="BA26" t="s">
         <v>57</v>
       </c>
-      <c r="AX26" s="1">
-        <f>AX24+AX25</f>
-        <v>85230.990424357398</v>
+      <c r="BB26" s="1">
+        <f>BB24+BB25</f>
+        <v>62147.633309521392</v>
       </c>
     </row>
-    <row r="27" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:F27" si="67">C16/C15</f>
+        <f t="shared" ref="C27:F27" si="64">C16/C15</f>
         <v>0.68060836501901145</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.14952751528627015</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.10751748251748251</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>0.15707369553523401</v>
       </c>
       <c r="G27" s="8">
@@ -4968,163 +5072,167 @@
         <v>-0.2580275229357798</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" ref="H27:V27" si="68">H16/H15</f>
+        <f t="shared" ref="H27:V27" si="65">H16/H15</f>
         <v>0.12684365781710916</v>
       </c>
       <c r="I27" s="8">
+        <f t="shared" si="65"/>
+        <v>6.6952789699570817E-2</v>
+      </c>
+      <c r="J27" s="8">
+        <f t="shared" si="65"/>
+        <v>-0.13456090651558072</v>
+      </c>
+      <c r="K27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.19077901430842609</v>
+      </c>
+      <c r="L27" s="8">
+        <f t="shared" si="65"/>
+        <v>7.9591836734693882</v>
+      </c>
+      <c r="M27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.15716096324461343</v>
+      </c>
+      <c r="N27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.17027027027027028</v>
+      </c>
+      <c r="O27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.25977653631284914</v>
+      </c>
+      <c r="P27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.21028396009209516</v>
+      </c>
+      <c r="Q27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.17808219178082191</v>
+      </c>
+      <c r="R27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.2180702732849972</v>
+      </c>
+      <c r="S27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.26550868486352358</v>
+      </c>
+      <c r="T27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.1937097927090779</v>
+      </c>
+      <c r="U27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.2295957284515637</v>
+      </c>
+      <c r="V27" s="8">
+        <f t="shared" si="65"/>
+        <v>0.20496453900709219</v>
+      </c>
+      <c r="W27" s="8">
+        <f t="shared" ref="W27:Z27" si="66">W16/W15</f>
+        <v>0.19713038053649407</v>
+      </c>
+      <c r="X27" s="8">
+        <f t="shared" si="66"/>
+        <v>0.17527795945062133</v>
+      </c>
+      <c r="Y27" s="8">
+        <f t="shared" si="66"/>
+        <v>0.18590998043052837</v>
+      </c>
+      <c r="Z27" s="8">
+        <f t="shared" si="66"/>
+        <v>0.11677934849416104</v>
+      </c>
+      <c r="AA27" s="8"/>
+      <c r="AB27" s="8"/>
+      <c r="AC27" s="8"/>
+      <c r="AD27" s="8"/>
+      <c r="AE27" s="8"/>
+      <c r="AG27" s="8">
+        <f t="shared" ref="AG27:AH27" si="67">AG16/AG15</f>
+        <v>0.13425925925925927</v>
+      </c>
+      <c r="AH27" s="8">
+        <f t="shared" si="67"/>
+        <v>0.17978652434956638</v>
+      </c>
+      <c r="AI27" s="8">
+        <f t="shared" ref="AI27:AX27" si="68">AI16/AI15</f>
+        <v>0.17038499506416585</v>
+      </c>
+      <c r="AJ27" s="8">
         <f t="shared" si="68"/>
-        <v>6.6952789699570817E-2</v>
-      </c>
-      <c r="J27" s="8">
+        <v>-1.7077335935594046E-2</v>
+      </c>
+      <c r="AK27" s="8">
         <f t="shared" si="68"/>
-        <v>-0.13456090651558072</v>
-      </c>
-      <c r="K27" s="8">
+        <v>0.28134284016636957</v>
+      </c>
+      <c r="AL27" s="8">
         <f t="shared" si="68"/>
-        <v>0.19077901430842609</v>
-      </c>
-      <c r="L27" s="8">
+        <v>0.21530216226205878</v>
+      </c>
+      <c r="AM27" s="8">
         <f t="shared" si="68"/>
-        <v>7.9591836734693882</v>
-      </c>
-      <c r="M27" s="8">
+        <v>0.22180521673860012</v>
+      </c>
+      <c r="AN27" s="8">
         <f t="shared" si="68"/>
-        <v>0.15716096324461343</v>
-      </c>
-      <c r="N27" s="8">
+        <v>0.16830896376350921</v>
+      </c>
+      <c r="AO27" s="8">
         <f t="shared" si="68"/>
-        <v>0.17027027027027028</v>
-      </c>
-      <c r="O27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AP27" s="8">
         <f t="shared" si="68"/>
-        <v>0.25977653631284914</v>
-      </c>
-      <c r="P27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AQ27" s="8">
         <f t="shared" si="68"/>
-        <v>0.21028396009209516</v>
-      </c>
-      <c r="Q27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AR27" s="8">
         <f t="shared" si="68"/>
-        <v>0.17808219178082191</v>
-      </c>
-      <c r="R27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AS27" s="8">
         <f t="shared" si="68"/>
-        <v>0.2180702732849972</v>
-      </c>
-      <c r="S27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AT27" s="8">
         <f t="shared" si="68"/>
-        <v>0.26550868486352358</v>
-      </c>
-      <c r="T27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AU27" s="8">
         <f t="shared" si="68"/>
-        <v>0.1937097927090779</v>
-      </c>
-      <c r="U27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AV27" s="8">
         <f t="shared" si="68"/>
-        <v>0.2295957284515637</v>
-      </c>
-      <c r="V27" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AW27" s="8">
         <f t="shared" si="68"/>
-        <v>0.20496453900709219</v>
-      </c>
-      <c r="W27" s="8">
-        <f t="shared" ref="W27:Z27" si="69">W16/W15</f>
-        <v>0.19713038053649407</v>
-      </c>
-      <c r="X27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.17527795945062133</v>
-      </c>
-      <c r="Y27" s="8">
-        <f t="shared" si="69"/>
-        <v>0.18590998043052837</v>
-      </c>
-      <c r="Z27" s="8">
-        <f t="shared" si="69"/>
         <v>0.2</v>
       </c>
-      <c r="AA27" s="8"/>
-      <c r="AC27" s="8">
-        <f t="shared" ref="AC27:AD27" si="70">AC16/AC15</f>
-        <v>0.13425925925925927</v>
-      </c>
-      <c r="AD27" s="8">
-        <f t="shared" si="70"/>
-        <v>0.17978652434956638</v>
-      </c>
-      <c r="AE27" s="8">
-        <f t="shared" ref="AE27:AT27" si="71">AE16/AE15</f>
-        <v>0.17038499506416585</v>
-      </c>
-      <c r="AF27" s="8">
-        <f t="shared" si="71"/>
-        <v>-1.7077335935594046E-2</v>
-      </c>
-      <c r="AG27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.28134284016636957</v>
-      </c>
-      <c r="AH27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.21530216226205878</v>
-      </c>
-      <c r="AI27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.22180521673860012</v>
-      </c>
-      <c r="AJ27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.18953241699239368</v>
-      </c>
-      <c r="AK27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AL27" s="8">
-        <f t="shared" si="71"/>
+      <c r="AX27" s="8">
+        <f t="shared" si="68"/>
         <v>0.2</v>
       </c>
-      <c r="AM27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
-      <c r="AN27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
-      <c r="AO27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
-      <c r="AP27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
-      <c r="AQ27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
-      <c r="AR27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
-      <c r="AS27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
-      <c r="AT27" s="8">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
-      <c r="AW27" t="s">
+      <c r="BA27" t="s">
         <v>58</v>
       </c>
-      <c r="AX27" s="9">
-        <f>AX26/AT18</f>
-        <v>91.087945307638549</v>
+      <c r="BB27" s="9">
+        <f>BB26/AX18</f>
+        <v>67.500416324015845</v>
       </c>
     </row>
-    <row r="28" spans="1:146" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:150" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>52</v>
       </c>
@@ -5133,191 +5241,195 @@
         <v>1.8189692507579038E-2</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" ref="D28:V28" si="72">D17/D3</f>
+        <f t="shared" ref="D28:V28" si="69">D17/D3</f>
         <v>0.29081923588671355</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.18703059168345851</v>
       </c>
       <c r="F28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.25621321124918245</v>
       </c>
       <c r="G28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.1818332504558263</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.18980442449503046</v>
       </c>
       <c r="I28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.17583306373341961</v>
       </c>
       <c r="J28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.11578490893321769</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>7.8513034089156261E-2</v>
       </c>
       <c r="L28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>-5.0102850426094622E-2</v>
       </c>
       <c r="M28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.19427402862985685</v>
       </c>
       <c r="N28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.12474603819585535</v>
       </c>
       <c r="O28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.11292613636363637</v>
       </c>
       <c r="P28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.14121037463976946</v>
       </c>
       <c r="Q28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.13750337018064168</v>
       </c>
       <c r="R28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.17468228258160975</v>
       </c>
       <c r="S28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.11533965450058449</v>
       </c>
       <c r="T28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.14305643627140138</v>
       </c>
       <c r="U28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.12871160953230534</v>
       </c>
       <c r="V28" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="69"/>
         <v>0.13399474061678221</v>
       </c>
       <c r="W28" s="8">
-        <f t="shared" ref="W28:Z28" si="73">W17/W3</f>
+        <f t="shared" ref="W28:Z28" si="70">W17/W3</f>
         <v>0.16519060454370427</v>
       </c>
       <c r="X28" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.15214768339768339</v>
       </c>
       <c r="Y28" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="70"/>
         <v>0.14827135558987764</v>
       </c>
       <c r="Z28" s="8">
-        <f t="shared" si="73"/>
-        <v>0.13719978318654241</v>
-      </c>
-      <c r="AC28" s="8">
-        <f t="shared" ref="AC28:AT28" si="74">AC17/AC3</f>
+        <f t="shared" si="70"/>
+        <v>0.16562932226832641</v>
+      </c>
+      <c r="AA28" s="8"/>
+      <c r="AB28" s="8"/>
+      <c r="AC28" s="8"/>
+      <c r="AD28" s="8"/>
+      <c r="AG28" s="8">
+        <f t="shared" ref="AG28:AX28" si="71">AG17/AG3</f>
         <v>0.13313054171251051</v>
       </c>
-      <c r="AD28" s="8">
-        <f t="shared" si="74"/>
+      <c r="AH28" s="8">
+        <f t="shared" si="71"/>
         <v>0.13836371820841772</v>
       </c>
-      <c r="AE28" s="8">
-        <f t="shared" si="74"/>
+      <c r="AI28" s="8">
+        <f t="shared" si="71"/>
         <v>0.19586091171809453</v>
       </c>
-      <c r="AF28" s="8">
-        <f t="shared" si="74"/>
+      <c r="AJ28" s="8">
+        <f t="shared" si="71"/>
         <v>0.16432146939419021</v>
       </c>
-      <c r="AG28" s="8">
-        <f t="shared" si="74"/>
+      <c r="AK28" s="8">
+        <f t="shared" si="71"/>
         <v>8.7906097826876958E-2</v>
       </c>
-      <c r="AH28" s="8">
-        <f t="shared" si="74"/>
+      <c r="AL28" s="8">
+        <f t="shared" si="71"/>
         <v>0.14262201471230393</v>
       </c>
-      <c r="AI28" s="8">
-        <f t="shared" si="74"/>
+      <c r="AM28" s="8">
+        <f t="shared" si="71"/>
         <v>0.13042110890964556</v>
       </c>
-      <c r="AJ28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.15040802096543235</v>
-      </c>
-      <c r="AK28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.1593443704739568</v>
-      </c>
-      <c r="AL28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.16788124940836865</v>
-      </c>
-      <c r="AM28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.16916019744723731</v>
-      </c>
       <c r="AN28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.17042615811598763</v>
+        <f t="shared" si="71"/>
+        <v>0.15775352707102375</v>
       </c>
       <c r="AO28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.17044836919791129</v>
+        <f t="shared" si="71"/>
+        <v>0.13708164780696463</v>
       </c>
       <c r="AP28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.17047036036813268</v>
+        <f t="shared" si="71"/>
+        <v>0.13763381378876857</v>
       </c>
       <c r="AQ28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.17049213380399547</v>
+        <f t="shared" si="71"/>
+        <v>0.13897552959578163</v>
       </c>
       <c r="AR28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.17051369166128538</v>
+        <f t="shared" si="71"/>
+        <v>0.14030361288986476</v>
       </c>
       <c r="AS28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.1705350360744437</v>
+        <f t="shared" si="71"/>
+        <v>0.14032729785969833</v>
       </c>
       <c r="AT28" s="8">
-        <f t="shared" si="74"/>
-        <v>0.17055616915677865</v>
-      </c>
-      <c r="AW28" t="s">
+        <f t="shared" si="71"/>
+        <v>0.14035074832488012</v>
+      </c>
+      <c r="AU28" s="8">
+        <f t="shared" si="71"/>
+        <v>0.14037396660723828</v>
+      </c>
+      <c r="AV28" s="8">
+        <f t="shared" si="71"/>
+        <v>0.14039695500561275</v>
+      </c>
+      <c r="AW28" s="8">
+        <f t="shared" si="71"/>
+        <v>0.14041971579608251</v>
+      </c>
+      <c r="AX28" s="8">
+        <f t="shared" si="71"/>
+        <v>0.14044225123219117</v>
+      </c>
+      <c r="BA28" t="s">
         <v>59</v>
       </c>
-      <c r="AX28" s="9">
+      <c r="BB28" s="9">
         <f>Main!D3</f>
-        <v>73.02</v>
+        <v>42.32</v>
       </c>
     </row>
-    <row r="29" spans="1:146" x14ac:dyDescent="0.3">
-      <c r="AW29" s="6" t="s">
+    <row r="29" spans="1:150" x14ac:dyDescent="0.3">
+      <c r="BA29" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AX29" s="10">
-        <f>AX27/AX28-1</f>
-        <v>0.24743830878716189</v>
+      <c r="BB29" s="10">
+        <f>BB27/BB28-1</f>
+        <v>0.59500038572816272</v>
       </c>
     </row>
-    <row r="30" spans="1:146" x14ac:dyDescent="0.3">
-      <c r="AW30" t="s">
+    <row r="30" spans="1:150" x14ac:dyDescent="0.3">
+      <c r="BA30" t="s">
         <v>61</v>
       </c>
-      <c r="AX30" s="2" t="s">
+      <c r="BB30" s="2" t="s">
         <v>66</v>
       </c>
     </row>
